--- a/experiments/full_estimate_review_pipeline/output/step_12_all_sections_review_template.xlsx
+++ b/experiments/full_estimate_review_pipeline/output/step_12_all_sections_review_template.xlsx
@@ -13656,130 +13656,102 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="44" customWidth="1" min="12" max="12"/>
-    <col width="78" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
-    <col hidden="1" width="20" customWidth="1" min="15" max="15"/>
-    <col hidden="1" width="26" customWidth="1" min="16" max="16"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="26" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Тип</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
+          <t>Земляные работы — Маршруты траншей</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Код маршрута</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>Длина, м</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>Глубина, м</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>Ширина, м</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>Объем, м3</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Диаметр, мм</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Длина одной, м</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Количество</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Итоговая длина, м</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Включено</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Источник</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Фрагмент проекта</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>Комментарий Елены</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>section_code</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>detail_table_key</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>Будущие detail-шаблоны</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr"/>
-      <c r="C2" s="4" t="inlineStr"/>
-      <c r="D2" s="4" t="inlineStr"/>
-      <c r="E2" s="4" t="inlineStr"/>
-      <c r="F2" s="4" t="inlineStr"/>
-      <c r="G2" s="4" t="inlineStr"/>
-      <c r="H2" s="4" t="inlineStr"/>
-      <c r="I2" s="4" t="inlineStr"/>
-      <c r="J2" s="4" t="inlineStr"/>
-      <c r="K2" s="4" t="inlineStr"/>
-      <c r="L2" s="4" t="inlineStr"/>
-      <c r="M2" s="4" t="inlineStr"/>
-      <c r="N2" s="4" t="inlineStr"/>
-      <c r="O2" s="4" t="inlineStr"/>
-      <c r="P2" s="4" t="inlineStr"/>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>target_code</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
+      <c r="P2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n"/>
@@ -13802,78 +13774,82 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Арматура</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr"/>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="4" t="inlineStr"/>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr"/>
-      <c r="O4" s="4" t="inlineStr"/>
-      <c r="P4" s="4" t="inlineStr"/>
+          <t>Земляные работы — Трубы коммуникаций</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="4" t="n"/>
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="4" t="n"/>
+      <c r="K4" s="4" t="n"/>
+      <c r="L4" s="4" t="n"/>
+      <c r="M4" s="4" t="n"/>
+      <c r="N4" s="4" t="n"/>
+      <c r="O4" s="4" t="n"/>
+      <c r="P4" s="4" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Арматура</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Марка / позиция арматуры</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr"/>
-      <c r="D5" s="7" t="inlineStr"/>
-      <c r="E5" s="7" t="inlineStr"/>
-      <c r="F5" s="7" t="inlineStr"/>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Код позиции</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>Диаметр, мм</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>Длина, м/п</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>Количество</t>
-        </is>
-      </c>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>Итоговая длина, м/п</t>
-        </is>
-      </c>
-      <c r="K5" s="7" t="inlineStr"/>
-      <c r="L5" s="7" t="inlineStr"/>
-      <c r="M5" s="7" t="inlineStr">
-        <is>
-          <t>Для foundation/floor slabs/load-bearing/lintels: spec_length_m является первичной единицей, если PDF дает м/п.</t>
-        </is>
-      </c>
-      <c r="N5" s="7" t="inlineStr"/>
-      <c r="O5" s="7" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
-      <c r="P5" s="7" t="inlineStr">
-        <is>
-          <t>rebar_items</t>
-        </is>
-      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>Длина одной, м</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>Количество, шт</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>Итоговая длина, м</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="inlineStr">
+        <is>
+          <t>Включено</t>
+        </is>
+      </c>
+      <c r="H5" s="1" t="inlineStr">
+        <is>
+          <t>Комментарий Елены</t>
+        </is>
+      </c>
+      <c r="I5" s="1" t="inlineStr">
+        <is>
+          <t>section_code</t>
+        </is>
+      </c>
+      <c r="J5" s="1" t="inlineStr">
+        <is>
+          <t>target_code</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n"/>
+      <c r="L5" s="2" t="n"/>
+      <c r="M5" s="2" t="n"/>
+      <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
+      <c r="P5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n"/>
@@ -13896,78 +13872,74 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Балки</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr"/>
-      <c r="C7" s="4" t="inlineStr"/>
-      <c r="D7" s="4" t="inlineStr"/>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr"/>
-      <c r="I7" s="4" t="inlineStr"/>
-      <c r="J7" s="4" t="inlineStr"/>
-      <c r="K7" s="4" t="inlineStr"/>
-      <c r="L7" s="4" t="inlineStr"/>
-      <c r="M7" s="4" t="inlineStr"/>
-      <c r="N7" s="4" t="inlineStr"/>
-      <c r="O7" s="4" t="inlineStr"/>
-      <c r="P7" s="4" t="inlineStr"/>
+          <t>Фундаментная плита — Арматура фундаментной плиты по диаметрам</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="4" t="n"/>
+      <c r="G7" s="4" t="n"/>
+      <c r="H7" s="4" t="n"/>
+      <c r="I7" s="4" t="n"/>
+      <c r="J7" s="4" t="n"/>
+      <c r="K7" s="4" t="n"/>
+      <c r="L7" s="4" t="n"/>
+      <c r="M7" s="4" t="n"/>
+      <c r="N7" s="4" t="n"/>
+      <c r="O7" s="4" t="n"/>
+      <c r="P7" s="4" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Балка</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Балка / позиция</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Длина, м</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>Высота, м</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>Ширина, м</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr"/>
-      <c r="G8" s="7" t="inlineStr"/>
-      <c r="H8" s="7" t="inlineStr"/>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>Количество</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr"/>
-      <c r="K8" s="7" t="inlineStr"/>
-      <c r="L8" s="7" t="inlineStr"/>
-      <c r="M8" s="7" t="inlineStr">
-        <is>
-          <t>Для плит перекрытия с балками: геометрия балки и/или строка спецификации Ж/Б балок.</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="inlineStr"/>
-      <c r="O8" s="7" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
-      <c r="P8" s="7" t="inlineStr">
-        <is>
-          <t>beam_items</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>Класс стали</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>Диаметр, мм</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>Длина по спецификации, мп</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>Масса 1 м, кг/м</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>Комментарий Елены</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>section_code</t>
+        </is>
+      </c>
+      <c r="H8" s="1" t="inlineStr">
+        <is>
+          <t>target_code</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="n"/>
+      <c r="L8" s="2" t="n"/>
+      <c r="M8" s="2" t="n"/>
+      <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
+      <c r="P8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -13990,74 +13962,86 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Перемычки</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr"/>
-      <c r="C10" s="4" t="inlineStr"/>
-      <c r="D10" s="4" t="inlineStr"/>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr"/>
-      <c r="G10" s="4" t="inlineStr"/>
-      <c r="H10" s="4" t="inlineStr"/>
-      <c r="I10" s="4" t="inlineStr"/>
-      <c r="J10" s="4" t="inlineStr"/>
-      <c r="K10" s="4" t="inlineStr"/>
-      <c r="L10" s="4" t="inlineStr"/>
-      <c r="M10" s="4" t="inlineStr"/>
-      <c r="N10" s="4" t="inlineStr"/>
-      <c r="O10" s="4" t="inlineStr"/>
-      <c r="P10" s="4" t="inlineStr"/>
+          <t>Стены и перемычки — Арматура несущих стен по диаметрам</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n"/>
+      <c r="G10" s="4" t="n"/>
+      <c r="H10" s="4" t="n"/>
+      <c r="I10" s="4" t="n"/>
+      <c r="J10" s="4" t="n"/>
+      <c r="K10" s="4" t="n"/>
+      <c r="L10" s="4" t="n"/>
+      <c r="M10" s="4" t="n"/>
+      <c r="N10" s="4" t="n"/>
+      <c r="O10" s="4" t="n"/>
+      <c r="P10" s="4" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Перемычка</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Перемычка / U-блок</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>Длина, м</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr"/>
-      <c r="E11" s="7" t="inlineStr"/>
-      <c r="F11" s="7" t="inlineStr"/>
-      <c r="G11" s="7" t="inlineStr"/>
-      <c r="H11" s="7" t="inlineStr"/>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>Количество</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>Итоговая длина, м</t>
-        </is>
-      </c>
-      <c r="K11" s="7" t="inlineStr"/>
-      <c r="L11" s="7" t="inlineStr"/>
-      <c r="M11" s="7" t="inlineStr">
-        <is>
-          <t>Для load_bearing_walls_lintels: длины перемычек и арматуры перемычек.</t>
-        </is>
-      </c>
-      <c r="N11" s="7" t="inlineStr"/>
-      <c r="O11" s="7" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
-      <c r="P11" s="7" t="inlineStr">
-        <is>
-          <t>lintel_items</t>
-        </is>
-      </c>
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Этаж</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>Компонент</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>Класс стали</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>Диаметр, мм</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>Длина по спецификации, мп</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="inlineStr">
+        <is>
+          <t>Масса 1 м, кг/м</t>
+        </is>
+      </c>
+      <c r="G11" s="1" t="inlineStr">
+        <is>
+          <t>Длина прутка, м</t>
+        </is>
+      </c>
+      <c r="H11" s="1" t="inlineStr">
+        <is>
+          <t>Цена за метр, руб/м</t>
+        </is>
+      </c>
+      <c r="I11" s="1" t="inlineStr">
+        <is>
+          <t>Комментарий Елены</t>
+        </is>
+      </c>
+      <c r="J11" s="1" t="inlineStr">
+        <is>
+          <t>section_code</t>
+        </is>
+      </c>
+      <c r="K11" s="1" t="inlineStr">
+        <is>
+          <t>target_code</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="n"/>
+      <c r="M11" s="2" t="n"/>
+      <c r="N11" s="2" t="n"/>
+      <c r="O11" s="2" t="n"/>
+      <c r="P11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n"/>
@@ -14080,70 +14064,86 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Вентканалы / сегменты</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr"/>
-      <c r="C13" s="4" t="inlineStr"/>
-      <c r="D13" s="4" t="inlineStr"/>
-      <c r="E13" s="4" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr"/>
-      <c r="G13" s="4" t="inlineStr"/>
-      <c r="H13" s="4" t="inlineStr"/>
-      <c r="I13" s="4" t="inlineStr"/>
-      <c r="J13" s="4" t="inlineStr"/>
-      <c r="K13" s="4" t="inlineStr"/>
-      <c r="L13" s="4" t="inlineStr"/>
-      <c r="M13" s="4" t="inlineStr"/>
-      <c r="N13" s="4" t="inlineStr"/>
-      <c r="O13" s="4" t="inlineStr"/>
-      <c r="P13" s="4" t="inlineStr"/>
+          <t>Стены и перемычки — Арматура перемычек по диаметрам</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="4" t="n"/>
+      <c r="G13" s="4" t="n"/>
+      <c r="H13" s="4" t="n"/>
+      <c r="I13" s="4" t="n"/>
+      <c r="J13" s="4" t="n"/>
+      <c r="K13" s="4" t="n"/>
+      <c r="L13" s="4" t="n"/>
+      <c r="M13" s="4" t="n"/>
+      <c r="N13" s="4" t="n"/>
+      <c r="O13" s="4" t="n"/>
+      <c r="P13" s="4" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Вентканал</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Сегмент / канал</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Длина, м</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr"/>
-      <c r="E14" s="7" t="inlineStr"/>
-      <c r="F14" s="7" t="inlineStr"/>
-      <c r="G14" s="7" t="inlineStr"/>
-      <c r="H14" s="7" t="inlineStr"/>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>Количество</t>
-        </is>
-      </c>
-      <c r="J14" s="7" t="inlineStr"/>
-      <c r="K14" s="7" t="inlineStr"/>
-      <c r="L14" s="7" t="inlineStr"/>
-      <c r="M14" s="7" t="inlineStr">
-        <is>
-          <t>Для Schiedel и обкладки вентканалов, если PDF дает повторяющиеся сегменты.</t>
-        </is>
-      </c>
-      <c r="N14" s="7" t="inlineStr"/>
-      <c r="O14" s="7" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
-      <c r="P14" s="7" t="inlineStr">
-        <is>
-          <t>vent_chimney_cladding_segments</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Этаж</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>Компонент</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>Класс стали</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>Диаметр, мм</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t>Длина по спецификации, мп</t>
+        </is>
+      </c>
+      <c r="F14" s="1" t="inlineStr">
+        <is>
+          <t>Масса 1 м, кг/м</t>
+        </is>
+      </c>
+      <c r="G14" s="1" t="inlineStr">
+        <is>
+          <t>Длина прутка, м</t>
+        </is>
+      </c>
+      <c r="H14" s="1" t="inlineStr">
+        <is>
+          <t>Цена за метр, руб/м</t>
+        </is>
+      </c>
+      <c r="I14" s="1" t="inlineStr">
+        <is>
+          <t>Комментарий Елены</t>
+        </is>
+      </c>
+      <c r="J14" s="1" t="inlineStr">
+        <is>
+          <t>section_code</t>
+        </is>
+      </c>
+      <c r="K14" s="1" t="inlineStr">
+        <is>
+          <t>target_code</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="n"/>
+      <c r="M14" s="2" t="n"/>
+      <c r="N14" s="2" t="n"/>
+      <c r="O14" s="2" t="n"/>
+      <c r="P14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n"/>
@@ -14166,70 +14166,70 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Спецификация материалов</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr"/>
-      <c r="C16" s="4" t="inlineStr"/>
-      <c r="D16" s="4" t="inlineStr"/>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr"/>
-      <c r="G16" s="4" t="inlineStr"/>
-      <c r="H16" s="4" t="inlineStr"/>
-      <c r="I16" s="4" t="inlineStr"/>
-      <c r="J16" s="4" t="inlineStr"/>
-      <c r="K16" s="4" t="inlineStr"/>
-      <c r="L16" s="4" t="inlineStr"/>
-      <c r="M16" s="4" t="inlineStr"/>
-      <c r="N16" s="4" t="inlineStr"/>
-      <c r="O16" s="4" t="inlineStr"/>
-      <c r="P16" s="4" t="inlineStr"/>
+          <t>Стены и перемычки — Позиции перемычек</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="n"/>
+      <c r="G16" s="4" t="n"/>
+      <c r="H16" s="4" t="n"/>
+      <c r="I16" s="4" t="n"/>
+      <c r="J16" s="4" t="n"/>
+      <c r="K16" s="4" t="n"/>
+      <c r="L16" s="4" t="n"/>
+      <c r="M16" s="4" t="n"/>
+      <c r="N16" s="4" t="n"/>
+      <c r="O16" s="4" t="n"/>
+      <c r="P16" s="4" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Материал</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Материал / строка спецификации</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr"/>
-      <c r="D17" s="7" t="inlineStr"/>
-      <c r="E17" s="7" t="inlineStr"/>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>Объем, м3</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="inlineStr"/>
-      <c r="H17" s="7" t="inlineStr"/>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>Количество</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="inlineStr"/>
-      <c r="K17" s="7" t="inlineStr"/>
-      <c r="L17" s="7" t="inlineStr"/>
-      <c r="M17" s="7" t="inlineStr">
-        <is>
-          <t>Для ЭППС, бетона, опалубки, мембран и других строк спецификаций, которые не являются отдельной геометрией.</t>
-        </is>
-      </c>
-      <c r="N17" s="7" t="inlineStr"/>
-      <c r="O17" s="7" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
-      <c r="P17" s="7" t="inlineStr">
-        <is>
-          <t>material_spec_rows</t>
-        </is>
-      </c>
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Марка</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>Длина одной, м</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>Количество, шт</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t>Итоговая длина, м</t>
+        </is>
+      </c>
+      <c r="E17" s="1" t="inlineStr">
+        <is>
+          <t>Комментарий Елены</t>
+        </is>
+      </c>
+      <c r="F17" s="1" t="inlineStr">
+        <is>
+          <t>section_code</t>
+        </is>
+      </c>
+      <c r="G17" s="1" t="inlineStr">
+        <is>
+          <t>target_code</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="n"/>
+      <c r="M17" s="2" t="n"/>
+      <c r="N17" s="2" t="n"/>
+      <c r="O17" s="2" t="n"/>
+      <c r="P17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n"/>
@@ -14252,58 +14252,1674 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
+          <t>Перекрытие 1 этажа — Арматура плиты перекрытия 1-го этажа по диаметрам</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="4" t="n"/>
+      <c r="H19" s="4" t="n"/>
+      <c r="I19" s="4" t="n"/>
+      <c r="J19" s="4" t="n"/>
+      <c r="K19" s="4" t="n"/>
+      <c r="L19" s="4" t="n"/>
+      <c r="M19" s="4" t="n"/>
+      <c r="N19" s="4" t="n"/>
+      <c r="O19" s="4" t="n"/>
+      <c r="P19" s="4" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Этаж</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>Компонент</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>Класс стали</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t>Диаметр, мм</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="inlineStr">
+        <is>
+          <t>Длина по спецификации, мп</t>
+        </is>
+      </c>
+      <c r="F20" s="1" t="inlineStr">
+        <is>
+          <t>Масса 1 м, кг/м</t>
+        </is>
+      </c>
+      <c r="G20" s="1" t="inlineStr">
+        <is>
+          <t>Длина прутка, м</t>
+        </is>
+      </c>
+      <c r="H20" s="1" t="inlineStr">
+        <is>
+          <t>Цена за метр, руб/мп</t>
+        </is>
+      </c>
+      <c r="I20" s="1" t="inlineStr">
+        <is>
+          <t>Комментарий Елены</t>
+        </is>
+      </c>
+      <c r="J20" s="1" t="inlineStr">
+        <is>
+          <t>section_code</t>
+        </is>
+      </c>
+      <c r="K20" s="1" t="inlineStr">
+        <is>
+          <t>target_code</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="n"/>
+      <c r="M20" s="2" t="n"/>
+      <c r="N20" s="2" t="n"/>
+      <c r="O20" s="2" t="n"/>
+      <c r="P20" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n"/>
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
+      <c r="E21" s="2" t="n"/>
+      <c r="F21" s="2" t="n"/>
+      <c r="G21" s="2" t="n"/>
+      <c r="H21" s="2" t="n"/>
+      <c r="I21" s="2" t="n"/>
+      <c r="J21" s="2" t="n"/>
+      <c r="K21" s="2" t="n"/>
+      <c r="L21" s="2" t="n"/>
+      <c r="M21" s="2" t="n"/>
+      <c r="N21" s="2" t="n"/>
+      <c r="O21" s="2" t="n"/>
+      <c r="P21" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Перекрытие 1 этажа — Ж/Б балки плиты перекрытия 1-го этажа</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="n"/>
+      <c r="G22" s="4" t="n"/>
+      <c r="H22" s="4" t="n"/>
+      <c r="I22" s="4" t="n"/>
+      <c r="J22" s="4" t="n"/>
+      <c r="K22" s="4" t="n"/>
+      <c r="L22" s="4" t="n"/>
+      <c r="M22" s="4" t="n"/>
+      <c r="N22" s="4" t="n"/>
+      <c r="O22" s="4" t="n"/>
+      <c r="P22" s="4" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>Код</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="inlineStr">
+        <is>
+          <t>Длина, м</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="inlineStr">
+        <is>
+          <t>Ширина, м</t>
+        </is>
+      </c>
+      <c r="E23" s="1" t="inlineStr">
+        <is>
+          <t>Высота, м</t>
+        </is>
+      </c>
+      <c r="F23" s="1" t="inlineStr">
+        <is>
+          <t>Количество, шт</t>
+        </is>
+      </c>
+      <c r="G23" s="1" t="inlineStr">
+        <is>
+          <t>Комментарий Елены</t>
+        </is>
+      </c>
+      <c r="H23" s="1" t="inlineStr">
+        <is>
+          <t>section_code</t>
+        </is>
+      </c>
+      <c r="I23" s="1" t="inlineStr">
+        <is>
+          <t>target_code</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="n"/>
+      <c r="K23" s="2" t="n"/>
+      <c r="L23" s="2" t="n"/>
+      <c r="M23" s="2" t="n"/>
+      <c r="N23" s="2" t="n"/>
+      <c r="O23" s="2" t="n"/>
+      <c r="P23" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
+      <c r="E24" s="2" t="n"/>
+      <c r="F24" s="2" t="n"/>
+      <c r="G24" s="2" t="n"/>
+      <c r="H24" s="2" t="n"/>
+      <c r="I24" s="2" t="n"/>
+      <c r="J24" s="2" t="n"/>
+      <c r="K24" s="2" t="n"/>
+      <c r="L24" s="2" t="n"/>
+      <c r="M24" s="2" t="n"/>
+      <c r="N24" s="2" t="n"/>
+      <c r="O24" s="2" t="n"/>
+      <c r="P24" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Перекрытие 1 этажа — Контрольные итоги таблицы Ж/Б балок</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4" t="n"/>
+      <c r="G25" s="4" t="n"/>
+      <c r="H25" s="4" t="n"/>
+      <c r="I25" s="4" t="n"/>
+      <c r="J25" s="4" t="n"/>
+      <c r="K25" s="4" t="n"/>
+      <c r="L25" s="4" t="n"/>
+      <c r="M25" s="4" t="n"/>
+      <c r="N25" s="4" t="n"/>
+      <c r="O25" s="4" t="n"/>
+      <c r="P25" s="4" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>Строка итога</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="inlineStr">
+        <is>
+          <t>Значение</t>
+        </is>
+      </c>
+      <c r="C26" s="1" t="inlineStr">
+        <is>
+          <t>Ед.</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="inlineStr">
+        <is>
+          <t>Комментарий Елены</t>
+        </is>
+      </c>
+      <c r="E26" s="1" t="inlineStr">
+        <is>
+          <t>section_code</t>
+        </is>
+      </c>
+      <c r="F26" s="1" t="inlineStr">
+        <is>
+          <t>target_code</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="n"/>
+      <c r="H26" s="2" t="n"/>
+      <c r="I26" s="2" t="n"/>
+      <c r="J26" s="2" t="n"/>
+      <c r="K26" s="2" t="n"/>
+      <c r="L26" s="2" t="n"/>
+      <c r="M26" s="2" t="n"/>
+      <c r="N26" s="2" t="n"/>
+      <c r="O26" s="2" t="n"/>
+      <c r="P26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n"/>
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n"/>
+      <c r="E27" s="2" t="n"/>
+      <c r="F27" s="2" t="n"/>
+      <c r="G27" s="2" t="n"/>
+      <c r="H27" s="2" t="n"/>
+      <c r="I27" s="2" t="n"/>
+      <c r="J27" s="2" t="n"/>
+      <c r="K27" s="2" t="n"/>
+      <c r="L27" s="2" t="n"/>
+      <c r="M27" s="2" t="n"/>
+      <c r="N27" s="2" t="n"/>
+      <c r="O27" s="2" t="n"/>
+      <c r="P27" s="2" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Перекрытие 2 этажа — Позиции балок плиты перекрытия 2-го этажа</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="4" t="n"/>
+      <c r="I28" s="4" t="n"/>
+      <c r="J28" s="4" t="n"/>
+      <c r="K28" s="4" t="n"/>
+      <c r="L28" s="4" t="n"/>
+      <c r="M28" s="4" t="n"/>
+      <c r="N28" s="4" t="n"/>
+      <c r="O28" s="4" t="n"/>
+      <c r="P28" s="4" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>Код балки</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="C29" s="1" t="inlineStr">
+        <is>
+          <t>Длина, м</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="inlineStr">
+        <is>
+          <t>Ширина, м</t>
+        </is>
+      </c>
+      <c r="E29" s="1" t="inlineStr">
+        <is>
+          <t>Высота, м</t>
+        </is>
+      </c>
+      <c r="F29" s="1" t="inlineStr">
+        <is>
+          <t>Количество, шт</t>
+        </is>
+      </c>
+      <c r="G29" s="1" t="inlineStr">
+        <is>
+          <t>Комментарий Елены</t>
+        </is>
+      </c>
+      <c r="H29" s="1" t="inlineStr">
+        <is>
+          <t>section_code</t>
+        </is>
+      </c>
+      <c r="I29" s="1" t="inlineStr">
+        <is>
+          <t>target_code</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="n"/>
+      <c r="K29" s="2" t="n"/>
+      <c r="L29" s="2" t="n"/>
+      <c r="M29" s="2" t="n"/>
+      <c r="N29" s="2" t="n"/>
+      <c r="O29" s="2" t="n"/>
+      <c r="P29" s="2" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n"/>
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n"/>
+      <c r="E30" s="2" t="n"/>
+      <c r="F30" s="2" t="n"/>
+      <c r="G30" s="2" t="n"/>
+      <c r="H30" s="2" t="n"/>
+      <c r="I30" s="2" t="n"/>
+      <c r="J30" s="2" t="n"/>
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" s="2" t="n"/>
+      <c r="M30" s="2" t="n"/>
+      <c r="N30" s="2" t="n"/>
+      <c r="O30" s="2" t="n"/>
+      <c r="P30" s="2" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Перекрытие 2 этажа — Арматура плиты перекрытия 2-го этажа по диаметрам</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n"/>
+      <c r="C31" s="4" t="n"/>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="4" t="n"/>
+      <c r="H31" s="4" t="n"/>
+      <c r="I31" s="4" t="n"/>
+      <c r="J31" s="4" t="n"/>
+      <c r="K31" s="4" t="n"/>
+      <c r="L31" s="4" t="n"/>
+      <c r="M31" s="4" t="n"/>
+      <c r="N31" s="4" t="n"/>
+      <c r="O31" s="4" t="n"/>
+      <c r="P31" s="4" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Класс стали</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="inlineStr">
+        <is>
+          <t>Диаметр, мм</t>
+        </is>
+      </c>
+      <c r="C32" s="1" t="inlineStr">
+        <is>
+          <t>Длина по спецификации, мп</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="inlineStr">
+        <is>
+          <t>Масса 1 м, кг/м</t>
+        </is>
+      </c>
+      <c r="E32" s="1" t="inlineStr">
+        <is>
+          <t>Длина прутка, м</t>
+        </is>
+      </c>
+      <c r="F32" s="1" t="inlineStr">
+        <is>
+          <t>Цена за метр, руб/мп</t>
+        </is>
+      </c>
+      <c r="G32" s="1" t="inlineStr">
+        <is>
+          <t>Комментарий Елены</t>
+        </is>
+      </c>
+      <c r="H32" s="1" t="inlineStr">
+        <is>
+          <t>section_code</t>
+        </is>
+      </c>
+      <c r="I32" s="1" t="inlineStr">
+        <is>
+          <t>target_code</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="n"/>
+      <c r="K32" s="2" t="n"/>
+      <c r="L32" s="2" t="n"/>
+      <c r="M32" s="2" t="n"/>
+      <c r="N32" s="2" t="n"/>
+      <c r="O32" s="2" t="n"/>
+      <c r="P32" s="2" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n"/>
+      <c r="B33" s="2" t="n"/>
+      <c r="C33" s="2" t="n"/>
+      <c r="D33" s="2" t="n"/>
+      <c r="E33" s="2" t="n"/>
+      <c r="F33" s="2" t="n"/>
+      <c r="G33" s="2" t="n"/>
+      <c r="H33" s="2" t="n"/>
+      <c r="I33" s="2" t="n"/>
+      <c r="J33" s="2" t="n"/>
+      <c r="K33" s="2" t="n"/>
+      <c r="L33" s="2" t="n"/>
+      <c r="M33" s="2" t="n"/>
+      <c r="N33" s="2" t="n"/>
+      <c r="O33" s="2" t="n"/>
+      <c r="P33" s="2" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Кровля — Сырые строки спецификации кровли</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="n"/>
+      <c r="C34" s="4" t="n"/>
+      <c r="D34" s="4" t="n"/>
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="4" t="n"/>
+      <c r="G34" s="4" t="n"/>
+      <c r="H34" s="4" t="n"/>
+      <c r="I34" s="4" t="n"/>
+      <c r="J34" s="4" t="n"/>
+      <c r="K34" s="4" t="n"/>
+      <c r="L34" s="4" t="n"/>
+      <c r="M34" s="4" t="n"/>
+      <c r="N34" s="4" t="n"/>
+      <c r="O34" s="4" t="n"/>
+      <c r="P34" s="4" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="inlineStr">
+        <is>
+          <t>Количество</t>
+        </is>
+      </c>
+      <c r="C35" s="1" t="inlineStr">
+        <is>
+          <t>Ед.</t>
+        </is>
+      </c>
+      <c r="D35" s="1" t="inlineStr">
+        <is>
+          <t>Комментарий Елены</t>
+        </is>
+      </c>
+      <c r="E35" s="1" t="inlineStr">
+        <is>
+          <t>section_code</t>
+        </is>
+      </c>
+      <c r="F35" s="1" t="inlineStr">
+        <is>
+          <t>target_code</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="n"/>
+      <c r="H35" s="2" t="n"/>
+      <c r="I35" s="2" t="n"/>
+      <c r="J35" s="2" t="n"/>
+      <c r="K35" s="2" t="n"/>
+      <c r="L35" s="2" t="n"/>
+      <c r="M35" s="2" t="n"/>
+      <c r="N35" s="2" t="n"/>
+      <c r="O35" s="2" t="n"/>
+      <c r="P35" s="2" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n"/>
+      <c r="B36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n"/>
+      <c r="E36" s="2" t="n"/>
+      <c r="F36" s="2" t="n"/>
+      <c r="G36" s="2" t="n"/>
+      <c r="H36" s="2" t="n"/>
+      <c r="I36" s="2" t="n"/>
+      <c r="J36" s="2" t="n"/>
+      <c r="K36" s="2" t="n"/>
+      <c r="L36" s="2" t="n"/>
+      <c r="M36" s="2" t="n"/>
+      <c r="N36" s="2" t="n"/>
+      <c r="O36" s="2" t="n"/>
+      <c r="P36" s="2" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Вентиляционные каналы Schiedel — Сегменты / строки спецификации вентканалов</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="n"/>
+      <c r="C37" s="4" t="n"/>
+      <c r="D37" s="4" t="n"/>
+      <c r="E37" s="4" t="n"/>
+      <c r="F37" s="4" t="n"/>
+      <c r="G37" s="4" t="n"/>
+      <c r="H37" s="4" t="n"/>
+      <c r="I37" s="4" t="n"/>
+      <c r="J37" s="4" t="n"/>
+      <c r="K37" s="4" t="n"/>
+      <c r="L37" s="4" t="n"/>
+      <c r="M37" s="4" t="n"/>
+      <c r="N37" s="4" t="n"/>
+      <c r="O37" s="4" t="n"/>
+      <c r="P37" s="4" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="B38" s="1" t="inlineStr">
+        <is>
+          <t>Высота / длина, м</t>
+        </is>
+      </c>
+      <c r="C38" s="1" t="inlineStr">
+        <is>
+          <t>Количество, шт</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="inlineStr">
+        <is>
+          <t>Итоговая длина, м</t>
+        </is>
+      </c>
+      <c r="E38" s="1" t="inlineStr">
+        <is>
+          <t>Комментарий Елены</t>
+        </is>
+      </c>
+      <c r="F38" s="1" t="inlineStr">
+        <is>
+          <t>section_code</t>
+        </is>
+      </c>
+      <c r="G38" s="1" t="inlineStr">
+        <is>
+          <t>target_code</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="n"/>
+      <c r="I38" s="2" t="n"/>
+      <c r="J38" s="2" t="n"/>
+      <c r="K38" s="2" t="n"/>
+      <c r="L38" s="2" t="n"/>
+      <c r="M38" s="2" t="n"/>
+      <c r="N38" s="2" t="n"/>
+      <c r="O38" s="2" t="n"/>
+      <c r="P38" s="2" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n"/>
+      <c r="B39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n"/>
+      <c r="E39" s="2" t="n"/>
+      <c r="F39" s="2" t="n"/>
+      <c r="G39" s="2" t="n"/>
+      <c r="H39" s="2" t="n"/>
+      <c r="I39" s="2" t="n"/>
+      <c r="J39" s="2" t="n"/>
+      <c r="K39" s="2" t="n"/>
+      <c r="L39" s="2" t="n"/>
+      <c r="M39" s="2" t="n"/>
+      <c r="N39" s="2" t="n"/>
+      <c r="O39" s="2" t="n"/>
+      <c r="P39" s="2" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Будущие detail-шаблоны (общие заготовки, не привязаны к конкретному контракту)</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="n"/>
+      <c r="C40" s="4" t="n"/>
+      <c r="D40" s="4" t="n"/>
+      <c r="E40" s="4" t="n"/>
+      <c r="F40" s="4" t="n"/>
+      <c r="G40" s="4" t="n"/>
+      <c r="H40" s="4" t="n"/>
+      <c r="I40" s="4" t="n"/>
+      <c r="J40" s="4" t="n"/>
+      <c r="K40" s="4" t="n"/>
+      <c r="L40" s="4" t="n"/>
+      <c r="M40" s="4" t="n"/>
+      <c r="N40" s="4" t="n"/>
+      <c r="O40" s="4" t="n"/>
+      <c r="P40" s="4" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n"/>
+      <c r="B41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n"/>
+      <c r="E41" s="2" t="n"/>
+      <c r="F41" s="2" t="n"/>
+      <c r="G41" s="2" t="n"/>
+      <c r="H41" s="2" t="n"/>
+      <c r="I41" s="2" t="n"/>
+      <c r="J41" s="2" t="n"/>
+      <c r="K41" s="2" t="n"/>
+      <c r="L41" s="2" t="n"/>
+      <c r="M41" s="2" t="n"/>
+      <c r="N41" s="2" t="n"/>
+      <c r="O41" s="2" t="n"/>
+      <c r="P41" s="2" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Арматура</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr"/>
+      <c r="C42" s="4" t="inlineStr"/>
+      <c r="D42" s="4" t="inlineStr"/>
+      <c r="E42" s="4" t="inlineStr"/>
+      <c r="F42" s="4" t="inlineStr"/>
+      <c r="G42" s="4" t="inlineStr"/>
+      <c r="H42" s="4" t="inlineStr"/>
+      <c r="I42" s="4" t="inlineStr"/>
+      <c r="J42" s="4" t="inlineStr"/>
+      <c r="K42" s="4" t="inlineStr"/>
+      <c r="L42" s="4" t="inlineStr"/>
+      <c r="M42" s="4" t="inlineStr"/>
+      <c r="N42" s="4" t="inlineStr"/>
+      <c r="O42" s="4" t="inlineStr"/>
+      <c r="P42" s="4" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>Тип</t>
+        </is>
+      </c>
+      <c r="B43" s="1" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="C43" s="1" t="inlineStr">
+        <is>
+          <t>Длина, м</t>
+        </is>
+      </c>
+      <c r="D43" s="1" t="inlineStr">
+        <is>
+          <t>Глубина, м</t>
+        </is>
+      </c>
+      <c r="E43" s="1" t="inlineStr">
+        <is>
+          <t>Ширина, м</t>
+        </is>
+      </c>
+      <c r="F43" s="1" t="inlineStr">
+        <is>
+          <t>Объем, м3</t>
+        </is>
+      </c>
+      <c r="G43" s="1" t="inlineStr">
+        <is>
+          <t>Диаметр, мм</t>
+        </is>
+      </c>
+      <c r="H43" s="1" t="inlineStr">
+        <is>
+          <t>Длина одной, м</t>
+        </is>
+      </c>
+      <c r="I43" s="1" t="inlineStr">
+        <is>
+          <t>Количество</t>
+        </is>
+      </c>
+      <c r="J43" s="1" t="inlineStr">
+        <is>
+          <t>Итоговая длина, м</t>
+        </is>
+      </c>
+      <c r="K43" s="1" t="inlineStr">
+        <is>
+          <t>Включено</t>
+        </is>
+      </c>
+      <c r="L43" s="1" t="inlineStr">
+        <is>
+          <t>Источник</t>
+        </is>
+      </c>
+      <c r="M43" s="1" t="inlineStr">
+        <is>
+          <t>Фрагмент проекта</t>
+        </is>
+      </c>
+      <c r="N43" s="1" t="inlineStr">
+        <is>
+          <t>Комментарий Елены</t>
+        </is>
+      </c>
+      <c r="O43" s="1" t="inlineStr">
+        <is>
+          <t>section_code</t>
+        </is>
+      </c>
+      <c r="P43" s="1" t="inlineStr">
+        <is>
+          <t>detail_table_key</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>Арматура</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Марка / позиция арматуры</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr"/>
+      <c r="D44" s="7" t="inlineStr"/>
+      <c r="E44" s="7" t="inlineStr"/>
+      <c r="F44" s="7" t="inlineStr"/>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>Диаметр, мм</t>
+        </is>
+      </c>
+      <c r="H44" s="7" t="inlineStr">
+        <is>
+          <t>Длина, м/п</t>
+        </is>
+      </c>
+      <c r="I44" s="7" t="inlineStr">
+        <is>
+          <t>Количество</t>
+        </is>
+      </c>
+      <c r="J44" s="7" t="inlineStr">
+        <is>
+          <t>Итоговая длина, м/п</t>
+        </is>
+      </c>
+      <c r="K44" s="7" t="inlineStr"/>
+      <c r="L44" s="7" t="inlineStr"/>
+      <c r="M44" s="7" t="inlineStr">
+        <is>
+          <t>Для foundation/floor slabs/load-bearing/lintels: spec_length_m является первичной единицей, если PDF дает м/п.</t>
+        </is>
+      </c>
+      <c r="N44" s="7" t="inlineStr"/>
+      <c r="O44" s="7" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="P44" s="7" t="inlineStr">
+        <is>
+          <t>rebar_items</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n"/>
+      <c r="B45" s="2" t="n"/>
+      <c r="C45" s="2" t="n"/>
+      <c r="D45" s="2" t="n"/>
+      <c r="E45" s="2" t="n"/>
+      <c r="F45" s="2" t="n"/>
+      <c r="G45" s="2" t="n"/>
+      <c r="H45" s="2" t="n"/>
+      <c r="I45" s="2" t="n"/>
+      <c r="J45" s="2" t="n"/>
+      <c r="K45" s="2" t="n"/>
+      <c r="L45" s="2" t="n"/>
+      <c r="M45" s="2" t="n"/>
+      <c r="N45" s="2" t="n"/>
+      <c r="O45" s="2" t="n"/>
+      <c r="P45" s="2" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Балки</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr"/>
+      <c r="C46" s="4" t="inlineStr"/>
+      <c r="D46" s="4" t="inlineStr"/>
+      <c r="E46" s="4" t="inlineStr"/>
+      <c r="F46" s="4" t="inlineStr"/>
+      <c r="G46" s="4" t="inlineStr"/>
+      <c r="H46" s="4" t="inlineStr"/>
+      <c r="I46" s="4" t="inlineStr"/>
+      <c r="J46" s="4" t="inlineStr"/>
+      <c r="K46" s="4" t="inlineStr"/>
+      <c r="L46" s="4" t="inlineStr"/>
+      <c r="M46" s="4" t="inlineStr"/>
+      <c r="N46" s="4" t="inlineStr"/>
+      <c r="O46" s="4" t="inlineStr"/>
+      <c r="P46" s="4" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>Тип</t>
+        </is>
+      </c>
+      <c r="B47" s="1" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="C47" s="1" t="inlineStr">
+        <is>
+          <t>Длина, м</t>
+        </is>
+      </c>
+      <c r="D47" s="1" t="inlineStr">
+        <is>
+          <t>Глубина, м</t>
+        </is>
+      </c>
+      <c r="E47" s="1" t="inlineStr">
+        <is>
+          <t>Ширина, м</t>
+        </is>
+      </c>
+      <c r="F47" s="1" t="inlineStr">
+        <is>
+          <t>Объем, м3</t>
+        </is>
+      </c>
+      <c r="G47" s="1" t="inlineStr">
+        <is>
+          <t>Диаметр, мм</t>
+        </is>
+      </c>
+      <c r="H47" s="1" t="inlineStr">
+        <is>
+          <t>Длина одной, м</t>
+        </is>
+      </c>
+      <c r="I47" s="1" t="inlineStr">
+        <is>
+          <t>Количество</t>
+        </is>
+      </c>
+      <c r="J47" s="1" t="inlineStr">
+        <is>
+          <t>Итоговая длина, м</t>
+        </is>
+      </c>
+      <c r="K47" s="1" t="inlineStr">
+        <is>
+          <t>Включено</t>
+        </is>
+      </c>
+      <c r="L47" s="1" t="inlineStr">
+        <is>
+          <t>Источник</t>
+        </is>
+      </c>
+      <c r="M47" s="1" t="inlineStr">
+        <is>
+          <t>Фрагмент проекта</t>
+        </is>
+      </c>
+      <c r="N47" s="1" t="inlineStr">
+        <is>
+          <t>Комментарий Елены</t>
+        </is>
+      </c>
+      <c r="O47" s="1" t="inlineStr">
+        <is>
+          <t>section_code</t>
+        </is>
+      </c>
+      <c r="P47" s="1" t="inlineStr">
+        <is>
+          <t>detail_table_key</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>Балка</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>Балка / позиция</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>Длина, м</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>Высота, м</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>Ширина, м</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr"/>
+      <c r="G48" s="7" t="inlineStr"/>
+      <c r="H48" s="7" t="inlineStr"/>
+      <c r="I48" s="7" t="inlineStr">
+        <is>
+          <t>Количество</t>
+        </is>
+      </c>
+      <c r="J48" s="7" t="inlineStr"/>
+      <c r="K48" s="7" t="inlineStr"/>
+      <c r="L48" s="7" t="inlineStr"/>
+      <c r="M48" s="7" t="inlineStr">
+        <is>
+          <t>Для плит перекрытия с балками: геометрия балки и/или строка спецификации Ж/Б балок.</t>
+        </is>
+      </c>
+      <c r="N48" s="7" t="inlineStr"/>
+      <c r="O48" s="7" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="P48" s="7" t="inlineStr">
+        <is>
+          <t>beam_items</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n"/>
+      <c r="B49" s="2" t="n"/>
+      <c r="C49" s="2" t="n"/>
+      <c r="D49" s="2" t="n"/>
+      <c r="E49" s="2" t="n"/>
+      <c r="F49" s="2" t="n"/>
+      <c r="G49" s="2" t="n"/>
+      <c r="H49" s="2" t="n"/>
+      <c r="I49" s="2" t="n"/>
+      <c r="J49" s="2" t="n"/>
+      <c r="K49" s="2" t="n"/>
+      <c r="L49" s="2" t="n"/>
+      <c r="M49" s="2" t="n"/>
+      <c r="N49" s="2" t="n"/>
+      <c r="O49" s="2" t="n"/>
+      <c r="P49" s="2" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Перемычки</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr"/>
+      <c r="C50" s="4" t="inlineStr"/>
+      <c r="D50" s="4" t="inlineStr"/>
+      <c r="E50" s="4" t="inlineStr"/>
+      <c r="F50" s="4" t="inlineStr"/>
+      <c r="G50" s="4" t="inlineStr"/>
+      <c r="H50" s="4" t="inlineStr"/>
+      <c r="I50" s="4" t="inlineStr"/>
+      <c r="J50" s="4" t="inlineStr"/>
+      <c r="K50" s="4" t="inlineStr"/>
+      <c r="L50" s="4" t="inlineStr"/>
+      <c r="M50" s="4" t="inlineStr"/>
+      <c r="N50" s="4" t="inlineStr"/>
+      <c r="O50" s="4" t="inlineStr"/>
+      <c r="P50" s="4" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>Тип</t>
+        </is>
+      </c>
+      <c r="B51" s="1" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="C51" s="1" t="inlineStr">
+        <is>
+          <t>Длина, м</t>
+        </is>
+      </c>
+      <c r="D51" s="1" t="inlineStr">
+        <is>
+          <t>Глубина, м</t>
+        </is>
+      </c>
+      <c r="E51" s="1" t="inlineStr">
+        <is>
+          <t>Ширина, м</t>
+        </is>
+      </c>
+      <c r="F51" s="1" t="inlineStr">
+        <is>
+          <t>Объем, м3</t>
+        </is>
+      </c>
+      <c r="G51" s="1" t="inlineStr">
+        <is>
+          <t>Диаметр, мм</t>
+        </is>
+      </c>
+      <c r="H51" s="1" t="inlineStr">
+        <is>
+          <t>Длина одной, м</t>
+        </is>
+      </c>
+      <c r="I51" s="1" t="inlineStr">
+        <is>
+          <t>Количество</t>
+        </is>
+      </c>
+      <c r="J51" s="1" t="inlineStr">
+        <is>
+          <t>Итоговая длина, м</t>
+        </is>
+      </c>
+      <c r="K51" s="1" t="inlineStr">
+        <is>
+          <t>Включено</t>
+        </is>
+      </c>
+      <c r="L51" s="1" t="inlineStr">
+        <is>
+          <t>Источник</t>
+        </is>
+      </c>
+      <c r="M51" s="1" t="inlineStr">
+        <is>
+          <t>Фрагмент проекта</t>
+        </is>
+      </c>
+      <c r="N51" s="1" t="inlineStr">
+        <is>
+          <t>Комментарий Елены</t>
+        </is>
+      </c>
+      <c r="O51" s="1" t="inlineStr">
+        <is>
+          <t>section_code</t>
+        </is>
+      </c>
+      <c r="P51" s="1" t="inlineStr">
+        <is>
+          <t>detail_table_key</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>Перемычка</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>Перемычка / U-блок</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>Длина, м</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr"/>
+      <c r="E52" s="7" t="inlineStr"/>
+      <c r="F52" s="7" t="inlineStr"/>
+      <c r="G52" s="7" t="inlineStr"/>
+      <c r="H52" s="7" t="inlineStr"/>
+      <c r="I52" s="7" t="inlineStr">
+        <is>
+          <t>Количество</t>
+        </is>
+      </c>
+      <c r="J52" s="7" t="inlineStr">
+        <is>
+          <t>Итоговая длина, м</t>
+        </is>
+      </c>
+      <c r="K52" s="7" t="inlineStr"/>
+      <c r="L52" s="7" t="inlineStr"/>
+      <c r="M52" s="7" t="inlineStr">
+        <is>
+          <t>Для load_bearing_walls_lintels: длины перемычек и арматуры перемычек.</t>
+        </is>
+      </c>
+      <c r="N52" s="7" t="inlineStr"/>
+      <c r="O52" s="7" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="P52" s="7" t="inlineStr">
+        <is>
+          <t>lintel_items</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n"/>
+      <c r="B53" s="2" t="n"/>
+      <c r="C53" s="2" t="n"/>
+      <c r="D53" s="2" t="n"/>
+      <c r="E53" s="2" t="n"/>
+      <c r="F53" s="2" t="n"/>
+      <c r="G53" s="2" t="n"/>
+      <c r="H53" s="2" t="n"/>
+      <c r="I53" s="2" t="n"/>
+      <c r="J53" s="2" t="n"/>
+      <c r="K53" s="2" t="n"/>
+      <c r="L53" s="2" t="n"/>
+      <c r="M53" s="2" t="n"/>
+      <c r="N53" s="2" t="n"/>
+      <c r="O53" s="2" t="n"/>
+      <c r="P53" s="2" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Вентканалы / сегменты</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr"/>
+      <c r="C54" s="4" t="inlineStr"/>
+      <c r="D54" s="4" t="inlineStr"/>
+      <c r="E54" s="4" t="inlineStr"/>
+      <c r="F54" s="4" t="inlineStr"/>
+      <c r="G54" s="4" t="inlineStr"/>
+      <c r="H54" s="4" t="inlineStr"/>
+      <c r="I54" s="4" t="inlineStr"/>
+      <c r="J54" s="4" t="inlineStr"/>
+      <c r="K54" s="4" t="inlineStr"/>
+      <c r="L54" s="4" t="inlineStr"/>
+      <c r="M54" s="4" t="inlineStr"/>
+      <c r="N54" s="4" t="inlineStr"/>
+      <c r="O54" s="4" t="inlineStr"/>
+      <c r="P54" s="4" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>Тип</t>
+        </is>
+      </c>
+      <c r="B55" s="1" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="C55" s="1" t="inlineStr">
+        <is>
+          <t>Длина, м</t>
+        </is>
+      </c>
+      <c r="D55" s="1" t="inlineStr">
+        <is>
+          <t>Глубина, м</t>
+        </is>
+      </c>
+      <c r="E55" s="1" t="inlineStr">
+        <is>
+          <t>Ширина, м</t>
+        </is>
+      </c>
+      <c r="F55" s="1" t="inlineStr">
+        <is>
+          <t>Объем, м3</t>
+        </is>
+      </c>
+      <c r="G55" s="1" t="inlineStr">
+        <is>
+          <t>Диаметр, мм</t>
+        </is>
+      </c>
+      <c r="H55" s="1" t="inlineStr">
+        <is>
+          <t>Длина одной, м</t>
+        </is>
+      </c>
+      <c r="I55" s="1" t="inlineStr">
+        <is>
+          <t>Количество</t>
+        </is>
+      </c>
+      <c r="J55" s="1" t="inlineStr">
+        <is>
+          <t>Итоговая длина, м</t>
+        </is>
+      </c>
+      <c r="K55" s="1" t="inlineStr">
+        <is>
+          <t>Включено</t>
+        </is>
+      </c>
+      <c r="L55" s="1" t="inlineStr">
+        <is>
+          <t>Источник</t>
+        </is>
+      </c>
+      <c r="M55" s="1" t="inlineStr">
+        <is>
+          <t>Фрагмент проекта</t>
+        </is>
+      </c>
+      <c r="N55" s="1" t="inlineStr">
+        <is>
+          <t>Комментарий Елены</t>
+        </is>
+      </c>
+      <c r="O55" s="1" t="inlineStr">
+        <is>
+          <t>section_code</t>
+        </is>
+      </c>
+      <c r="P55" s="1" t="inlineStr">
+        <is>
+          <t>detail_table_key</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>Вентканал</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>Сегмент / канал</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>Длина, м</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr"/>
+      <c r="E56" s="7" t="inlineStr"/>
+      <c r="F56" s="7" t="inlineStr"/>
+      <c r="G56" s="7" t="inlineStr"/>
+      <c r="H56" s="7" t="inlineStr"/>
+      <c r="I56" s="7" t="inlineStr">
+        <is>
+          <t>Количество</t>
+        </is>
+      </c>
+      <c r="J56" s="7" t="inlineStr"/>
+      <c r="K56" s="7" t="inlineStr"/>
+      <c r="L56" s="7" t="inlineStr"/>
+      <c r="M56" s="7" t="inlineStr">
+        <is>
+          <t>Для Schiedel и обкладки вентканалов, если PDF дает повторяющиеся сегменты.</t>
+        </is>
+      </c>
+      <c r="N56" s="7" t="inlineStr"/>
+      <c r="O56" s="7" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="P56" s="7" t="inlineStr">
+        <is>
+          <t>vent_chimney_cladding_segments</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n"/>
+      <c r="B57" s="2" t="n"/>
+      <c r="C57" s="2" t="n"/>
+      <c r="D57" s="2" t="n"/>
+      <c r="E57" s="2" t="n"/>
+      <c r="F57" s="2" t="n"/>
+      <c r="G57" s="2" t="n"/>
+      <c r="H57" s="2" t="n"/>
+      <c r="I57" s="2" t="n"/>
+      <c r="J57" s="2" t="n"/>
+      <c r="K57" s="2" t="n"/>
+      <c r="L57" s="2" t="n"/>
+      <c r="M57" s="2" t="n"/>
+      <c r="N57" s="2" t="n"/>
+      <c r="O57" s="2" t="n"/>
+      <c r="P57" s="2" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Спецификация материалов</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr"/>
+      <c r="C58" s="4" t="inlineStr"/>
+      <c r="D58" s="4" t="inlineStr"/>
+      <c r="E58" s="4" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr"/>
+      <c r="G58" s="4" t="inlineStr"/>
+      <c r="H58" s="4" t="inlineStr"/>
+      <c r="I58" s="4" t="inlineStr"/>
+      <c r="J58" s="4" t="inlineStr"/>
+      <c r="K58" s="4" t="inlineStr"/>
+      <c r="L58" s="4" t="inlineStr"/>
+      <c r="M58" s="4" t="inlineStr"/>
+      <c r="N58" s="4" t="inlineStr"/>
+      <c r="O58" s="4" t="inlineStr"/>
+      <c r="P58" s="4" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>Тип</t>
+        </is>
+      </c>
+      <c r="B59" s="1" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="C59" s="1" t="inlineStr">
+        <is>
+          <t>Длина, м</t>
+        </is>
+      </c>
+      <c r="D59" s="1" t="inlineStr">
+        <is>
+          <t>Глубина, м</t>
+        </is>
+      </c>
+      <c r="E59" s="1" t="inlineStr">
+        <is>
+          <t>Ширина, м</t>
+        </is>
+      </c>
+      <c r="F59" s="1" t="inlineStr">
+        <is>
+          <t>Объем, м3</t>
+        </is>
+      </c>
+      <c r="G59" s="1" t="inlineStr">
+        <is>
+          <t>Диаметр, мм</t>
+        </is>
+      </c>
+      <c r="H59" s="1" t="inlineStr">
+        <is>
+          <t>Длина одной, м</t>
+        </is>
+      </c>
+      <c r="I59" s="1" t="inlineStr">
+        <is>
+          <t>Количество</t>
+        </is>
+      </c>
+      <c r="J59" s="1" t="inlineStr">
+        <is>
+          <t>Итоговая длина, м</t>
+        </is>
+      </c>
+      <c r="K59" s="1" t="inlineStr">
+        <is>
+          <t>Включено</t>
+        </is>
+      </c>
+      <c r="L59" s="1" t="inlineStr">
+        <is>
+          <t>Источник</t>
+        </is>
+      </c>
+      <c r="M59" s="1" t="inlineStr">
+        <is>
+          <t>Фрагмент проекта</t>
+        </is>
+      </c>
+      <c r="N59" s="1" t="inlineStr">
+        <is>
+          <t>Комментарий Елены</t>
+        </is>
+      </c>
+      <c r="O59" s="1" t="inlineStr">
+        <is>
+          <t>section_code</t>
+        </is>
+      </c>
+      <c r="P59" s="1" t="inlineStr">
+        <is>
+          <t>detail_table_key</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>Материал</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>Материал / строка спецификации</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr"/>
+      <c r="D60" s="7" t="inlineStr"/>
+      <c r="E60" s="7" t="inlineStr"/>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>Объем, м3</t>
+        </is>
+      </c>
+      <c r="G60" s="7" t="inlineStr"/>
+      <c r="H60" s="7" t="inlineStr"/>
+      <c r="I60" s="7" t="inlineStr">
+        <is>
+          <t>Количество</t>
+        </is>
+      </c>
+      <c r="J60" s="7" t="inlineStr"/>
+      <c r="K60" s="7" t="inlineStr"/>
+      <c r="L60" s="7" t="inlineStr"/>
+      <c r="M60" s="7" t="inlineStr">
+        <is>
+          <t>Для ЭППС, бетона, опалубки, мембран и других строк спецификаций, которые не являются отдельной геометрией.</t>
+        </is>
+      </c>
+      <c r="N60" s="7" t="inlineStr"/>
+      <c r="O60" s="7" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="P60" s="7" t="inlineStr">
+        <is>
+          <t>material_spec_rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n"/>
+      <c r="B61" s="2" t="n"/>
+      <c r="C61" s="2" t="n"/>
+      <c r="D61" s="2" t="n"/>
+      <c r="E61" s="2" t="n"/>
+      <c r="F61" s="2" t="n"/>
+      <c r="G61" s="2" t="n"/>
+      <c r="H61" s="2" t="n"/>
+      <c r="I61" s="2" t="n"/>
+      <c r="J61" s="2" t="n"/>
+      <c r="K61" s="2" t="n"/>
+      <c r="L61" s="2" t="n"/>
+      <c r="M61" s="2" t="n"/>
+      <c r="N61" s="2" t="n"/>
+      <c r="O61" s="2" t="n"/>
+      <c r="P61" s="2" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
           <t>Сырые строки таблиц</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr"/>
-      <c r="C19" s="4" t="inlineStr"/>
-      <c r="D19" s="4" t="inlineStr"/>
-      <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="4" t="inlineStr"/>
-      <c r="G19" s="4" t="inlineStr"/>
-      <c r="H19" s="4" t="inlineStr"/>
-      <c r="I19" s="4" t="inlineStr"/>
-      <c r="J19" s="4" t="inlineStr"/>
-      <c r="K19" s="4" t="inlineStr"/>
-      <c r="L19" s="4" t="inlineStr"/>
-      <c r="M19" s="4" t="inlineStr"/>
-      <c r="N19" s="4" t="inlineStr"/>
-      <c r="O19" s="4" t="inlineStr"/>
-      <c r="P19" s="4" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="B62" s="4" t="inlineStr"/>
+      <c r="C62" s="4" t="inlineStr"/>
+      <c r="D62" s="4" t="inlineStr"/>
+      <c r="E62" s="4" t="inlineStr"/>
+      <c r="F62" s="4" t="inlineStr"/>
+      <c r="G62" s="4" t="inlineStr"/>
+      <c r="H62" s="4" t="inlineStr"/>
+      <c r="I62" s="4" t="inlineStr"/>
+      <c r="J62" s="4" t="inlineStr"/>
+      <c r="K62" s="4" t="inlineStr"/>
+      <c r="L62" s="4" t="inlineStr"/>
+      <c r="M62" s="4" t="inlineStr"/>
+      <c r="N62" s="4" t="inlineStr"/>
+      <c r="O62" s="4" t="inlineStr"/>
+      <c r="P62" s="4" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t>Тип</t>
+        </is>
+      </c>
+      <c r="B63" s="1" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="C63" s="1" t="inlineStr">
+        <is>
+          <t>Длина, м</t>
+        </is>
+      </c>
+      <c r="D63" s="1" t="inlineStr">
+        <is>
+          <t>Глубина, м</t>
+        </is>
+      </c>
+      <c r="E63" s="1" t="inlineStr">
+        <is>
+          <t>Ширина, м</t>
+        </is>
+      </c>
+      <c r="F63" s="1" t="inlineStr">
+        <is>
+          <t>Объем, м3</t>
+        </is>
+      </c>
+      <c r="G63" s="1" t="inlineStr">
+        <is>
+          <t>Диаметр, мм</t>
+        </is>
+      </c>
+      <c r="H63" s="1" t="inlineStr">
+        <is>
+          <t>Длина одной, м</t>
+        </is>
+      </c>
+      <c r="I63" s="1" t="inlineStr">
+        <is>
+          <t>Количество</t>
+        </is>
+      </c>
+      <c r="J63" s="1" t="inlineStr">
+        <is>
+          <t>Итоговая длина, м</t>
+        </is>
+      </c>
+      <c r="K63" s="1" t="inlineStr">
+        <is>
+          <t>Включено</t>
+        </is>
+      </c>
+      <c r="L63" s="1" t="inlineStr">
+        <is>
+          <t>Источник</t>
+        </is>
+      </c>
+      <c r="M63" s="1" t="inlineStr">
+        <is>
+          <t>Фрагмент проекта</t>
+        </is>
+      </c>
+      <c r="N63" s="1" t="inlineStr">
+        <is>
+          <t>Комментарий Елены</t>
+        </is>
+      </c>
+      <c r="O63" s="1" t="inlineStr">
+        <is>
+          <t>section_code</t>
+        </is>
+      </c>
+      <c r="P63" s="1" t="inlineStr">
+        <is>
+          <t>detail_table_key</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
         <is>
           <t>Raw row</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B64" s="7" t="inlineStr">
         <is>
           <t>Сырая строка PDF</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr"/>
-      <c r="D20" s="7" t="inlineStr"/>
-      <c r="E20" s="7" t="inlineStr"/>
-      <c r="F20" s="7" t="inlineStr"/>
-      <c r="G20" s="7" t="inlineStr"/>
-      <c r="H20" s="7" t="inlineStr"/>
-      <c r="I20" s="7" t="inlineStr"/>
-      <c r="J20" s="7" t="inlineStr"/>
-      <c r="K20" s="7" t="inlineStr"/>
-      <c r="L20" s="7" t="inlineStr"/>
-      <c r="M20" s="7" t="inlineStr">
+      <c r="C64" s="7" t="inlineStr"/>
+      <c r="D64" s="7" t="inlineStr"/>
+      <c r="E64" s="7" t="inlineStr"/>
+      <c r="F64" s="7" t="inlineStr"/>
+      <c r="G64" s="7" t="inlineStr"/>
+      <c r="H64" s="7" t="inlineStr"/>
+      <c r="I64" s="7" t="inlineStr"/>
+      <c r="J64" s="7" t="inlineStr"/>
+      <c r="K64" s="7" t="inlineStr"/>
+      <c r="L64" s="7" t="inlineStr"/>
+      <c r="M64" s="7" t="inlineStr">
         <is>
           <t>Raw table row from chat extraction before mapping to target_code.</t>
         </is>
       </c>
-      <c r="N20" s="7" t="inlineStr"/>
-      <c r="O20" s="7" t="inlineStr">
+      <c r="N64" s="7" t="inlineStr"/>
+      <c r="O64" s="7" t="inlineStr">
         <is>
           <t>template</t>
         </is>
       </c>
-      <c r="P20" s="7" t="inlineStr">
+      <c r="P64" s="7" t="inlineStr">
         <is>
           <t>raw_table_rows</t>
         </is>
@@ -18068,7 +19684,7 @@
       "formula_ready_required": true,
       "excel_formula_exportable": true
     },
-    "notes": "Calculator has a hardcoded display_quantity=1.2 override for this line (found 2026-07-10, not fixed — same class of issue already fixed for waterproofing's display_quantity). Production quantity/money uses the formula above, not the display override."
+    "notes": "Fixed 2026-07-11: calculator had a hardcoded display_quantity=1.2 override for this line (found 2026-07-10), now replaced with a computed _round_decimal(timber_raw_volume_m3, 0.01), same pattern as waterproofing's fix. Never affected material_total/work_total, cosmetic only."
   },
   {
     "code": "eps50_laying_under_slab",

--- a/experiments/full_estimate_review_pipeline/output/step_12_all_sections_review_template.xlsx
+++ b/experiments/full_estimate_review_pipeline/output/step_12_all_sections_review_template.xlsx
@@ -672,7 +672,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>строки проверки: 17; цены: 25; детали: 0</t>
+          <t>строки проверки: 16; цены: 25; детали: 0</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>строки проверки: 18; цены: 17; детали: 0</t>
+          <t>строки проверки: 19; цены: 17; детали: 0</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>строки проверки: 12; цены: 15; детали: 0</t>
+          <t>строки проверки: 13; цены: 15; детали: 0</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M119"/>
+  <dimension ref="A1:R134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -836,6 +836,11 @@
     <col hidden="1" width="28" customWidth="1" min="11" max="11"/>
     <col hidden="1" width="18" customWidth="1" min="12" max="12"/>
     <col hidden="1" width="24" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="17" max="17"/>
+    <col hidden="1" width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -857,6 +862,11 @@
       <c r="K1" s="2" t="inlineStr"/>
       <c r="L1" s="2" t="inlineStr"/>
       <c r="M1" s="2" t="inlineStr"/>
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
+      <c r="P1" s="2" t="n"/>
+      <c r="Q1" s="2" t="n"/>
+      <c r="R1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -866,7 +876,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Проверьте: 107</t>
+          <t>Проверьте: 108</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -888,6 +898,11 @@
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
+      <c r="P2" s="2" t="n"/>
+      <c r="Q2" s="2" t="n"/>
+      <c r="R2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n"/>
@@ -903,6 +918,11 @@
       <c r="K3" s="2" t="n"/>
       <c r="L3" s="2" t="n"/>
       <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
+      <c r="P3" s="2" t="n"/>
+      <c r="Q3" s="2" t="n"/>
+      <c r="R3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -970,6 +990,11 @@
           <t>target_code</t>
         </is>
       </c>
+      <c r="N4" s="1" t="n"/>
+      <c r="O4" s="1" t="n"/>
+      <c r="P4" s="1" t="n"/>
+      <c r="Q4" s="1" t="n"/>
+      <c r="R4" s="1" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -989,6 +1014,11 @@
       <c r="K5" s="4" t="inlineStr"/>
       <c r="L5" s="4" t="inlineStr"/>
       <c r="M5" s="4" t="inlineStr"/>
+      <c r="N5" s="4" t="n"/>
+      <c r="O5" s="4" t="n"/>
+      <c r="P5" s="4" t="n"/>
+      <c r="Q5" s="4" t="n"/>
+      <c r="R5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -1036,6 +1066,11 @@
           <t>pit_area_m2</t>
         </is>
       </c>
+      <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
+      <c r="P6" s="2" t="n"/>
+      <c r="Q6" s="2" t="n"/>
+      <c r="R6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -1083,6 +1118,11 @@
           <t>pit_excavation_depth_m</t>
         </is>
       </c>
+      <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="n"/>
+      <c r="P7" s="2" t="n"/>
+      <c r="Q7" s="2" t="n"/>
+      <c r="R7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -1130,6 +1170,11 @@
           <t>sand_base_volume_m3</t>
         </is>
       </c>
+      <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
+      <c r="P8" s="2" t="n"/>
+      <c r="Q8" s="2" t="n"/>
+      <c r="R8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -1177,6 +1222,11 @@
           <t>trench_volume_m3</t>
         </is>
       </c>
+      <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="n"/>
+      <c r="P9" s="2" t="n"/>
+      <c r="Q9" s="2" t="n"/>
+      <c r="R9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -1224,6 +1274,11 @@
           <t>geotextile_area_m2</t>
         </is>
       </c>
+      <c r="N10" s="2" t="n"/>
+      <c r="O10" s="2" t="n"/>
+      <c r="P10" s="2" t="n"/>
+      <c r="Q10" s="2" t="n"/>
+      <c r="R10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -1271,6 +1326,11 @@
           <t>geotextile_laying_area_m2</t>
         </is>
       </c>
+      <c r="N11" s="2" t="n"/>
+      <c r="O11" s="2" t="n"/>
+      <c r="P11" s="2" t="n"/>
+      <c r="Q11" s="2" t="n"/>
+      <c r="R11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1318,6 +1378,11 @@
           <t>communications_length_m</t>
         </is>
       </c>
+      <c r="N12" s="2" t="n"/>
+      <c r="O12" s="2" t="n"/>
+      <c r="P12" s="2" t="n"/>
+      <c r="Q12" s="2" t="n"/>
+      <c r="R12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1365,6 +1430,11 @@
           <t>trench_routes</t>
         </is>
       </c>
+      <c r="N13" s="2" t="n"/>
+      <c r="O13" s="2" t="n"/>
+      <c r="P13" s="2" t="n"/>
+      <c r="Q13" s="2" t="n"/>
+      <c r="R13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1412,6 +1482,11 @@
           <t>communications_pipe_items</t>
         </is>
       </c>
+      <c r="N14" s="2" t="n"/>
+      <c r="O14" s="2" t="n"/>
+      <c r="P14" s="2" t="n"/>
+      <c r="Q14" s="2" t="n"/>
+      <c r="R14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -1431,6 +1506,11 @@
       <c r="K15" s="4" t="inlineStr"/>
       <c r="L15" s="4" t="inlineStr"/>
       <c r="M15" s="4" t="inlineStr"/>
+      <c r="N15" s="4" t="n"/>
+      <c r="O15" s="4" t="n"/>
+      <c r="P15" s="4" t="n"/>
+      <c r="Q15" s="4" t="n"/>
+      <c r="R15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1478,6 +1558,11 @@
           <t>membrane_area_m2</t>
         </is>
       </c>
+      <c r="N16" s="2" t="n"/>
+      <c r="O16" s="2" t="n"/>
+      <c r="P16" s="2" t="n"/>
+      <c r="Q16" s="2" t="n"/>
+      <c r="R16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1525,6 +1610,11 @@
           <t>slab_side_formwork_area</t>
         </is>
       </c>
+      <c r="N17" s="2" t="n"/>
+      <c r="O17" s="2" t="n"/>
+      <c r="P17" s="2" t="n"/>
+      <c r="Q17" s="2" t="n"/>
+      <c r="R17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -1572,6 +1662,11 @@
           <t>eps_50_under_slab_volume</t>
         </is>
       </c>
+      <c r="N18" s="2" t="n"/>
+      <c r="O18" s="2" t="n"/>
+      <c r="P18" s="2" t="n"/>
+      <c r="Q18" s="2" t="n"/>
+      <c r="R18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -1619,6 +1714,11 @@
           <t>concrete_project_volume</t>
         </is>
       </c>
+      <c r="N19" s="2" t="n"/>
+      <c r="O19" s="2" t="n"/>
+      <c r="P19" s="2" t="n"/>
+      <c r="Q19" s="2" t="n"/>
+      <c r="R19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -1666,6 +1766,11 @@
           <t>thermal_insert_50_length</t>
         </is>
       </c>
+      <c r="N20" s="2" t="n"/>
+      <c r="O20" s="2" t="n"/>
+      <c r="P20" s="2" t="n"/>
+      <c r="Q20" s="2" t="n"/>
+      <c r="R20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -1713,6 +1818,11 @@
           <t>thermal_insert_100_length</t>
         </is>
       </c>
+      <c r="N21" s="2" t="n"/>
+      <c r="O21" s="2" t="n"/>
+      <c r="P21" s="2" t="n"/>
+      <c r="Q21" s="2" t="n"/>
+      <c r="R21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -1760,6 +1870,11 @@
           <t>thermal_insert_50_material_spec_qty</t>
         </is>
       </c>
+      <c r="N22" s="2" t="n"/>
+      <c r="O22" s="2" t="n"/>
+      <c r="P22" s="2" t="n"/>
+      <c r="Q22" s="2" t="n"/>
+      <c r="R22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -1807,17 +1922,22 @@
           <t>thermal_insert_100_material_spec_qty</t>
         </is>
       </c>
+      <c r="N23" s="2" t="n"/>
+      <c r="O23" s="2" t="n"/>
+      <c r="P23" s="2" t="n"/>
+      <c r="Q23" s="2" t="n"/>
+      <c r="R23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Арматура фундаментной плиты по диаметрам</t>
+          <t>Подача арматуры автокраном, смены</t>
         </is>
       </c>
       <c r="B24" s="5" t="n"/>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>смена</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -1827,7 +1947,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Проверьте позиции арматуры фундаментной плиты по диаметрам, каждая строка спецификации отдельной строкой.</t>
+          <t>Введите или подтвердите смены крана для подачи арматуры.</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr"/>
@@ -1841,30 +1961,31 @@
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>foundation_rebar_items</t>
+          <t>rebar_crane_shifts</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>AUTO_PROJECT</t>
-        </is>
-      </c>
-      <c r="M24" s="5" t="inlineStr">
-        <is>
-          <t>foundation_rebar_items</t>
-        </is>
-      </c>
+          <t>MANUAL_REVIEW</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="inlineStr"/>
+      <c r="N24" s="2" t="n"/>
+      <c r="O24" s="2" t="n"/>
+      <c r="P24" s="2" t="n"/>
+      <c r="Q24" s="2" t="n"/>
+      <c r="R24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Подача арматуры автокраном, смены</t>
+          <t>Доставка арматуры и металла, машины</t>
         </is>
       </c>
       <c r="B25" s="5" t="n"/>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>смена</t>
+          <t>маш</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -1874,7 +1995,7 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>Введите или подтвердите смены крана для подачи арматуры.</t>
+          <t>Введите или подтвердите количество машин доставки арматуры/металла.</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr"/>
@@ -1888,7 +2009,7 @@
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>rebar_crane_shifts</t>
+          <t>rebar_metal_delivery_trucks</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
@@ -1897,17 +2018,22 @@
         </is>
       </c>
       <c r="M25" s="5" t="inlineStr"/>
+      <c r="N25" s="2" t="n"/>
+      <c r="O25" s="2" t="n"/>
+      <c r="P25" s="2" t="n"/>
+      <c r="Q25" s="2" t="n"/>
+      <c r="R25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Доставка арматуры и металла, машины</t>
+          <t>Общий вес металла коробки для контроля доставки</t>
         </is>
       </c>
       <c r="B26" s="5" t="n"/>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>маш</t>
+          <t>кг</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -1917,7 +2043,7 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>Введите или подтвердите количество машин доставки арматуры/металла.</t>
+          <t>Введите общий вес металла коробки для контроля доставки.</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr"/>
@@ -1931,7 +2057,7 @@
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>rebar_metal_delivery_trucks</t>
+          <t>box_total_metal_weight_kg</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
@@ -1940,17 +2066,22 @@
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr"/>
+      <c r="N26" s="2" t="n"/>
+      <c r="O26" s="2" t="n"/>
+      <c r="P26" s="2" t="n"/>
+      <c r="Q26" s="2" t="n"/>
+      <c r="R26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Общий вес металла коробки для контроля доставки</t>
+          <t>Работа бетононасоса, смены</t>
         </is>
       </c>
       <c r="B27" s="5" t="n"/>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>кг</t>
+          <t>смена</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -1960,7 +2091,7 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Введите общий вес металла коробки для контроля доставки.</t>
+          <t>Введите или подтвердите смены бетононасоса.</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr"/>
@@ -1974,7 +2105,7 @@
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>box_total_metal_weight_kg</t>
+          <t>concrete_pump_shifts</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
@@ -1983,17 +2114,22 @@
         </is>
       </c>
       <c r="M27" s="5" t="inlineStr"/>
+      <c r="N27" s="2" t="n"/>
+      <c r="O27" s="2" t="n"/>
+      <c r="P27" s="2" t="n"/>
+      <c r="Q27" s="2" t="n"/>
+      <c r="R27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Работа бетононасоса, смены</t>
+          <t>Логистика и снабжение</t>
         </is>
       </c>
       <c r="B28" s="5" t="n"/>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>смена</t>
+          <t>руб</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -2003,7 +2139,7 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Введите или подтвердите смены бетононасоса.</t>
+          <t>Введите или подтвердите фиксированную сумму логистики и снабжения.</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr"/>
@@ -2017,7 +2153,7 @@
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>concrete_pump_shifts</t>
+          <t>logistics_and_supply_amount</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
@@ -2026,11 +2162,16 @@
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr"/>
+      <c r="N28" s="2" t="n"/>
+      <c r="O28" s="2" t="n"/>
+      <c r="P28" s="2" t="n"/>
+      <c r="Q28" s="2" t="n"/>
+      <c r="R28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Логистика и снабжение</t>
+          <t>Расходные материалы, амортизация инструмента</t>
         </is>
       </c>
       <c r="B29" s="5" t="n"/>
@@ -2046,7 +2187,7 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Введите или подтвердите фиксированную сумму логистики и снабжения.</t>
+          <t>Введите или подтвердите фиксированную сумму расходников и амортизации.</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr"/>
@@ -2060,7 +2201,7 @@
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>logistics_and_supply_amount</t>
+          <t>consumables_tool_amortization_amount</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
@@ -2069,192 +2210,226 @@
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr"/>
+      <c r="N29" s="2" t="n"/>
+      <c r="O29" s="2" t="n"/>
+      <c r="P29" s="2" t="n"/>
+      <c r="Q29" s="2" t="n"/>
+      <c r="R29" s="2" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>Расходные материалы, амортизация инструмента</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="n"/>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>руб</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>Проверьте</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>Введите или подтвердите фиксированную сумму расходников и амортизации.</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr">
-        <is>
-          <t>foundation_slab</t>
-        </is>
-      </c>
-      <c r="K30" s="5" t="inlineStr">
-        <is>
-          <t>consumables_tool_amortization_amount</t>
-        </is>
-      </c>
-      <c r="L30" s="5" t="inlineStr">
-        <is>
-          <t>MANUAL_REVIEW</t>
-        </is>
-      </c>
-      <c r="M30" s="5" t="inlineStr"/>
+      <c r="A30" s="2" t="n"/>
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n"/>
+      <c r="E30" s="2" t="n"/>
+      <c r="F30" s="2" t="n"/>
+      <c r="G30" s="2" t="n"/>
+      <c r="H30" s="2" t="n"/>
+      <c r="I30" s="2" t="n"/>
+      <c r="J30" s="2" t="n"/>
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" s="2" t="n"/>
+      <c r="M30" s="2" t="n"/>
+      <c r="N30" s="2" t="n"/>
+      <c r="O30" s="2" t="n"/>
+      <c r="P30" s="2" t="n"/>
+      <c r="Q30" s="2" t="n"/>
+      <c r="R30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
+          <t>Фундаментная плита — Арматура фундаментной плиты по диаметрам (Проверьте позиции арматуры фундаментной плиты по диаметрам, каждая строка спецификации отдельной строкой.)</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n"/>
+      <c r="C31" s="4" t="n"/>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="4" t="n"/>
+      <c r="H31" s="4" t="n"/>
+      <c r="I31" s="4" t="n"/>
+      <c r="J31" s="4" t="n"/>
+      <c r="K31" s="4" t="n"/>
+      <c r="L31" s="4" t="n"/>
+      <c r="M31" s="4" t="n"/>
+      <c r="N31" s="4" t="n"/>
+      <c r="O31" s="4" t="n"/>
+      <c r="P31" s="4" t="n"/>
+      <c r="Q31" s="4" t="n"/>
+      <c r="R31" s="4" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Что проверяем</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="inlineStr">
+        <is>
+          <t>Найдено в проекте</t>
+        </is>
+      </c>
+      <c r="C32" s="1" t="inlineStr">
+        <is>
+          <t>Ед.</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="E32" s="1" t="inlineStr">
+        <is>
+          <t>Что нужно сделать</t>
+        </is>
+      </c>
+      <c r="F32" s="1" t="inlineStr">
+        <is>
+          <t>Источник</t>
+        </is>
+      </c>
+      <c r="G32" s="1" t="inlineStr">
+        <is>
+          <t>Фрагмент проекта</t>
+        </is>
+      </c>
+      <c r="H32" s="1" t="inlineStr">
+        <is>
+          <t>Исправить / ввести значение</t>
+        </is>
+      </c>
+      <c r="I32" s="1" t="inlineStr">
+        <is>
+          <t>Комментарий Елены</t>
+        </is>
+      </c>
+      <c r="J32" s="1" t="inlineStr">
+        <is>
+          <t>section_code</t>
+        </is>
+      </c>
+      <c r="K32" s="1" t="inlineStr">
+        <is>
+          <t>technical_key</t>
+        </is>
+      </c>
+      <c r="L32" s="1" t="inlineStr">
+        <is>
+          <t>source_class</t>
+        </is>
+      </c>
+      <c r="M32" s="1" t="inlineStr">
+        <is>
+          <t>target_code</t>
+        </is>
+      </c>
+      <c r="N32" s="1" t="inlineStr">
+        <is>
+          <t>Исправить: Длина по спецификации, мп</t>
+        </is>
+      </c>
+      <c r="O32" s="1" t="inlineStr">
+        <is>
+          <t>Исправить: Масса 1 м, кг/м</t>
+        </is>
+      </c>
+      <c r="P32" s="1" t="inlineStr"/>
+      <c r="Q32" s="1" t="inlineStr"/>
+      <c r="R32" s="1" t="inlineStr">
+        <is>
+          <t>row_data_json</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
           <t>Гидроизоляция фундаментной плиты</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr"/>
-      <c r="C31" s="4" t="inlineStr"/>
-      <c r="D31" s="4" t="inlineStr"/>
-      <c r="E31" s="4" t="inlineStr"/>
-      <c r="F31" s="4" t="inlineStr"/>
-      <c r="G31" s="4" t="inlineStr"/>
-      <c r="H31" s="4" t="inlineStr"/>
-      <c r="I31" s="4" t="inlineStr"/>
-      <c r="J31" s="4" t="inlineStr"/>
-      <c r="K31" s="4" t="inlineStr"/>
-      <c r="L31" s="4" t="inlineStr"/>
-      <c r="M31" s="4" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr"/>
+      <c r="C33" s="4" t="inlineStr"/>
+      <c r="D33" s="4" t="inlineStr"/>
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr"/>
+      <c r="G33" s="4" t="inlineStr"/>
+      <c r="H33" s="4" t="inlineStr"/>
+      <c r="I33" s="4" t="inlineStr"/>
+      <c r="J33" s="4" t="inlineStr"/>
+      <c r="K33" s="4" t="inlineStr"/>
+      <c r="L33" s="4" t="inlineStr"/>
+      <c r="M33" s="4" t="inlineStr"/>
+      <c r="N33" s="4" t="n"/>
+      <c r="O33" s="4" t="n"/>
+      <c r="P33" s="4" t="n"/>
+      <c r="Q33" s="4" t="n"/>
+      <c r="R33" s="4" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>Площадь гидроизоляции фундаментной плиты</t>
         </is>
       </c>
-      <c r="B32" s="5" t="n"/>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="B34" s="5" t="n"/>
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>м2</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>Проверьте</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>Проверьте площадь гидроизоляции из спецификации.</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr"/>
-      <c r="G32" s="5" t="inlineStr"/>
-      <c r="H32" s="5" t="inlineStr"/>
-      <c r="I32" s="5" t="inlineStr"/>
-      <c r="J32" s="5" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr"/>
+      <c r="G34" s="5" t="inlineStr"/>
+      <c r="H34" s="5" t="inlineStr"/>
+      <c r="I34" s="5" t="inlineStr"/>
+      <c r="J34" s="5" t="inlineStr">
         <is>
           <t>waterproofing</t>
         </is>
       </c>
-      <c r="K32" s="5" t="inlineStr">
+      <c r="K34" s="5" t="inlineStr">
         <is>
           <t>waterproofing_area_m2</t>
         </is>
       </c>
-      <c r="L32" s="5" t="inlineStr">
+      <c r="L34" s="5" t="inlineStr">
         <is>
           <t>AUTO_PROJECT</t>
         </is>
       </c>
-      <c r="M32" s="5" t="inlineStr">
+      <c r="M34" s="5" t="inlineStr">
         <is>
           <t>waterproofing_area_m2</t>
         </is>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>ЭППС 100 мм по торцу фундаментной плиты, объем</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="n"/>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>м3</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>Проверьте</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>Проверьте объем ЭППС 100 мм по торцу фундаментной плиты.</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr"/>
-      <c r="G33" s="5" t="inlineStr"/>
-      <c r="H33" s="5" t="inlineStr"/>
-      <c r="I33" s="5" t="inlineStr"/>
-      <c r="J33" s="5" t="inlineStr">
-        <is>
-          <t>waterproofing</t>
-        </is>
-      </c>
-      <c r="K33" s="5" t="inlineStr">
-        <is>
-          <t>eps100_wall_volume_m3</t>
-        </is>
-      </c>
-      <c r="L33" s="5" t="inlineStr">
-        <is>
-          <t>AUTO_PROJECT</t>
-        </is>
-      </c>
-      <c r="M33" s="5" t="inlineStr">
-        <is>
-          <t>eps100_wall_volume_m3</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>Стены и перемычки</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr"/>
-      <c r="C34" s="4" t="inlineStr"/>
-      <c r="D34" s="4" t="inlineStr"/>
-      <c r="E34" s="4" t="inlineStr"/>
-      <c r="F34" s="4" t="inlineStr"/>
-      <c r="G34" s="4" t="inlineStr"/>
-      <c r="H34" s="4" t="inlineStr"/>
-      <c r="I34" s="4" t="inlineStr"/>
-      <c r="J34" s="4" t="inlineStr"/>
-      <c r="K34" s="4" t="inlineStr"/>
-      <c r="L34" s="4" t="inlineStr"/>
-      <c r="M34" s="4" t="inlineStr"/>
+      <c r="N34" s="5" t="n"/>
+      <c r="O34" s="5" t="n"/>
+      <c r="P34" s="5" t="n"/>
+      <c r="Q34" s="5" t="n"/>
+      <c r="R34" s="5" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Количество этажей для расчета стен</t>
+          <t>ЭППС 100 мм по торцу фундаментной плиты, объем</t>
         </is>
       </c>
       <c r="B35" s="5" t="n"/>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>эт.</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -2264,7 +2439,7 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Проверьте этажность для раздела стен.</t>
+          <t>Проверьте объем ЭППС 100 мм по торцу фундаментной плиты.</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr"/>
@@ -2273,12 +2448,12 @@
       <c r="I35" s="5" t="inlineStr"/>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>load_bearing_walls_lintels</t>
+          <t>waterproofing</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>floors_count</t>
+          <t>eps100_wall_volume_m3</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
@@ -2288,67 +2463,49 @@
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>floors_count</t>
-        </is>
-      </c>
+          <t>eps100_wall_volume_m3</t>
+        </is>
+      </c>
+      <c r="N35" s="5" t="n"/>
+      <c r="O35" s="5" t="n"/>
+      <c r="P35" s="5" t="n"/>
+      <c r="Q35" s="5" t="n"/>
+      <c r="R35" s="5" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>Гидроизоляция под первый ряд несущих стен, площадь</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="n"/>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>м2</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>Проверьте</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>Проверьте площадь отсечной гидроизоляции только под несущие стены.</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="inlineStr"/>
-      <c r="G36" s="5" t="inlineStr"/>
-      <c r="H36" s="5" t="inlineStr"/>
-      <c r="I36" s="5" t="inlineStr"/>
-      <c r="J36" s="5" t="inlineStr">
-        <is>
-          <t>load_bearing_walls_lintels</t>
-        </is>
-      </c>
-      <c r="K36" s="5" t="inlineStr">
-        <is>
-          <t>cutoff_waterproofing_load_bearing_walls_area_m2</t>
-        </is>
-      </c>
-      <c r="L36" s="5" t="inlineStr">
-        <is>
-          <t>AUTO_PROJECT</t>
-        </is>
-      </c>
-      <c r="M36" s="5" t="inlineStr">
-        <is>
-          <t>cutoff_waterproofing_load_bearing_walls_area</t>
-        </is>
-      </c>
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Стены и перемычки</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr"/>
+      <c r="C36" s="4" t="inlineStr"/>
+      <c r="D36" s="4" t="inlineStr"/>
+      <c r="E36" s="4" t="inlineStr"/>
+      <c r="F36" s="4" t="inlineStr"/>
+      <c r="G36" s="4" t="inlineStr"/>
+      <c r="H36" s="4" t="inlineStr"/>
+      <c r="I36" s="4" t="inlineStr"/>
+      <c r="J36" s="4" t="inlineStr"/>
+      <c r="K36" s="4" t="inlineStr"/>
+      <c r="L36" s="4" t="inlineStr"/>
+      <c r="M36" s="4" t="inlineStr"/>
+      <c r="N36" s="4" t="n"/>
+      <c r="O36" s="4" t="n"/>
+      <c r="P36" s="4" t="n"/>
+      <c r="Q36" s="4" t="n"/>
+      <c r="R36" s="4" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>Газобетон D400 600x400x250 для основных стен, объем</t>
+          <t>Количество этажей для расчета стен</t>
         </is>
       </c>
       <c r="B37" s="5" t="n"/>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>эт.</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -2358,7 +2515,7 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Проверьте объем D400 400 мм для основных несущих стен.</t>
+          <t>Проверьте этажность для раздела стен.</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr"/>
@@ -2372,7 +2529,7 @@
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>main_wall_gas_block_400_spec_volume_m3</t>
+          <t>floors_count</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
@@ -2382,20 +2539,25 @@
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>main_wall_gas_block_400_spec_volume</t>
-        </is>
-      </c>
+          <t>floors_count</t>
+        </is>
+      </c>
+      <c r="N37" s="5" t="n"/>
+      <c r="O37" s="5" t="n"/>
+      <c r="P37" s="5" t="n"/>
+      <c r="Q37" s="5" t="n"/>
+      <c r="R37" s="5" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>Газобетон D500 600x250x250 для основных стен, объем</t>
+          <t>Гидроизоляция под первый ряд несущих стен, площадь</t>
         </is>
       </c>
       <c r="B38" s="5" t="n"/>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -2405,7 +2567,7 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>Проверьте объем D500 250 мм для основных несущих стен.</t>
+          <t>Проверьте площадь отсечной гидроизоляции только под несущие стены.</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr"/>
@@ -2419,7 +2581,7 @@
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>main_wall_gas_block_250_spec_volume_m3</t>
+          <t>cutoff_waterproofing_load_bearing_walls_area_m2</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
@@ -2429,20 +2591,25 @@
       </c>
       <c r="M38" s="5" t="inlineStr">
         <is>
-          <t>main_wall_gas_block_250_spec_volume</t>
-        </is>
-      </c>
+          <t>cutoff_waterproofing_load_bearing_walls_area</t>
+        </is>
+      </c>
+      <c r="N38" s="5" t="n"/>
+      <c r="O38" s="5" t="n"/>
+      <c r="P38" s="5" t="n"/>
+      <c r="Q38" s="5" t="n"/>
+      <c r="R38" s="5" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Суммарная длина перемычек</t>
+          <t>Газобетон D400 600x400x250 для основных стен, объем</t>
         </is>
       </c>
       <c r="B39" s="5" t="n"/>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -2452,7 +2619,7 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Проверьте суммарную длину перемычек.</t>
+          <t>Проверьте объем D400 400 мм для основных несущих стен.</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr"/>
@@ -2466,7 +2633,7 @@
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>lintel_total_length_m</t>
+          <t>main_wall_gas_block_400_spec_volume_m3</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
@@ -2476,14 +2643,19 @@
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>lintel_total_length</t>
-        </is>
-      </c>
+          <t>main_wall_gas_block_400_spec_volume</t>
+        </is>
+      </c>
+      <c r="N39" s="5" t="n"/>
+      <c r="O39" s="5" t="n"/>
+      <c r="P39" s="5" t="n"/>
+      <c r="Q39" s="5" t="n"/>
+      <c r="R39" s="5" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>Бетон перемычек, объем по спецификации</t>
+          <t>Газобетон D500 600x250x250 для основных стен, объем</t>
         </is>
       </c>
       <c r="B40" s="5" t="n"/>
@@ -2499,7 +2671,7 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>Проверьте объем бетона перемычек по спецификации.</t>
+          <t>Проверьте объем D500 250 мм для основных несущих стен.</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr"/>
@@ -2513,7 +2685,7 @@
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>lintel_concrete_spec_volume_m3</t>
+          <t>main_wall_gas_block_250_spec_volume_m3</t>
         </is>
       </c>
       <c r="L40" s="5" t="inlineStr">
@@ -2523,20 +2695,25 @@
       </c>
       <c r="M40" s="5" t="inlineStr">
         <is>
-          <t>lintel_concrete_volume</t>
-        </is>
-      </c>
+          <t>main_wall_gas_block_250_spec_volume</t>
+        </is>
+      </c>
+      <c r="N40" s="5" t="n"/>
+      <c r="O40" s="5" t="n"/>
+      <c r="P40" s="5" t="n"/>
+      <c r="Q40" s="5" t="n"/>
+      <c r="R40" s="5" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>Кладка несущих стен 2-го этажа, объем</t>
+          <t>Суммарная длина перемычек</t>
         </is>
       </c>
       <c r="B41" s="5" t="n"/>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>мп</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -2546,7 +2723,7 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Если в проекте два этажа, проверьте объем кладки несущих стен 2-го этажа.</t>
+          <t>Проверьте суммарную длину перемычек.</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr"/>
@@ -2560,7 +2737,7 @@
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>floor_2_masonry_volume_m3</t>
+          <t>lintel_total_length_m</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
@@ -2570,14 +2747,19 @@
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>floor_2_masonry_volume</t>
-        </is>
-      </c>
+          <t>lintel_total_length</t>
+        </is>
+      </c>
+      <c r="N41" s="5" t="n"/>
+      <c r="O41" s="5" t="n"/>
+      <c r="P41" s="5" t="n"/>
+      <c r="Q41" s="5" t="n"/>
+      <c r="R41" s="5" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>Кладка парапета, объем</t>
+          <t>Бетон перемычек, объем по спецификации</t>
         </is>
       </c>
       <c r="B42" s="5" t="n"/>
@@ -2593,7 +2775,7 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>Если есть плоская кровля с парапетом, проверьте объем кладки парапета.</t>
+          <t>Проверьте объем бетона перемычек по спецификации.</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr"/>
@@ -2607,7 +2789,7 @@
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>parapet_masonry_volume_m3</t>
+          <t>lintel_concrete_spec_volume_m3</t>
         </is>
       </c>
       <c r="L42" s="5" t="inlineStr">
@@ -2617,14 +2799,19 @@
       </c>
       <c r="M42" s="5" t="inlineStr">
         <is>
-          <t>parapet_masonry_volume</t>
-        </is>
-      </c>
+          <t>lintel_concrete_volume</t>
+        </is>
+      </c>
+      <c r="N42" s="5" t="n"/>
+      <c r="O42" s="5" t="n"/>
+      <c r="P42" s="5" t="n"/>
+      <c r="Q42" s="5" t="n"/>
+      <c r="R42" s="5" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>Газобетон 150 мм для обкладки вентканалов, объем</t>
+          <t>Кладка несущих стен 2-го этажа, объем</t>
         </is>
       </c>
       <c r="B43" s="5" t="n"/>
@@ -2640,7 +2827,7 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Если есть обкладка вентканалов, проверьте объем газобетона 150 мм.</t>
+          <t>Если в проекте два этажа, проверьте объем кладки несущих стен 2-го этажа.</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr"/>
@@ -2654,7 +2841,7 @@
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>vent_chimney_gas_block_spec_volume_m3</t>
+          <t>floor_2_masonry_volume_m3</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
@@ -2664,20 +2851,25 @@
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>vent_chimney_gas_block_150_volume</t>
-        </is>
-      </c>
+          <t>floor_2_masonry_volume</t>
+        </is>
+      </c>
+      <c r="N43" s="5" t="n"/>
+      <c r="O43" s="5" t="n"/>
+      <c r="P43" s="5" t="n"/>
+      <c r="Q43" s="5" t="n"/>
+      <c r="R43" s="5" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>Арматура несущих стен по диаметрам</t>
+          <t>Кладка парапета, объем</t>
         </is>
       </c>
       <c r="B44" s="5" t="n"/>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -2687,7 +2879,7 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>Проверьте позиции арматуры несущих стен по диаметрам, каждая строка спецификации отдельной строкой.</t>
+          <t>Если есть плоская кровля с парапетом, проверьте объем кладки парапета.</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr"/>
@@ -2701,7 +2893,7 @@
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>main_wall_rebar_items</t>
+          <t>parapet_masonry_volume_m3</t>
         </is>
       </c>
       <c r="L44" s="5" t="inlineStr">
@@ -2711,20 +2903,25 @@
       </c>
       <c r="M44" s="5" t="inlineStr">
         <is>
-          <t>main_wall_rebar_items</t>
-        </is>
-      </c>
+          <t>parapet_masonry_volume</t>
+        </is>
+      </c>
+      <c r="N44" s="5" t="n"/>
+      <c r="O44" s="5" t="n"/>
+      <c r="P44" s="5" t="n"/>
+      <c r="Q44" s="5" t="n"/>
+      <c r="R44" s="5" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>Арматура перемычек по диаметрам</t>
+          <t>Газобетон 150 мм для обкладки вентканалов, объем</t>
         </is>
       </c>
       <c r="B45" s="5" t="n"/>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -2734,7 +2931,7 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>Проверьте позиции арматуры перемычек по диаметрам, каждая строка спецификации отдельной строкой.</t>
+          <t>Если есть обкладка вентканалов, проверьте объем газобетона 150 мм.</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr"/>
@@ -2748,7 +2945,7 @@
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>lintel_rebar_items</t>
+          <t>vent_chimney_gas_block_spec_volume_m3</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
@@ -2758,20 +2955,25 @@
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>lintel_rebar_items</t>
-        </is>
-      </c>
+          <t>vent_chimney_gas_block_150_volume</t>
+        </is>
+      </c>
+      <c r="N45" s="5" t="n"/>
+      <c r="O45" s="5" t="n"/>
+      <c r="P45" s="5" t="n"/>
+      <c r="Q45" s="5" t="n"/>
+      <c r="R45" s="5" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>Позиции перемычек</t>
+          <t>Есть плоская кровля для парапета/вентканалов</t>
         </is>
       </c>
       <c r="B46" s="5" t="n"/>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>да/нет</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -2781,7 +2983,7 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>Необязательная разбивка перемычек по маркам, для справки; сверьте с lintel_total_length_m выше.</t>
+          <t>Проверьте, нужна ли связка с плоской кровлей для парапета и обкладки вентканалов.</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr"/>
@@ -2795,30 +2997,31 @@
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>lintel_items</t>
+          <t>flat_roof_enabled</t>
         </is>
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>AUTO_PROJECT</t>
-        </is>
-      </c>
-      <c r="M46" s="5" t="inlineStr">
-        <is>
-          <t>lintel_items</t>
-        </is>
-      </c>
+          <t>MANUAL_REVIEW</t>
+        </is>
+      </c>
+      <c r="M46" s="5" t="inlineStr"/>
+      <c r="N46" s="5" t="n"/>
+      <c r="O46" s="5" t="n"/>
+      <c r="P46" s="5" t="n"/>
+      <c r="Q46" s="5" t="n"/>
+      <c r="R46" s="5" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>Есть плоская кровля для парапета/вентканалов</t>
+          <t>Доставка бетона для перемычек, рейсы</t>
         </is>
       </c>
       <c r="B47" s="5" t="n"/>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>да/нет</t>
+          <t>рейс</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
@@ -2828,7 +3031,7 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>Проверьте, нужна ли связка с плоской кровлей для парапета и обкладки вентканалов.</t>
+          <t>Укажите количество рейсов доставки бетона.</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr"/>
@@ -2842,26 +3045,31 @@
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>flat_roof_enabled</t>
+          <t>concrete_delivery_trips</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>MANUAL_REVIEW</t>
+          <t>SUPPLIER_INPUT</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr"/>
+      <c r="N47" s="5" t="n"/>
+      <c r="O47" s="5" t="n"/>
+      <c r="P47" s="5" t="n"/>
+      <c r="Q47" s="5" t="n"/>
+      <c r="R47" s="5" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>Доставка бетона для перемычек, рейсы</t>
+          <t>Кран для парапета, смены</t>
         </is>
       </c>
       <c r="B48" s="5" t="n"/>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>рейс</t>
+          <t>смена</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -2871,7 +3079,7 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>Укажите количество рейсов доставки бетона.</t>
+          <t>Укажите смены крана для парапета, если применимо.</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr"/>
@@ -2885,7 +3093,7 @@
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>concrete_delivery_trips</t>
+          <t>parapet_crane_shifts</t>
         </is>
       </c>
       <c r="L48" s="5" t="inlineStr">
@@ -2894,17 +3102,22 @@
         </is>
       </c>
       <c r="M48" s="5" t="inlineStr"/>
+      <c r="N48" s="5" t="n"/>
+      <c r="O48" s="5" t="n"/>
+      <c r="P48" s="5" t="n"/>
+      <c r="Q48" s="5" t="n"/>
+      <c r="R48" s="5" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>Кран для парапета, смены</t>
+          <t>Вывоз мусора, машины</t>
         </is>
       </c>
       <c r="B49" s="5" t="n"/>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>смена</t>
+          <t>маш</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
@@ -2914,7 +3127,7 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Укажите смены крана для парапета, если применимо.</t>
+          <t>Укажите количество машин вывоза мусора.</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr"/>
@@ -2928,7 +3141,7 @@
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>parapet_crane_shifts</t>
+          <t>waste_removal_trucks</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
@@ -2937,17 +3150,22 @@
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr"/>
+      <c r="N49" s="5" t="n"/>
+      <c r="O49" s="5" t="n"/>
+      <c r="P49" s="5" t="n"/>
+      <c r="Q49" s="5" t="n"/>
+      <c r="R49" s="5" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>Вывоз мусора, машины</t>
+          <t>Расходные материалы и амортизация инструмента</t>
         </is>
       </c>
       <c r="B50" s="5" t="n"/>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>маш</t>
+          <t>руб.</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
@@ -2957,7 +3175,7 @@
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>Укажите количество машин вывоза мусора.</t>
+          <t>Укажите фиксированную сумму расходников или замените будущей формулой.</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr"/>
@@ -2971,7 +3189,7 @@
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>waste_removal_trucks</t>
+          <t>walls_consumables_tool_amortization_amount_raw</t>
         </is>
       </c>
       <c r="L50" s="5" t="inlineStr">
@@ -2980,314 +3198,302 @@
         </is>
       </c>
       <c r="M50" s="5" t="inlineStr"/>
+      <c r="N50" s="5" t="n"/>
+      <c r="O50" s="5" t="n"/>
+      <c r="P50" s="5" t="n"/>
+      <c r="Q50" s="5" t="n"/>
+      <c r="R50" s="5" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>Расходные материалы и амортизация инструмента</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="n"/>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>руб.</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t>Проверьте</t>
-        </is>
-      </c>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>Укажите фиксированную сумму расходников или замените будущей формулой.</t>
-        </is>
-      </c>
-      <c r="F51" s="5" t="inlineStr"/>
-      <c r="G51" s="5" t="inlineStr"/>
-      <c r="H51" s="5" t="inlineStr"/>
-      <c r="I51" s="5" t="inlineStr"/>
-      <c r="J51" s="5" t="inlineStr">
-        <is>
-          <t>load_bearing_walls_lintels</t>
-        </is>
-      </c>
-      <c r="K51" s="5" t="inlineStr">
-        <is>
-          <t>walls_consumables_tool_amortization_amount_raw</t>
-        </is>
-      </c>
-      <c r="L51" s="5" t="inlineStr">
-        <is>
-          <t>SUPPLIER_INPUT</t>
-        </is>
-      </c>
-      <c r="M51" s="5" t="inlineStr"/>
+      <c r="A51" s="2" t="n"/>
+      <c r="B51" s="2" t="n"/>
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="2" t="n"/>
+      <c r="E51" s="2" t="n"/>
+      <c r="F51" s="2" t="n"/>
+      <c r="G51" s="2" t="n"/>
+      <c r="H51" s="2" t="n"/>
+      <c r="I51" s="2" t="n"/>
+      <c r="J51" s="2" t="n"/>
+      <c r="K51" s="2" t="n"/>
+      <c r="L51" s="2" t="n"/>
+      <c r="M51" s="2" t="n"/>
+      <c r="N51" s="2" t="n"/>
+      <c r="O51" s="2" t="n"/>
+      <c r="P51" s="2" t="n"/>
+      <c r="Q51" s="2" t="n"/>
+      <c r="R51" s="2" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
+          <t>Стены и перемычки — Арматура несущих стен по диаметрам (Проверьте позиции арматуры несущих стен по диаметрам, каждая строка спецификации отдельной строкой.)</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="n"/>
+      <c r="C52" s="4" t="n"/>
+      <c r="D52" s="4" t="n"/>
+      <c r="E52" s="4" t="n"/>
+      <c r="F52" s="4" t="n"/>
+      <c r="G52" s="4" t="n"/>
+      <c r="H52" s="4" t="n"/>
+      <c r="I52" s="4" t="n"/>
+      <c r="J52" s="4" t="n"/>
+      <c r="K52" s="4" t="n"/>
+      <c r="L52" s="4" t="n"/>
+      <c r="M52" s="4" t="n"/>
+      <c r="N52" s="4" t="n"/>
+      <c r="O52" s="4" t="n"/>
+      <c r="P52" s="4" t="n"/>
+      <c r="Q52" s="4" t="n"/>
+      <c r="R52" s="4" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>Что проверяем</t>
+        </is>
+      </c>
+      <c r="B53" s="1" t="inlineStr">
+        <is>
+          <t>Найдено в проекте</t>
+        </is>
+      </c>
+      <c r="C53" s="1" t="inlineStr">
+        <is>
+          <t>Ед.</t>
+        </is>
+      </c>
+      <c r="D53" s="1" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="E53" s="1" t="inlineStr">
+        <is>
+          <t>Что нужно сделать</t>
+        </is>
+      </c>
+      <c r="F53" s="1" t="inlineStr">
+        <is>
+          <t>Источник</t>
+        </is>
+      </c>
+      <c r="G53" s="1" t="inlineStr">
+        <is>
+          <t>Фрагмент проекта</t>
+        </is>
+      </c>
+      <c r="H53" s="1" t="inlineStr">
+        <is>
+          <t>Исправить / ввести значение</t>
+        </is>
+      </c>
+      <c r="I53" s="1" t="inlineStr">
+        <is>
+          <t>Комментарий Елены</t>
+        </is>
+      </c>
+      <c r="J53" s="1" t="inlineStr">
+        <is>
+          <t>section_code</t>
+        </is>
+      </c>
+      <c r="K53" s="1" t="inlineStr">
+        <is>
+          <t>technical_key</t>
+        </is>
+      </c>
+      <c r="L53" s="1" t="inlineStr">
+        <is>
+          <t>source_class</t>
+        </is>
+      </c>
+      <c r="M53" s="1" t="inlineStr">
+        <is>
+          <t>target_code</t>
+        </is>
+      </c>
+      <c r="N53" s="1" t="inlineStr">
+        <is>
+          <t>Исправить: Длина по спецификации, мп</t>
+        </is>
+      </c>
+      <c r="O53" s="1" t="inlineStr">
+        <is>
+          <t>Исправить: Масса 1 м, кг/м</t>
+        </is>
+      </c>
+      <c r="P53" s="1" t="inlineStr"/>
+      <c r="Q53" s="1" t="inlineStr"/>
+      <c r="R53" s="1" t="inlineStr">
+        <is>
+          <t>row_data_json</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n"/>
+      <c r="B54" s="2" t="n"/>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="2" t="n"/>
+      <c r="E54" s="2" t="n"/>
+      <c r="F54" s="2" t="n"/>
+      <c r="G54" s="2" t="n"/>
+      <c r="H54" s="2" t="n"/>
+      <c r="I54" s="2" t="n"/>
+      <c r="J54" s="2" t="n"/>
+      <c r="K54" s="2" t="n"/>
+      <c r="L54" s="2" t="n"/>
+      <c r="M54" s="2" t="n"/>
+      <c r="N54" s="2" t="n"/>
+      <c r="O54" s="2" t="n"/>
+      <c r="P54" s="2" t="n"/>
+      <c r="Q54" s="2" t="n"/>
+      <c r="R54" s="2" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Стены и перемычки — Арматура перемычек по диаметрам (Проверьте позиции арматуры перемычек по диаметрам, каждая строка спецификации отдельной строкой.)</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="n"/>
+      <c r="C55" s="4" t="n"/>
+      <c r="D55" s="4" t="n"/>
+      <c r="E55" s="4" t="n"/>
+      <c r="F55" s="4" t="n"/>
+      <c r="G55" s="4" t="n"/>
+      <c r="H55" s="4" t="n"/>
+      <c r="I55" s="4" t="n"/>
+      <c r="J55" s="4" t="n"/>
+      <c r="K55" s="4" t="n"/>
+      <c r="L55" s="4" t="n"/>
+      <c r="M55" s="4" t="n"/>
+      <c r="N55" s="4" t="n"/>
+      <c r="O55" s="4" t="n"/>
+      <c r="P55" s="4" t="n"/>
+      <c r="Q55" s="4" t="n"/>
+      <c r="R55" s="4" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>Что проверяем</t>
+        </is>
+      </c>
+      <c r="B56" s="1" t="inlineStr">
+        <is>
+          <t>Найдено в проекте</t>
+        </is>
+      </c>
+      <c r="C56" s="1" t="inlineStr">
+        <is>
+          <t>Ед.</t>
+        </is>
+      </c>
+      <c r="D56" s="1" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="E56" s="1" t="inlineStr">
+        <is>
+          <t>Что нужно сделать</t>
+        </is>
+      </c>
+      <c r="F56" s="1" t="inlineStr">
+        <is>
+          <t>Источник</t>
+        </is>
+      </c>
+      <c r="G56" s="1" t="inlineStr">
+        <is>
+          <t>Фрагмент проекта</t>
+        </is>
+      </c>
+      <c r="H56" s="1" t="inlineStr">
+        <is>
+          <t>Исправить / ввести значение</t>
+        </is>
+      </c>
+      <c r="I56" s="1" t="inlineStr">
+        <is>
+          <t>Комментарий Елены</t>
+        </is>
+      </c>
+      <c r="J56" s="1" t="inlineStr">
+        <is>
+          <t>section_code</t>
+        </is>
+      </c>
+      <c r="K56" s="1" t="inlineStr">
+        <is>
+          <t>technical_key</t>
+        </is>
+      </c>
+      <c r="L56" s="1" t="inlineStr">
+        <is>
+          <t>source_class</t>
+        </is>
+      </c>
+      <c r="M56" s="1" t="inlineStr">
+        <is>
+          <t>target_code</t>
+        </is>
+      </c>
+      <c r="N56" s="1" t="inlineStr">
+        <is>
+          <t>Исправить: Длина по спецификации, мп</t>
+        </is>
+      </c>
+      <c r="O56" s="1" t="inlineStr">
+        <is>
+          <t>Исправить: Масса 1 м, кг/м</t>
+        </is>
+      </c>
+      <c r="P56" s="1" t="inlineStr"/>
+      <c r="Q56" s="1" t="inlineStr"/>
+      <c r="R56" s="1" t="inlineStr">
+        <is>
+          <t>row_data_json</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
           <t>Перекрытие 1 этажа</t>
         </is>
       </c>
-      <c r="B52" s="4" t="inlineStr"/>
-      <c r="C52" s="4" t="inlineStr"/>
-      <c r="D52" s="4" t="inlineStr"/>
-      <c r="E52" s="4" t="inlineStr"/>
-      <c r="F52" s="4" t="inlineStr"/>
-      <c r="G52" s="4" t="inlineStr"/>
-      <c r="H52" s="4" t="inlineStr"/>
-      <c r="I52" s="4" t="inlineStr"/>
-      <c r="J52" s="4" t="inlineStr"/>
-      <c r="K52" s="4" t="inlineStr"/>
-      <c r="L52" s="4" t="inlineStr"/>
-      <c r="M52" s="4" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>Бетон плиты перекрытия 1-го этажа, общий объем по спецификации</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="n"/>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>м3</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>Проверьте</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="inlineStr">
-        <is>
-          <t>Проверьте общий объем бетона плиты перекрытия 1-го этажа по спецификации.</t>
-        </is>
-      </c>
-      <c r="F53" s="5" t="inlineStr"/>
-      <c r="G53" s="5" t="inlineStr"/>
-      <c r="H53" s="5" t="inlineStr"/>
-      <c r="I53" s="5" t="inlineStr"/>
-      <c r="J53" s="5" t="inlineStr">
-        <is>
-          <t>floor_slab_1</t>
-        </is>
-      </c>
-      <c r="K53" s="5" t="inlineStr">
-        <is>
-          <t>total_concrete_volume_from_spec_m3</t>
-        </is>
-      </c>
-      <c r="L53" s="5" t="inlineStr">
-        <is>
-          <t>AUTO_PROJECT</t>
-        </is>
-      </c>
-      <c r="M53" s="5" t="inlineStr">
-        <is>
-          <t>floor_slab_1_concrete_volume</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>Толщина плиты перекрытия 1-го этажа</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="n"/>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>Проверьте</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>Проверьте толщину плиты перекрытия 1-го этажа.</t>
-        </is>
-      </c>
-      <c r="F54" s="5" t="inlineStr"/>
-      <c r="G54" s="5" t="inlineStr"/>
-      <c r="H54" s="5" t="inlineStr"/>
-      <c r="I54" s="5" t="inlineStr"/>
-      <c r="J54" s="5" t="inlineStr">
-        <is>
-          <t>floor_slab_1</t>
-        </is>
-      </c>
-      <c r="K54" s="5" t="inlineStr">
-        <is>
-          <t>slab_thickness_m</t>
-        </is>
-      </c>
-      <c r="L54" s="5" t="inlineStr">
-        <is>
-          <t>AUTO_PROJECT</t>
-        </is>
-      </c>
-      <c r="M54" s="5" t="inlineStr">
-        <is>
-          <t>floor_slab_1_slab_thickness</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>Высота торцевой опалубки плиты перекрытия 1-го этажа</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="n"/>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>Проверьте</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="inlineStr">
-        <is>
-          <t>Проверьте высоту торцевой опалубки; если отдельной строки нет, она принимается равной толщине плиты для контрольного расчета.</t>
-        </is>
-      </c>
-      <c r="F55" s="5" t="inlineStr"/>
-      <c r="G55" s="5" t="inlineStr"/>
-      <c r="H55" s="5" t="inlineStr"/>
-      <c r="I55" s="5" t="inlineStr"/>
-      <c r="J55" s="5" t="inlineStr">
-        <is>
-          <t>floor_slab_1</t>
-        </is>
-      </c>
-      <c r="K55" s="5" t="inlineStr">
-        <is>
-          <t>edge_formwork_height_m</t>
-        </is>
-      </c>
-      <c r="L55" s="5" t="inlineStr">
-        <is>
-          <t>AUTO_CALCULATED</t>
-        </is>
-      </c>
-      <c r="M55" s="5" t="inlineStr">
-        <is>
-          <t>floor_slab_1_edge_formwork_height</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>Периметр торца плиты перекрытия 1-го этажа</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="n"/>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>мп</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr">
-        <is>
-          <t>Проверьте</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t>Проверьте периметр/длину торца плиты перекрытия 1-го этажа.</t>
-        </is>
-      </c>
-      <c r="F56" s="5" t="inlineStr"/>
-      <c r="G56" s="5" t="inlineStr"/>
-      <c r="H56" s="5" t="inlineStr"/>
-      <c r="I56" s="5" t="inlineStr"/>
-      <c r="J56" s="5" t="inlineStr">
-        <is>
-          <t>floor_slab_1</t>
-        </is>
-      </c>
-      <c r="K56" s="5" t="inlineStr">
-        <is>
-          <t>slab_edge_perimeter_m</t>
-        </is>
-      </c>
-      <c r="L56" s="5" t="inlineStr">
-        <is>
-          <t>AUTO_PROJECT</t>
-        </is>
-      </c>
-      <c r="M56" s="5" t="inlineStr">
-        <is>
-          <t>floor_slab_1_slab_edge_perimeter</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>Площадь опалубки под плитой перекрытия 1-го этажа</t>
-        </is>
-      </c>
-      <c r="B57" s="5" t="n"/>
-      <c r="C57" s="5" t="inlineStr">
-        <is>
-          <t>м2</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>Проверьте</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>Проверьте площадь основной опалубки под плитой.</t>
-        </is>
-      </c>
-      <c r="F57" s="5" t="inlineStr"/>
-      <c r="G57" s="5" t="inlineStr"/>
-      <c r="H57" s="5" t="inlineStr"/>
-      <c r="I57" s="5" t="inlineStr"/>
-      <c r="J57" s="5" t="inlineStr">
-        <is>
-          <t>floor_slab_1</t>
-        </is>
-      </c>
-      <c r="K57" s="5" t="inlineStr">
-        <is>
-          <t>main_formwork_area_m2</t>
-        </is>
-      </c>
-      <c r="L57" s="5" t="inlineStr">
-        <is>
-          <t>AUTO_PROJECT</t>
-        </is>
-      </c>
-      <c r="M57" s="5" t="inlineStr">
-        <is>
-          <t>floor_slab_1_under_slab_formwork_area</t>
-        </is>
-      </c>
+      <c r="B57" s="4" t="inlineStr"/>
+      <c r="C57" s="4" t="inlineStr"/>
+      <c r="D57" s="4" t="inlineStr"/>
+      <c r="E57" s="4" t="inlineStr"/>
+      <c r="F57" s="4" t="inlineStr"/>
+      <c r="G57" s="4" t="inlineStr"/>
+      <c r="H57" s="4" t="inlineStr"/>
+      <c r="I57" s="4" t="inlineStr"/>
+      <c r="J57" s="4" t="inlineStr"/>
+      <c r="K57" s="4" t="inlineStr"/>
+      <c r="L57" s="4" t="inlineStr"/>
+      <c r="M57" s="4" t="inlineStr"/>
+      <c r="N57" s="4" t="n"/>
+      <c r="O57" s="4" t="n"/>
+      <c r="P57" s="4" t="n"/>
+      <c r="Q57" s="4" t="n"/>
+      <c r="R57" s="4" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>Площадь опалубки торца плиты перекрытия 1-го этажа</t>
+          <t>Бетон плиты перекрытия 1-го этажа, общий объем по спецификации</t>
         </is>
       </c>
       <c r="B58" s="5" t="n"/>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
@@ -3297,7 +3503,7 @@
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>Проверьте площадь опалубки торца плиты.</t>
+          <t>Проверьте общий объем бетона плиты перекрытия 1-го этажа по спецификации.</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr"/>
@@ -3311,7 +3517,7 @@
       </c>
       <c r="K58" s="5" t="inlineStr">
         <is>
-          <t>edge_formwork_area_m2</t>
+          <t>total_concrete_volume_from_spec_m3</t>
         </is>
       </c>
       <c r="L58" s="5" t="inlineStr">
@@ -3321,20 +3527,25 @@
       </c>
       <c r="M58" s="5" t="inlineStr">
         <is>
-          <t>floor_slab_1_edge_formwork_area</t>
-        </is>
-      </c>
+          <t>floor_slab_1_concrete_volume</t>
+        </is>
+      </c>
+      <c r="N58" s="5" t="n"/>
+      <c r="O58" s="5" t="n"/>
+      <c r="P58" s="5" t="n"/>
+      <c r="Q58" s="5" t="n"/>
+      <c r="R58" s="5" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>Площадь опалубки балок перекрытия 1-го этажа</t>
+          <t>Толщина плиты перекрытия 1-го этажа</t>
         </is>
       </c>
       <c r="B59" s="5" t="n"/>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>м</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
@@ -3344,7 +3555,7 @@
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>Если у этой плиты есть балки, проверьте площадь опалубки балок; иначе оставьте пустым — она посчитается из позиций балок ниже.</t>
+          <t>Проверьте толщину плиты перекрытия 1-го этажа.</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr"/>
@@ -3358,7 +3569,7 @@
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>beams_formwork_area_m2</t>
+          <t>slab_thickness_m</t>
         </is>
       </c>
       <c r="L59" s="5" t="inlineStr">
@@ -3368,20 +3579,25 @@
       </c>
       <c r="M59" s="5" t="inlineStr">
         <is>
-          <t>floor_slab_1_beams_formwork_area</t>
-        </is>
-      </c>
+          <t>floor_slab_1_slab_thickness</t>
+        </is>
+      </c>
+      <c r="N59" s="5" t="n"/>
+      <c r="O59" s="5" t="n"/>
+      <c r="P59" s="5" t="n"/>
+      <c r="Q59" s="5" t="n"/>
+      <c r="R59" s="5" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>ЭППС 100 мм торец плиты, длина работ</t>
+          <t>Высота торцевой опалубки плиты перекрытия 1-го этажа</t>
         </is>
       </c>
       <c r="B60" s="5" t="n"/>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>м</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
@@ -3391,7 +3607,7 @@
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>Проверьте длину работ по ЭППС торца плиты.</t>
+          <t>Проверьте высоту торцевой опалубки; если отдельной строки нет, она принимается равной толщине плиты для контрольного расчета.</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr"/>
@@ -3405,30 +3621,35 @@
       </c>
       <c r="K60" s="5" t="inlineStr">
         <is>
-          <t>slab_outer_edge_eps_work_length_m</t>
+          <t>edge_formwork_height_m</t>
         </is>
       </c>
       <c r="L60" s="5" t="inlineStr">
         <is>
-          <t>AUTO_PROJECT</t>
+          <t>AUTO_CALCULATED</t>
         </is>
       </c>
       <c r="M60" s="5" t="inlineStr">
         <is>
-          <t>floor_slab_1_edge_eps_work_length</t>
-        </is>
-      </c>
+          <t>floor_slab_1_edge_formwork_height</t>
+        </is>
+      </c>
+      <c r="N60" s="5" t="n"/>
+      <c r="O60" s="5" t="n"/>
+      <c r="P60" s="5" t="n"/>
+      <c r="Q60" s="5" t="n"/>
+      <c r="R60" s="5" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>Высота утепления торца плиты перекрытия 1-го этажа</t>
+          <t>Периметр торца плиты перекрытия 1-го этажа</t>
         </is>
       </c>
       <c r="B61" s="5" t="n"/>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>мп</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
@@ -3438,7 +3659,7 @@
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>Проверьте высоту утепления торца плиты.</t>
+          <t>Проверьте периметр/длину торца плиты перекрытия 1-го этажа.</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr"/>
@@ -3452,7 +3673,7 @@
       </c>
       <c r="K61" s="5" t="inlineStr">
         <is>
-          <t>edge_insulation_height_m</t>
+          <t>slab_edge_perimeter_m</t>
         </is>
       </c>
       <c r="L61" s="5" t="inlineStr">
@@ -3462,14 +3683,19 @@
       </c>
       <c r="M61" s="5" t="inlineStr">
         <is>
-          <t>floor_slab_1_edge_insulation_height</t>
-        </is>
-      </c>
+          <t>floor_slab_1_slab_edge_perimeter</t>
+        </is>
+      </c>
+      <c r="N61" s="5" t="n"/>
+      <c r="O61" s="5" t="n"/>
+      <c r="P61" s="5" t="n"/>
+      <c r="Q61" s="5" t="n"/>
+      <c r="R61" s="5" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>ЭППС 100 мм торец плиты, площадь материала</t>
+          <t>Площадь опалубки под плитой перекрытия 1-го этажа</t>
         </is>
       </c>
       <c r="B62" s="5" t="n"/>
@@ -3485,7 +3711,7 @@
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>Проверьте площадь материала ЭППС по торцу плиты.</t>
+          <t>Проверьте площадь основной опалубки под плитой.</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr"/>
@@ -3499,7 +3725,7 @@
       </c>
       <c r="K62" s="5" t="inlineStr">
         <is>
-          <t>slab_edge_eps_material_area_m2</t>
+          <t>main_formwork_area_m2</t>
         </is>
       </c>
       <c r="L62" s="5" t="inlineStr">
@@ -3509,14 +3735,19 @@
       </c>
       <c r="M62" s="5" t="inlineStr">
         <is>
-          <t>floor_slab_1_edge_eps_material_area</t>
-        </is>
-      </c>
+          <t>floor_slab_1_under_slab_formwork_area</t>
+        </is>
+      </c>
+      <c r="N62" s="5" t="n"/>
+      <c r="O62" s="5" t="n"/>
+      <c r="P62" s="5" t="n"/>
+      <c r="Q62" s="5" t="n"/>
+      <c r="R62" s="5" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>ЭППС 100 мм низ плиты, площадь работ</t>
+          <t>Площадь опалубки торца плиты перекрытия 1-го этажа</t>
         </is>
       </c>
       <c r="B63" s="5" t="n"/>
@@ -3532,7 +3763,7 @@
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>Проверьте площадь работ ЭППС по низу плиты.</t>
+          <t>Проверьте площадь опалубки торца плиты.</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr"/>
@@ -3546,7 +3777,7 @@
       </c>
       <c r="K63" s="5" t="inlineStr">
         <is>
-          <t>bottom_slab_eps_work_area_m2</t>
+          <t>edge_formwork_area_m2</t>
         </is>
       </c>
       <c r="L63" s="5" t="inlineStr">
@@ -3556,20 +3787,25 @@
       </c>
       <c r="M63" s="5" t="inlineStr">
         <is>
-          <t>floor_slab_1_bottom_eps_work_area</t>
-        </is>
-      </c>
+          <t>floor_slab_1_edge_formwork_area</t>
+        </is>
+      </c>
+      <c r="N63" s="5" t="n"/>
+      <c r="O63" s="5" t="n"/>
+      <c r="P63" s="5" t="n"/>
+      <c r="Q63" s="5" t="n"/>
+      <c r="R63" s="5" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>ЭППС 100 мм для плиты перекрытия 1-го этажа, общий объем</t>
+          <t>Площадь опалубки балок перекрытия 1-го этажа</t>
         </is>
       </c>
       <c r="B64" s="5" t="n"/>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
@@ -3579,7 +3815,7 @@
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>Проверьте общий объем ЭППС 100 мм по спецификации.</t>
+          <t>Если у этой плиты есть балки, проверьте площадь опалубки балок; иначе оставьте пустым — она посчитается из позиций балок ниже.</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr"/>
@@ -3593,7 +3829,7 @@
       </c>
       <c r="K64" s="5" t="inlineStr">
         <is>
-          <t>total_eps_volume_from_spec_m3</t>
+          <t>beams_formwork_area_m2</t>
         </is>
       </c>
       <c r="L64" s="5" t="inlineStr">
@@ -3603,20 +3839,25 @@
       </c>
       <c r="M64" s="5" t="inlineStr">
         <is>
-          <t>floor_slab_1_eps100_volume</t>
-        </is>
-      </c>
+          <t>floor_slab_1_beams_formwork_area</t>
+        </is>
+      </c>
+      <c r="N64" s="5" t="n"/>
+      <c r="O64" s="5" t="n"/>
+      <c r="P64" s="5" t="n"/>
+      <c r="Q64" s="5" t="n"/>
+      <c r="R64" s="5" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>Арматура плиты перекрытия 1-го этажа по диаметрам</t>
+          <t>Объем бетона балок перекрытия 1-го этажа</t>
         </is>
       </c>
       <c r="B65" s="5" t="n"/>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
@@ -3626,7 +3867,7 @@
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>Проверьте позиции арматуры плиты перекрытия 1-го этажа по диаметрам, каждая строка спецификации отдельной строкой.</t>
+          <t>Если у этой плиты есть балки и в спецификации есть готовый итог по бетону балок, сверьте его; иначе оставьте пустым — он посчитается из позиций балок ниже.</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr"/>
@@ -3640,7 +3881,7 @@
       </c>
       <c r="K65" s="5" t="inlineStr">
         <is>
-          <t>floor_slab_1_rebar_items</t>
+          <t>beams_concrete_volume_m3</t>
         </is>
       </c>
       <c r="L65" s="5" t="inlineStr">
@@ -3650,20 +3891,25 @@
       </c>
       <c r="M65" s="5" t="inlineStr">
         <is>
-          <t>floor_slab_1_rebar_items</t>
-        </is>
-      </c>
+          <t>floor_slab_1_beams_concrete_volume</t>
+        </is>
+      </c>
+      <c r="N65" s="5" t="n"/>
+      <c r="O65" s="5" t="n"/>
+      <c r="P65" s="5" t="n"/>
+      <c r="Q65" s="5" t="n"/>
+      <c r="R65" s="5" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Ж/Б балки плиты перекрытия 1-го этажа</t>
+          <t>ЭППС 100 мм торец плиты, длина работ</t>
         </is>
       </c>
       <c r="B66" s="5" t="n"/>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>мп</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
@@ -3673,7 +3919,7 @@
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>Если у этой плиты перекрытия есть балки, проверьте их построчно; если балок нет, оставьте пустым.</t>
+          <t>Проверьте длину работ по ЭППС торца плиты.</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr"/>
@@ -3687,7 +3933,7 @@
       </c>
       <c r="K66" s="5" t="inlineStr">
         <is>
-          <t>beam_items</t>
+          <t>slab_outer_edge_eps_work_length_m</t>
         </is>
       </c>
       <c r="L66" s="5" t="inlineStr">
@@ -3697,18 +3943,27 @@
       </c>
       <c r="M66" s="5" t="inlineStr">
         <is>
-          <t>beam_items</t>
-        </is>
-      </c>
+          <t>floor_slab_1_edge_eps_work_length</t>
+        </is>
+      </c>
+      <c r="N66" s="5" t="n"/>
+      <c r="O66" s="5" t="n"/>
+      <c r="P66" s="5" t="n"/>
+      <c r="Q66" s="5" t="n"/>
+      <c r="R66" s="5" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>Контрольные итоги таблицы Ж/Б балок</t>
+          <t>Высота утепления торца плиты перекрытия 1-го этажа</t>
         </is>
       </c>
       <c r="B67" s="5" t="n"/>
-      <c r="C67" s="5" t="inlineStr"/>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
           <t>Проверьте</t>
@@ -3716,7 +3971,7 @@
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>Необязательные контрольные итоги таблицы балок, для справки.</t>
+          <t>Проверьте высоту утепления торца плиты.</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr"/>
@@ -3730,7 +3985,7 @@
       </c>
       <c r="K67" s="5" t="inlineStr">
         <is>
-          <t>beam_table_controls</t>
+          <t>edge_insulation_height_m</t>
         </is>
       </c>
       <c r="L67" s="5" t="inlineStr">
@@ -3740,20 +3995,25 @@
       </c>
       <c r="M67" s="5" t="inlineStr">
         <is>
-          <t>beam_table_controls</t>
-        </is>
-      </c>
+          <t>floor_slab_1_edge_insulation_height</t>
+        </is>
+      </c>
+      <c r="N67" s="5" t="n"/>
+      <c r="O67" s="5" t="n"/>
+      <c r="P67" s="5" t="n"/>
+      <c r="Q67" s="5" t="n"/>
+      <c r="R67" s="5" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>Подача опалубки и арматуры краном</t>
+          <t>ЭППС 100 мм торец плиты, площадь материала</t>
         </is>
       </c>
       <c r="B68" s="5" t="n"/>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>смена</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
@@ -3763,7 +4023,7 @@
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>Укажите смены крана для подачи опалубки и арматуры.</t>
+          <t>Проверьте площадь материала ЭППС по торцу плиты.</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr"/>
@@ -3777,26 +4037,35 @@
       </c>
       <c r="K68" s="5" t="inlineStr">
         <is>
-          <t>formwork_rebar_crane_shifts</t>
+          <t>slab_edge_eps_material_area_m2</t>
         </is>
       </c>
       <c r="L68" s="5" t="inlineStr">
         <is>
-          <t>SUPPLIER_INPUT</t>
-        </is>
-      </c>
-      <c r="M68" s="5" t="inlineStr"/>
+          <t>AUTO_PROJECT</t>
+        </is>
+      </c>
+      <c r="M68" s="5" t="inlineStr">
+        <is>
+          <t>floor_slab_1_edge_eps_material_area</t>
+        </is>
+      </c>
+      <c r="N68" s="5" t="n"/>
+      <c r="O68" s="5" t="n"/>
+      <c r="P68" s="5" t="n"/>
+      <c r="Q68" s="5" t="n"/>
+      <c r="R68" s="5" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>Работа бетононасоса</t>
+          <t>ЭППС 100 мм низ плиты, площадь работ</t>
         </is>
       </c>
       <c r="B69" s="5" t="n"/>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>смена</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
@@ -3806,7 +4075,7 @@
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>Укажите смены бетононасоса.</t>
+          <t>Проверьте площадь работ ЭППС по низу плиты.</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr"/>
@@ -3820,26 +4089,35 @@
       </c>
       <c r="K69" s="5" t="inlineStr">
         <is>
-          <t>concrete_pump_shifts</t>
+          <t>bottom_slab_eps_work_area_m2</t>
         </is>
       </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
-          <t>SUPPLIER_INPUT</t>
-        </is>
-      </c>
-      <c r="M69" s="5" t="inlineStr"/>
+          <t>AUTO_PROJECT</t>
+        </is>
+      </c>
+      <c r="M69" s="5" t="inlineStr">
+        <is>
+          <t>floor_slab_1_bottom_eps_work_area</t>
+        </is>
+      </c>
+      <c r="N69" s="5" t="n"/>
+      <c r="O69" s="5" t="n"/>
+      <c r="P69" s="5" t="n"/>
+      <c r="Q69" s="5" t="n"/>
+      <c r="R69" s="5" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>Эквивалент листов фанеры для свесов и доборов</t>
+          <t>ЭППС 100 мм для плиты перекрытия 1-го этажа, общий объем</t>
         </is>
       </c>
       <c r="B70" s="5" t="n"/>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>лист</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
@@ -3849,7 +4127,7 @@
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>Укажите эквивалент листов фанеры для свесов и доборов; не брать проектный fallback как универсальный дефолт.</t>
+          <t>Проверьте общий объем ЭППС 100 мм по спецификации.</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr"/>
@@ -3863,45 +4141,83 @@
       </c>
       <c r="K70" s="5" t="inlineStr">
         <is>
-          <t>overhang_sheet_equivalent</t>
+          <t>total_eps_volume_from_spec_m3</t>
         </is>
       </c>
       <c r="L70" s="5" t="inlineStr">
         <is>
-          <t>SUPPLIER_INPUT</t>
-        </is>
-      </c>
-      <c r="M70" s="5" t="inlineStr"/>
+          <t>AUTO_PROJECT</t>
+        </is>
+      </c>
+      <c r="M70" s="5" t="inlineStr">
+        <is>
+          <t>floor_slab_1_eps100_volume</t>
+        </is>
+      </c>
+      <c r="N70" s="5" t="n"/>
+      <c r="O70" s="5" t="n"/>
+      <c r="P70" s="5" t="n"/>
+      <c r="Q70" s="5" t="n"/>
+      <c r="R70" s="5" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="inlineStr">
-        <is>
-          <t>Перекрытие 2 этажа</t>
-        </is>
-      </c>
-      <c r="B71" s="4" t="inlineStr"/>
-      <c r="C71" s="4" t="inlineStr"/>
-      <c r="D71" s="4" t="inlineStr"/>
-      <c r="E71" s="4" t="inlineStr"/>
-      <c r="F71" s="4" t="inlineStr"/>
-      <c r="G71" s="4" t="inlineStr"/>
-      <c r="H71" s="4" t="inlineStr"/>
-      <c r="I71" s="4" t="inlineStr"/>
-      <c r="J71" s="4" t="inlineStr"/>
-      <c r="K71" s="4" t="inlineStr"/>
-      <c r="L71" s="4" t="inlineStr"/>
-      <c r="M71" s="4" t="inlineStr"/>
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>Контрольные итоги таблицы Ж/Б балок</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="n"/>
+      <c r="C71" s="5" t="inlineStr"/>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>Проверьте</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>Необязательные контрольные итоги таблицы балок, для справки.</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr"/>
+      <c r="G71" s="5" t="inlineStr"/>
+      <c r="H71" s="5" t="inlineStr"/>
+      <c r="I71" s="5" t="inlineStr"/>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>floor_slab_1</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="inlineStr">
+        <is>
+          <t>beam_table_controls</t>
+        </is>
+      </c>
+      <c r="L71" s="5" t="inlineStr">
+        <is>
+          <t>AUTO_PROJECT</t>
+        </is>
+      </c>
+      <c r="M71" s="5" t="inlineStr">
+        <is>
+          <t>beam_table_controls</t>
+        </is>
+      </c>
+      <c r="N71" s="5" t="n"/>
+      <c r="O71" s="5" t="n"/>
+      <c r="P71" s="5" t="n"/>
+      <c r="Q71" s="5" t="n"/>
+      <c r="R71" s="5" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>Площадь опалубки под плитой перекрытия 2-го этажа</t>
+          <t>Подача опалубки и арматуры краном</t>
         </is>
       </c>
       <c r="B72" s="5" t="n"/>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>смена</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
@@ -3911,7 +4227,7 @@
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>Проверьте площадь основной опалубки под плитой перекрытия 2-го этажа.</t>
+          <t>Укажите смены крана для подачи опалубки и арматуры.</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr"/>
@@ -3920,35 +4236,36 @@
       <c r="I72" s="5" t="inlineStr"/>
       <c r="J72" s="5" t="inlineStr">
         <is>
-          <t>floor_slab_2</t>
+          <t>floor_slab_1</t>
         </is>
       </c>
       <c r="K72" s="5" t="inlineStr">
         <is>
-          <t>main_formwork_area_m2</t>
+          <t>formwork_rebar_crane_shifts</t>
         </is>
       </c>
       <c r="L72" s="5" t="inlineStr">
         <is>
-          <t>AUTO_PROJECT</t>
-        </is>
-      </c>
-      <c r="M72" s="5" t="inlineStr">
-        <is>
-          <t>floor_slab_2_main_formwork_area</t>
-        </is>
-      </c>
+          <t>SUPPLIER_INPUT</t>
+        </is>
+      </c>
+      <c r="M72" s="5" t="inlineStr"/>
+      <c r="N72" s="5" t="n"/>
+      <c r="O72" s="5" t="n"/>
+      <c r="P72" s="5" t="n"/>
+      <c r="Q72" s="5" t="n"/>
+      <c r="R72" s="5" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>Площадь опалубки торца плиты перекрытия 2-го этажа</t>
+          <t>Работа бетононасоса</t>
         </is>
       </c>
       <c r="B73" s="5" t="n"/>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>смена</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
@@ -3958,7 +4275,7 @@
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>Проверьте площадь опалубки торца плиты перекрытия 2-го этажа.</t>
+          <t>Укажите смены бетононасоса.</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr"/>
@@ -3967,35 +4284,36 @@
       <c r="I73" s="5" t="inlineStr"/>
       <c r="J73" s="5" t="inlineStr">
         <is>
-          <t>floor_slab_2</t>
+          <t>floor_slab_1</t>
         </is>
       </c>
       <c r="K73" s="5" t="inlineStr">
         <is>
-          <t>edge_formwork_area_m2</t>
+          <t>concrete_pump_shifts</t>
         </is>
       </c>
       <c r="L73" s="5" t="inlineStr">
         <is>
-          <t>AUTO_PROJECT</t>
-        </is>
-      </c>
-      <c r="M73" s="5" t="inlineStr">
-        <is>
-          <t>floor_slab_2_edge_formwork_area</t>
-        </is>
-      </c>
+          <t>SUPPLIER_INPUT</t>
+        </is>
+      </c>
+      <c r="M73" s="5" t="inlineStr"/>
+      <c r="N73" s="5" t="n"/>
+      <c r="O73" s="5" t="n"/>
+      <c r="P73" s="5" t="n"/>
+      <c r="Q73" s="5" t="n"/>
+      <c r="R73" s="5" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>Площадь опалубки балок перекрытия 2-го этажа</t>
+          <t>Эквивалент листов фанеры для свесов и доборов</t>
         </is>
       </c>
       <c r="B74" s="5" t="n"/>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>лист</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
@@ -4005,7 +4323,7 @@
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>Если в этой плите есть балки, проверьте площадь опалубки балок; иначе оставьте пустым (не 0) — она посчитается из позиций балок ниже.</t>
+          <t>Укажите эквивалент листов фанеры для свесов и доборов; не брать проектный fallback как универсальный дефолт.</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr"/>
@@ -4014,360 +4332,324 @@
       <c r="I74" s="5" t="inlineStr"/>
       <c r="J74" s="5" t="inlineStr">
         <is>
-          <t>floor_slab_2</t>
+          <t>floor_slab_1</t>
         </is>
       </c>
       <c r="K74" s="5" t="inlineStr">
         <is>
-          <t>beams_formwork_area_m2</t>
+          <t>overhang_sheet_equivalent</t>
         </is>
       </c>
       <c r="L74" s="5" t="inlineStr">
         <is>
-          <t>AUTO_PROJECT</t>
-        </is>
-      </c>
-      <c r="M74" s="5" t="inlineStr">
-        <is>
-          <t>floor_slab_2_beams_formwork_area</t>
-        </is>
-      </c>
+          <t>SUPPLIER_INPUT</t>
+        </is>
+      </c>
+      <c r="M74" s="5" t="inlineStr"/>
+      <c r="N74" s="5" t="n"/>
+      <c r="O74" s="5" t="n"/>
+      <c r="P74" s="5" t="n"/>
+      <c r="Q74" s="5" t="n"/>
+      <c r="R74" s="5" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>Позиции балок плиты перекрытия 2-го этажа</t>
-        </is>
-      </c>
-      <c r="B75" s="5" t="n"/>
-      <c r="C75" s="5" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="D75" s="5" t="inlineStr">
-        <is>
-          <t>Проверьте</t>
-        </is>
-      </c>
-      <c r="E75" s="5" t="inlineStr">
-        <is>
-          <t>Если у этой плиты перекрытия есть балки, проверьте их построчно; если балок нет, оставьте пустым.</t>
-        </is>
-      </c>
-      <c r="F75" s="5" t="inlineStr"/>
-      <c r="G75" s="5" t="inlineStr"/>
-      <c r="H75" s="5" t="inlineStr"/>
-      <c r="I75" s="5" t="inlineStr"/>
-      <c r="J75" s="5" t="inlineStr">
-        <is>
-          <t>floor_slab_2</t>
-        </is>
-      </c>
-      <c r="K75" s="5" t="inlineStr">
-        <is>
-          <t>beam_items</t>
-        </is>
-      </c>
-      <c r="L75" s="5" t="inlineStr">
-        <is>
-          <t>AUTO_PROJECT</t>
-        </is>
-      </c>
-      <c r="M75" s="5" t="inlineStr">
-        <is>
-          <t>floor_slab_2_beam_items</t>
-        </is>
-      </c>
+      <c r="A75" s="2" t="n"/>
+      <c r="B75" s="2" t="n"/>
+      <c r="C75" s="2" t="n"/>
+      <c r="D75" s="2" t="n"/>
+      <c r="E75" s="2" t="n"/>
+      <c r="F75" s="2" t="n"/>
+      <c r="G75" s="2" t="n"/>
+      <c r="H75" s="2" t="n"/>
+      <c r="I75" s="2" t="n"/>
+      <c r="J75" s="2" t="n"/>
+      <c r="K75" s="2" t="n"/>
+      <c r="L75" s="2" t="n"/>
+      <c r="M75" s="2" t="n"/>
+      <c r="N75" s="2" t="n"/>
+      <c r="O75" s="2" t="n"/>
+      <c r="P75" s="2" t="n"/>
+      <c r="Q75" s="2" t="n"/>
+      <c r="R75" s="2" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>Периметр торца плиты перекрытия 2-го этажа</t>
-        </is>
-      </c>
-      <c r="B76" s="5" t="n"/>
-      <c r="C76" s="5" t="inlineStr">
-        <is>
-          <t>мп</t>
-        </is>
-      </c>
-      <c r="D76" s="5" t="inlineStr">
-        <is>
-          <t>Проверьте</t>
-        </is>
-      </c>
-      <c r="E76" s="5" t="inlineStr">
-        <is>
-          <t>Проверьте периметр/длину торца плиты перекрытия 2-го этажа.</t>
-        </is>
-      </c>
-      <c r="F76" s="5" t="inlineStr"/>
-      <c r="G76" s="5" t="inlineStr"/>
-      <c r="H76" s="5" t="inlineStr"/>
-      <c r="I76" s="5" t="inlineStr"/>
-      <c r="J76" s="5" t="inlineStr">
-        <is>
-          <t>floor_slab_2</t>
-        </is>
-      </c>
-      <c r="K76" s="5" t="inlineStr">
-        <is>
-          <t>slab_edge_perimeter_m</t>
-        </is>
-      </c>
-      <c r="L76" s="5" t="inlineStr">
-        <is>
-          <t>AUTO_PROJECT</t>
-        </is>
-      </c>
-      <c r="M76" s="5" t="inlineStr">
-        <is>
-          <t>floor_slab_2_slab_edge_perimeter</t>
-        </is>
-      </c>
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>Перекрытие 1 этажа — Арматура плиты перекрытия 1-го этажа по диаметрам (Проверьте позиции арматуры плиты перекрытия 1-го этажа по диаметрам, каждая строка спецификации отдельной строкой.)</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="n"/>
+      <c r="C76" s="4" t="n"/>
+      <c r="D76" s="4" t="n"/>
+      <c r="E76" s="4" t="n"/>
+      <c r="F76" s="4" t="n"/>
+      <c r="G76" s="4" t="n"/>
+      <c r="H76" s="4" t="n"/>
+      <c r="I76" s="4" t="n"/>
+      <c r="J76" s="4" t="n"/>
+      <c r="K76" s="4" t="n"/>
+      <c r="L76" s="4" t="n"/>
+      <c r="M76" s="4" t="n"/>
+      <c r="N76" s="4" t="n"/>
+      <c r="O76" s="4" t="n"/>
+      <c r="P76" s="4" t="n"/>
+      <c r="Q76" s="4" t="n"/>
+      <c r="R76" s="4" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="5" t="inlineStr">
-        <is>
-          <t>Высота утепления торца плиты перекрытия 2-го этажа</t>
-        </is>
-      </c>
-      <c r="B77" s="5" t="n"/>
-      <c r="C77" s="5" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="D77" s="5" t="inlineStr">
-        <is>
-          <t>Проверьте</t>
-        </is>
-      </c>
-      <c r="E77" s="5" t="inlineStr">
-        <is>
-          <t>Проверьте высоту утепления торца плиты перекрытия 2-го этажа.</t>
-        </is>
-      </c>
-      <c r="F77" s="5" t="inlineStr"/>
-      <c r="G77" s="5" t="inlineStr"/>
-      <c r="H77" s="5" t="inlineStr"/>
-      <c r="I77" s="5" t="inlineStr"/>
-      <c r="J77" s="5" t="inlineStr">
-        <is>
-          <t>floor_slab_2</t>
-        </is>
-      </c>
-      <c r="K77" s="5" t="inlineStr">
-        <is>
-          <t>edge_insulation_height_m</t>
-        </is>
-      </c>
-      <c r="L77" s="5" t="inlineStr">
-        <is>
-          <t>AUTO_PROJECT</t>
-        </is>
-      </c>
-      <c r="M77" s="5" t="inlineStr">
-        <is>
-          <t>floor_slab_2_edge_insulation_height</t>
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>Что проверяем</t>
+        </is>
+      </c>
+      <c r="B77" s="1" t="inlineStr">
+        <is>
+          <t>Найдено в проекте</t>
+        </is>
+      </c>
+      <c r="C77" s="1" t="inlineStr">
+        <is>
+          <t>Ед.</t>
+        </is>
+      </c>
+      <c r="D77" s="1" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="E77" s="1" t="inlineStr">
+        <is>
+          <t>Что нужно сделать</t>
+        </is>
+      </c>
+      <c r="F77" s="1" t="inlineStr">
+        <is>
+          <t>Источник</t>
+        </is>
+      </c>
+      <c r="G77" s="1" t="inlineStr">
+        <is>
+          <t>Фрагмент проекта</t>
+        </is>
+      </c>
+      <c r="H77" s="1" t="inlineStr">
+        <is>
+          <t>Исправить / ввести значение</t>
+        </is>
+      </c>
+      <c r="I77" s="1" t="inlineStr">
+        <is>
+          <t>Комментарий Елены</t>
+        </is>
+      </c>
+      <c r="J77" s="1" t="inlineStr">
+        <is>
+          <t>section_code</t>
+        </is>
+      </c>
+      <c r="K77" s="1" t="inlineStr">
+        <is>
+          <t>technical_key</t>
+        </is>
+      </c>
+      <c r="L77" s="1" t="inlineStr">
+        <is>
+          <t>source_class</t>
+        </is>
+      </c>
+      <c r="M77" s="1" t="inlineStr">
+        <is>
+          <t>target_code</t>
+        </is>
+      </c>
+      <c r="N77" s="1" t="inlineStr">
+        <is>
+          <t>Исправить: Длина по спецификации, мп</t>
+        </is>
+      </c>
+      <c r="O77" s="1" t="inlineStr">
+        <is>
+          <t>Исправить: Масса 1 м, кг/м</t>
+        </is>
+      </c>
+      <c r="P77" s="1" t="inlineStr"/>
+      <c r="Q77" s="1" t="inlineStr"/>
+      <c r="R77" s="1" t="inlineStr">
+        <is>
+          <t>row_data_json</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t>Бетон плиты перекрытия 2-го этажа, объем</t>
-        </is>
-      </c>
-      <c r="B78" s="5" t="n"/>
-      <c r="C78" s="5" t="inlineStr">
-        <is>
-          <t>м3</t>
-        </is>
-      </c>
-      <c r="D78" s="5" t="inlineStr">
-        <is>
-          <t>Проверьте</t>
-        </is>
-      </c>
-      <c r="E78" s="5" t="inlineStr">
-        <is>
-          <t>Проверьте объем бетона плиты перекрытия 2-го этажа по спецификации.</t>
-        </is>
-      </c>
-      <c r="F78" s="5" t="inlineStr"/>
-      <c r="G78" s="5" t="inlineStr"/>
-      <c r="H78" s="5" t="inlineStr"/>
-      <c r="I78" s="5" t="inlineStr"/>
-      <c r="J78" s="5" t="inlineStr">
-        <is>
-          <t>floor_slab_2</t>
-        </is>
-      </c>
-      <c r="K78" s="5" t="inlineStr">
-        <is>
-          <t>concrete_placing_volume_m3</t>
-        </is>
-      </c>
-      <c r="L78" s="5" t="inlineStr">
-        <is>
-          <t>AUTO_PROJECT</t>
-        </is>
-      </c>
-      <c r="M78" s="5" t="inlineStr">
-        <is>
-          <t>floor_slab_2_concrete_volume</t>
-        </is>
-      </c>
+      <c r="A78" s="2" t="n"/>
+      <c r="B78" s="2" t="n"/>
+      <c r="C78" s="2" t="n"/>
+      <c r="D78" s="2" t="n"/>
+      <c r="E78" s="2" t="n"/>
+      <c r="F78" s="2" t="n"/>
+      <c r="G78" s="2" t="n"/>
+      <c r="H78" s="2" t="n"/>
+      <c r="I78" s="2" t="n"/>
+      <c r="J78" s="2" t="n"/>
+      <c r="K78" s="2" t="n"/>
+      <c r="L78" s="2" t="n"/>
+      <c r="M78" s="2" t="n"/>
+      <c r="N78" s="2" t="n"/>
+      <c r="O78" s="2" t="n"/>
+      <c r="P78" s="2" t="n"/>
+      <c r="Q78" s="2" t="n"/>
+      <c r="R78" s="2" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t>Площадь плиты перекрытия 2-го этажа для контроля</t>
-        </is>
-      </c>
-      <c r="B79" s="5" t="n"/>
-      <c r="C79" s="5" t="inlineStr">
-        <is>
-          <t>м2</t>
-        </is>
-      </c>
-      <c r="D79" s="5" t="inlineStr">
-        <is>
-          <t>Проверьте</t>
-        </is>
-      </c>
-      <c r="E79" s="5" t="inlineStr">
-        <is>
-          <t>Если площадь плиты указана отдельно, проверьте ее как контроль.</t>
-        </is>
-      </c>
-      <c r="F79" s="5" t="inlineStr"/>
-      <c r="G79" s="5" t="inlineStr"/>
-      <c r="H79" s="5" t="inlineStr"/>
-      <c r="I79" s="5" t="inlineStr"/>
-      <c r="J79" s="5" t="inlineStr">
-        <is>
-          <t>floor_slab_2</t>
-        </is>
-      </c>
-      <c r="K79" s="5" t="inlineStr">
-        <is>
-          <t>slab_area_m2</t>
-        </is>
-      </c>
-      <c r="L79" s="5" t="inlineStr">
-        <is>
-          <t>AUTO_PROJECT</t>
-        </is>
-      </c>
-      <c r="M79" s="5" t="inlineStr">
-        <is>
-          <t>floor_slab_2_slab_area</t>
-        </is>
-      </c>
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>Перекрытие 1 этажа — Ж/Б балки плиты перекрытия 1-го этажа (Если у этой плиты перекрытия есть балки, проверьте их построчно; если балок нет, оставьте пустым.)</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="n"/>
+      <c r="C79" s="4" t="n"/>
+      <c r="D79" s="4" t="n"/>
+      <c r="E79" s="4" t="n"/>
+      <c r="F79" s="4" t="n"/>
+      <c r="G79" s="4" t="n"/>
+      <c r="H79" s="4" t="n"/>
+      <c r="I79" s="4" t="n"/>
+      <c r="J79" s="4" t="n"/>
+      <c r="K79" s="4" t="n"/>
+      <c r="L79" s="4" t="n"/>
+      <c r="M79" s="4" t="n"/>
+      <c r="N79" s="4" t="n"/>
+      <c r="O79" s="4" t="n"/>
+      <c r="P79" s="4" t="n"/>
+      <c r="Q79" s="4" t="n"/>
+      <c r="R79" s="4" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>Арматура плиты перекрытия 2-го этажа по диаметрам</t>
-        </is>
-      </c>
-      <c r="B80" s="5" t="n"/>
-      <c r="C80" s="5" t="inlineStr">
-        <is>
-          <t>мп</t>
-        </is>
-      </c>
-      <c r="D80" s="5" t="inlineStr">
-        <is>
-          <t>Проверьте</t>
-        </is>
-      </c>
-      <c r="E80" s="5" t="inlineStr">
-        <is>
-          <t>Проверьте позиции арматуры плиты перекрытия 2-го этажа по диаметрам, каждая строка спецификации отдельной строкой.</t>
-        </is>
-      </c>
-      <c r="F80" s="5" t="inlineStr"/>
-      <c r="G80" s="5" t="inlineStr"/>
-      <c r="H80" s="5" t="inlineStr"/>
-      <c r="I80" s="5" t="inlineStr"/>
-      <c r="J80" s="5" t="inlineStr">
-        <is>
-          <t>floor_slab_2</t>
-        </is>
-      </c>
-      <c r="K80" s="5" t="inlineStr">
-        <is>
-          <t>floor_slab_2_rebar_items</t>
-        </is>
-      </c>
-      <c r="L80" s="5" t="inlineStr">
-        <is>
-          <t>AUTO_PROJECT</t>
-        </is>
-      </c>
-      <c r="M80" s="5" t="inlineStr">
-        <is>
-          <t>floor_slab_2_rebar_items</t>
+      <c r="A80" s="1" t="inlineStr">
+        <is>
+          <t>Что проверяем</t>
+        </is>
+      </c>
+      <c r="B80" s="1" t="inlineStr">
+        <is>
+          <t>Найдено в проекте</t>
+        </is>
+      </c>
+      <c r="C80" s="1" t="inlineStr">
+        <is>
+          <t>Ед.</t>
+        </is>
+      </c>
+      <c r="D80" s="1" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="E80" s="1" t="inlineStr">
+        <is>
+          <t>Что нужно сделать</t>
+        </is>
+      </c>
+      <c r="F80" s="1" t="inlineStr">
+        <is>
+          <t>Источник</t>
+        </is>
+      </c>
+      <c r="G80" s="1" t="inlineStr">
+        <is>
+          <t>Фрагмент проекта</t>
+        </is>
+      </c>
+      <c r="H80" s="1" t="inlineStr">
+        <is>
+          <t>Исправить / ввести значение</t>
+        </is>
+      </c>
+      <c r="I80" s="1" t="inlineStr">
+        <is>
+          <t>Комментарий Елены</t>
+        </is>
+      </c>
+      <c r="J80" s="1" t="inlineStr">
+        <is>
+          <t>section_code</t>
+        </is>
+      </c>
+      <c r="K80" s="1" t="inlineStr">
+        <is>
+          <t>technical_key</t>
+        </is>
+      </c>
+      <c r="L80" s="1" t="inlineStr">
+        <is>
+          <t>source_class</t>
+        </is>
+      </c>
+      <c r="M80" s="1" t="inlineStr">
+        <is>
+          <t>target_code</t>
+        </is>
+      </c>
+      <c r="N80" s="1" t="inlineStr">
+        <is>
+          <t>Исправить: Длина, м</t>
+        </is>
+      </c>
+      <c r="O80" s="1" t="inlineStr">
+        <is>
+          <t>Исправить: Ширина, м</t>
+        </is>
+      </c>
+      <c r="P80" s="1" t="inlineStr">
+        <is>
+          <t>Исправить: Высота, м</t>
+        </is>
+      </c>
+      <c r="Q80" s="1" t="inlineStr">
+        <is>
+          <t>Исправить: Количество, шт</t>
+        </is>
+      </c>
+      <c r="R80" s="1" t="inlineStr">
+        <is>
+          <t>row_data_json</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>Коммерческое предложение поставщика на аренду опалубки, итого</t>
-        </is>
-      </c>
-      <c r="B81" s="5" t="n"/>
-      <c r="C81" s="5" t="inlineStr">
-        <is>
-          <t>руб</t>
-        </is>
-      </c>
-      <c r="D81" s="5" t="inlineStr">
-        <is>
-          <t>Проверьте</t>
-        </is>
-      </c>
-      <c r="E81" s="5" t="inlineStr">
-        <is>
-          <t>Укажите итоговую сумму коммерческого предложения поставщика на аренду опалубки.</t>
-        </is>
-      </c>
-      <c r="F81" s="5" t="inlineStr"/>
-      <c r="G81" s="5" t="inlineStr"/>
-      <c r="H81" s="5" t="inlineStr"/>
-      <c r="I81" s="5" t="inlineStr"/>
-      <c r="J81" s="5" t="inlineStr">
-        <is>
-          <t>floor_slab_2</t>
-        </is>
-      </c>
-      <c r="K81" s="5" t="inlineStr">
-        <is>
-          <t>formwork_rental_supplier_quote_total</t>
-        </is>
-      </c>
-      <c r="L81" s="5" t="inlineStr">
-        <is>
-          <t>SUPPLIER_INPUT</t>
-        </is>
-      </c>
-      <c r="M81" s="5" t="inlineStr"/>
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>Перекрытие 2 этажа</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr"/>
+      <c r="C81" s="4" t="inlineStr"/>
+      <c r="D81" s="4" t="inlineStr"/>
+      <c r="E81" s="4" t="inlineStr"/>
+      <c r="F81" s="4" t="inlineStr"/>
+      <c r="G81" s="4" t="inlineStr"/>
+      <c r="H81" s="4" t="inlineStr"/>
+      <c r="I81" s="4" t="inlineStr"/>
+      <c r="J81" s="4" t="inlineStr"/>
+      <c r="K81" s="4" t="inlineStr"/>
+      <c r="L81" s="4" t="inlineStr"/>
+      <c r="M81" s="4" t="inlineStr"/>
+      <c r="N81" s="4" t="n"/>
+      <c r="O81" s="4" t="n"/>
+      <c r="P81" s="4" t="n"/>
+      <c r="Q81" s="4" t="n"/>
+      <c r="R81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>Подача опалубки и арматуры краном</t>
+          <t>Площадь опалубки под плитой перекрытия 2-го этажа</t>
         </is>
       </c>
       <c r="B82" s="5" t="n"/>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>смена</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
@@ -4377,7 +4659,7 @@
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>Укажите смены крана для подачи опалубки и арматуры.</t>
+          <t>Проверьте площадь основной опалубки под плитой перекрытия 2-го этажа.</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr"/>
@@ -4391,26 +4673,35 @@
       </c>
       <c r="K82" s="5" t="inlineStr">
         <is>
-          <t>crane_shifts</t>
+          <t>main_formwork_area_m2</t>
         </is>
       </c>
       <c r="L82" s="5" t="inlineStr">
         <is>
-          <t>SUPPLIER_INPUT</t>
-        </is>
-      </c>
-      <c r="M82" s="5" t="inlineStr"/>
+          <t>AUTO_PROJECT</t>
+        </is>
+      </c>
+      <c r="M82" s="5" t="inlineStr">
+        <is>
+          <t>floor_slab_2_main_formwork_area</t>
+        </is>
+      </c>
+      <c r="N82" s="5" t="n"/>
+      <c r="O82" s="5" t="n"/>
+      <c r="P82" s="5" t="n"/>
+      <c r="Q82" s="5" t="n"/>
+      <c r="R82" s="5" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>Работа бетононасоса</t>
+          <t>Площадь опалубки торца плиты перекрытия 2-го этажа</t>
         </is>
       </c>
       <c r="B83" s="5" t="n"/>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>смена</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
@@ -4420,7 +4711,7 @@
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>Укажите смены бетононасоса.</t>
+          <t>Проверьте площадь опалубки торца плиты перекрытия 2-го этажа.</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr"/>
@@ -4434,45 +4725,87 @@
       </c>
       <c r="K83" s="5" t="inlineStr">
         <is>
-          <t>concrete_pump_shifts</t>
+          <t>edge_formwork_area_m2</t>
         </is>
       </c>
       <c r="L83" s="5" t="inlineStr">
         <is>
-          <t>SUPPLIER_INPUT</t>
-        </is>
-      </c>
-      <c r="M83" s="5" t="inlineStr"/>
+          <t>AUTO_PROJECT</t>
+        </is>
+      </c>
+      <c r="M83" s="5" t="inlineStr">
+        <is>
+          <t>floor_slab_2_edge_formwork_area</t>
+        </is>
+      </c>
+      <c r="N83" s="5" t="n"/>
+      <c r="O83" s="5" t="n"/>
+      <c r="P83" s="5" t="n"/>
+      <c r="Q83" s="5" t="n"/>
+      <c r="R83" s="5" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="4" t="inlineStr">
-        <is>
-          <t>Кровля</t>
-        </is>
-      </c>
-      <c r="B84" s="4" t="inlineStr"/>
-      <c r="C84" s="4" t="inlineStr"/>
-      <c r="D84" s="4" t="inlineStr"/>
-      <c r="E84" s="4" t="inlineStr"/>
-      <c r="F84" s="4" t="inlineStr"/>
-      <c r="G84" s="4" t="inlineStr"/>
-      <c r="H84" s="4" t="inlineStr"/>
-      <c r="I84" s="4" t="inlineStr"/>
-      <c r="J84" s="4" t="inlineStr"/>
-      <c r="K84" s="4" t="inlineStr"/>
-      <c r="L84" s="4" t="inlineStr"/>
-      <c r="M84" s="4" t="inlineStr"/>
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>Площадь опалубки балок перекрытия 2-го этажа</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="n"/>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>Проверьте</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>Если в этой плите есть балки, проверьте площадь опалубки балок; иначе оставьте пустым (не 0) — она посчитается из позиций балок ниже.</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="inlineStr"/>
+      <c r="G84" s="5" t="inlineStr"/>
+      <c r="H84" s="5" t="inlineStr"/>
+      <c r="I84" s="5" t="inlineStr"/>
+      <c r="J84" s="5" t="inlineStr">
+        <is>
+          <t>floor_slab_2</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="inlineStr">
+        <is>
+          <t>beams_formwork_area_m2</t>
+        </is>
+      </c>
+      <c r="L84" s="5" t="inlineStr">
+        <is>
+          <t>AUTO_PROJECT</t>
+        </is>
+      </c>
+      <c r="M84" s="5" t="inlineStr">
+        <is>
+          <t>floor_slab_2_beams_formwork_area</t>
+        </is>
+      </c>
+      <c r="N84" s="5" t="n"/>
+      <c r="O84" s="5" t="n"/>
+      <c r="P84" s="5" t="n"/>
+      <c r="Q84" s="5" t="n"/>
+      <c r="R84" s="5" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>Площадь кровли уровня 1</t>
+          <t>Объем бетона балок перекрытия 2-го этажа</t>
         </is>
       </c>
       <c r="B85" s="5" t="n"/>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
@@ -4482,7 +4815,7 @@
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>Проверьте площадь кровли первого уровня.</t>
+          <t>Если у этой плиты есть балки и в спецификации есть готовый итог по бетону балок, сверьте его; иначе оставьте пустым — он посчитается из позиций балок ниже.</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr"/>
@@ -4491,12 +4824,12 @@
       <c r="I85" s="5" t="inlineStr"/>
       <c r="J85" s="5" t="inlineStr">
         <is>
-          <t>flat_roof</t>
+          <t>floor_slab_2</t>
         </is>
       </c>
       <c r="K85" s="5" t="inlineStr">
         <is>
-          <t>roof_area_level_1_m2</t>
+          <t>beams_concrete_volume_m3</t>
         </is>
       </c>
       <c r="L85" s="5" t="inlineStr">
@@ -4506,20 +4839,25 @@
       </c>
       <c r="M85" s="5" t="inlineStr">
         <is>
-          <t>roof_area_level_1</t>
-        </is>
-      </c>
+          <t>floor_slab_2_beams_concrete_volume</t>
+        </is>
+      </c>
+      <c r="N85" s="5" t="n"/>
+      <c r="O85" s="5" t="n"/>
+      <c r="P85" s="5" t="n"/>
+      <c r="Q85" s="5" t="n"/>
+      <c r="R85" s="5" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>Площадь кровли уровня 2</t>
+          <t>Периметр торца плиты перекрытия 2-го этажа</t>
         </is>
       </c>
       <c r="B86" s="5" t="n"/>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>мп</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
@@ -4529,7 +4867,7 @@
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>Проверьте площадь кровли второго уровня или подтвердите 0.</t>
+          <t>Проверьте периметр/длину торца плиты перекрытия 2-го этажа.</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr"/>
@@ -4538,12 +4876,12 @@
       <c r="I86" s="5" t="inlineStr"/>
       <c r="J86" s="5" t="inlineStr">
         <is>
-          <t>flat_roof</t>
+          <t>floor_slab_2</t>
         </is>
       </c>
       <c r="K86" s="5" t="inlineStr">
         <is>
-          <t>roof_area_level_2_m2</t>
+          <t>slab_edge_perimeter_m</t>
         </is>
       </c>
       <c r="L86" s="5" t="inlineStr">
@@ -4553,20 +4891,25 @@
       </c>
       <c r="M86" s="5" t="inlineStr">
         <is>
-          <t>roof_area_level_2</t>
-        </is>
-      </c>
+          <t>floor_slab_2_slab_edge_perimeter</t>
+        </is>
+      </c>
+      <c r="N86" s="5" t="n"/>
+      <c r="O86" s="5" t="n"/>
+      <c r="P86" s="5" t="n"/>
+      <c r="Q86" s="5" t="n"/>
+      <c r="R86" s="5" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>Площадь кровли по спецификации, контроль</t>
+          <t>Высота утепления торца плиты перекрытия 2-го этажа</t>
         </is>
       </c>
       <c r="B87" s="5" t="n"/>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>м</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
@@ -4576,7 +4919,7 @@
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>Если есть отдельная итоговая площадь кровли, проверьте ее как контроль.</t>
+          <t>Проверьте высоту утепления торца плиты перекрытия 2-го этажа.</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr"/>
@@ -4585,12 +4928,12 @@
       <c r="I87" s="5" t="inlineStr"/>
       <c r="J87" s="5" t="inlineStr">
         <is>
-          <t>flat_roof</t>
+          <t>floor_slab_2</t>
         </is>
       </c>
       <c r="K87" s="5" t="inlineStr">
         <is>
-          <t>project_spec_roof_area_m2</t>
+          <t>edge_insulation_height_m</t>
         </is>
       </c>
       <c r="L87" s="5" t="inlineStr">
@@ -4600,20 +4943,25 @@
       </c>
       <c r="M87" s="5" t="inlineStr">
         <is>
-          <t>project_spec_roof_area</t>
-        </is>
-      </c>
+          <t>floor_slab_2_edge_insulation_height</t>
+        </is>
+      </c>
+      <c r="N87" s="5" t="n"/>
+      <c r="O87" s="5" t="n"/>
+      <c r="P87" s="5" t="n"/>
+      <c r="Q87" s="5" t="n"/>
+      <c r="R87" s="5" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>Длина парапета уровня 1</t>
+          <t>Бетон плиты перекрытия 2-го этажа, объем</t>
         </is>
       </c>
       <c r="B88" s="5" t="n"/>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
@@ -4623,7 +4971,7 @@
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>Проверьте длину парапета первого уровня.</t>
+          <t>Проверьте объем бетона плиты перекрытия 2-го этажа по спецификации.</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr"/>
@@ -4632,12 +4980,12 @@
       <c r="I88" s="5" t="inlineStr"/>
       <c r="J88" s="5" t="inlineStr">
         <is>
-          <t>flat_roof</t>
+          <t>floor_slab_2</t>
         </is>
       </c>
       <c r="K88" s="5" t="inlineStr">
         <is>
-          <t>parapet_length_level_1_m</t>
+          <t>concrete_placing_volume_m3</t>
         </is>
       </c>
       <c r="L88" s="5" t="inlineStr">
@@ -4647,20 +4995,25 @@
       </c>
       <c r="M88" s="5" t="inlineStr">
         <is>
-          <t>roof_parapet_length_level_1</t>
-        </is>
-      </c>
+          <t>floor_slab_2_concrete_volume</t>
+        </is>
+      </c>
+      <c r="N88" s="5" t="n"/>
+      <c r="O88" s="5" t="n"/>
+      <c r="P88" s="5" t="n"/>
+      <c r="Q88" s="5" t="n"/>
+      <c r="R88" s="5" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>Длина парапета уровня 2</t>
+          <t>Площадь плиты перекрытия 2-го этажа для контроля</t>
         </is>
       </c>
       <c r="B89" s="5" t="n"/>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
@@ -4670,7 +5023,7 @@
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>Проверьте длину парапета второго уровня или подтвердите 0.</t>
+          <t>Если площадь плиты указана отдельно, проверьте ее как контроль.</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr"/>
@@ -4679,12 +5032,12 @@
       <c r="I89" s="5" t="inlineStr"/>
       <c r="J89" s="5" t="inlineStr">
         <is>
-          <t>flat_roof</t>
+          <t>floor_slab_2</t>
         </is>
       </c>
       <c r="K89" s="5" t="inlineStr">
         <is>
-          <t>parapet_length_level_2_m</t>
+          <t>slab_area_m2</t>
         </is>
       </c>
       <c r="L89" s="5" t="inlineStr">
@@ -4694,20 +5047,25 @@
       </c>
       <c r="M89" s="5" t="inlineStr">
         <is>
-          <t>roof_parapet_length_level_2</t>
-        </is>
-      </c>
+          <t>floor_slab_2_slab_area</t>
+        </is>
+      </c>
+      <c r="N89" s="5" t="n"/>
+      <c r="O89" s="5" t="n"/>
+      <c r="P89" s="5" t="n"/>
+      <c r="Q89" s="5" t="n"/>
+      <c r="R89" s="5" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>Длина примыканий к вентшахтам уровня 1</t>
+          <t>Коммерческое предложение поставщика на аренду опалубки, итого</t>
         </is>
       </c>
       <c r="B90" s="5" t="n"/>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>руб</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
@@ -4717,7 +5075,7 @@
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>Проверьте длину примыканий к вентшахтам первого уровня.</t>
+          <t>Укажите итоговую сумму коммерческого предложения поставщика на аренду опалубки.</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr"/>
@@ -4726,35 +5084,36 @@
       <c r="I90" s="5" t="inlineStr"/>
       <c r="J90" s="5" t="inlineStr">
         <is>
-          <t>flat_roof</t>
+          <t>floor_slab_2</t>
         </is>
       </c>
       <c r="K90" s="5" t="inlineStr">
         <is>
-          <t>vent_wall_abutment_level_1_m</t>
+          <t>formwork_rental_supplier_quote_total</t>
         </is>
       </c>
       <c r="L90" s="5" t="inlineStr">
         <is>
-          <t>AUTO_PROJECT</t>
-        </is>
-      </c>
-      <c r="M90" s="5" t="inlineStr">
-        <is>
-          <t>roof_vent_wall_abutment_level_1</t>
-        </is>
-      </c>
+          <t>SUPPLIER_INPUT</t>
+        </is>
+      </c>
+      <c r="M90" s="5" t="inlineStr"/>
+      <c r="N90" s="5" t="n"/>
+      <c r="O90" s="5" t="n"/>
+      <c r="P90" s="5" t="n"/>
+      <c r="Q90" s="5" t="n"/>
+      <c r="R90" s="5" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>Длина примыканий к вентшахтам уровня 2</t>
+          <t>Подача опалубки и арматуры краном</t>
         </is>
       </c>
       <c r="B91" s="5" t="n"/>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>смена</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
@@ -4764,7 +5123,7 @@
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>Проверьте длину примыканий к вентшахтам второго уровня или подтвердите 0.</t>
+          <t>Укажите смены крана для подачи опалубки и арматуры.</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr"/>
@@ -4773,35 +5132,36 @@
       <c r="I91" s="5" t="inlineStr"/>
       <c r="J91" s="5" t="inlineStr">
         <is>
-          <t>flat_roof</t>
+          <t>floor_slab_2</t>
         </is>
       </c>
       <c r="K91" s="5" t="inlineStr">
         <is>
-          <t>vent_wall_abutment_level_2_m</t>
+          <t>crane_shifts</t>
         </is>
       </c>
       <c r="L91" s="5" t="inlineStr">
         <is>
-          <t>AUTO_PROJECT</t>
-        </is>
-      </c>
-      <c r="M91" s="5" t="inlineStr">
-        <is>
-          <t>roof_vent_wall_abutment_level_2</t>
-        </is>
-      </c>
+          <t>SUPPLIER_INPUT</t>
+        </is>
+      </c>
+      <c r="M91" s="5" t="inlineStr"/>
+      <c r="N91" s="5" t="n"/>
+      <c r="O91" s="5" t="n"/>
+      <c r="P91" s="5" t="n"/>
+      <c r="Q91" s="5" t="n"/>
+      <c r="R91" s="5" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>Аэраторы кровельные</t>
+          <t>Работа бетононасоса</t>
         </is>
       </c>
       <c r="B92" s="5" t="n"/>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>смена</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
@@ -4811,7 +5171,7 @@
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>Проверьте количество кровельных аэраторов.</t>
+          <t>Укажите смены бетононасоса.</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr"/>
@@ -4820,344 +5180,324 @@
       <c r="I92" s="5" t="inlineStr"/>
       <c r="J92" s="5" t="inlineStr">
         <is>
-          <t>flat_roof</t>
+          <t>floor_slab_2</t>
         </is>
       </c>
       <c r="K92" s="5" t="inlineStr">
         <is>
-          <t>roof_aerators_count</t>
+          <t>concrete_pump_shifts</t>
         </is>
       </c>
       <c r="L92" s="5" t="inlineStr">
         <is>
-          <t>AUTO_PROJECT</t>
-        </is>
-      </c>
-      <c r="M92" s="5" t="inlineStr">
-        <is>
-          <t>roof_aerators_count</t>
-        </is>
-      </c>
+          <t>SUPPLIER_INPUT</t>
+        </is>
+      </c>
+      <c r="M92" s="5" t="inlineStr"/>
+      <c r="N92" s="5" t="n"/>
+      <c r="O92" s="5" t="n"/>
+      <c r="P92" s="5" t="n"/>
+      <c r="Q92" s="5" t="n"/>
+      <c r="R92" s="5" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="5" t="inlineStr">
-        <is>
-          <t>Парапетные воронки</t>
-        </is>
-      </c>
-      <c r="B93" s="5" t="n"/>
-      <c r="C93" s="5" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D93" s="5" t="inlineStr">
-        <is>
-          <t>Проверьте</t>
-        </is>
-      </c>
-      <c r="E93" s="5" t="inlineStr">
-        <is>
-          <t>Проверьте количество парапетных воронок.</t>
-        </is>
-      </c>
-      <c r="F93" s="5" t="inlineStr"/>
-      <c r="G93" s="5" t="inlineStr"/>
-      <c r="H93" s="5" t="inlineStr"/>
-      <c r="I93" s="5" t="inlineStr"/>
-      <c r="J93" s="5" t="inlineStr">
-        <is>
-          <t>flat_roof</t>
-        </is>
-      </c>
-      <c r="K93" s="5" t="inlineStr">
-        <is>
-          <t>parapet_roof_drains_count</t>
-        </is>
-      </c>
-      <c r="L93" s="5" t="inlineStr">
-        <is>
-          <t>AUTO_PROJECT</t>
-        </is>
-      </c>
-      <c r="M93" s="5" t="inlineStr">
-        <is>
-          <t>roof_parapet_drains_count</t>
-        </is>
-      </c>
+      <c r="A93" s="2" t="n"/>
+      <c r="B93" s="2" t="n"/>
+      <c r="C93" s="2" t="n"/>
+      <c r="D93" s="2" t="n"/>
+      <c r="E93" s="2" t="n"/>
+      <c r="F93" s="2" t="n"/>
+      <c r="G93" s="2" t="n"/>
+      <c r="H93" s="2" t="n"/>
+      <c r="I93" s="2" t="n"/>
+      <c r="J93" s="2" t="n"/>
+      <c r="K93" s="2" t="n"/>
+      <c r="L93" s="2" t="n"/>
+      <c r="M93" s="2" t="n"/>
+      <c r="N93" s="2" t="n"/>
+      <c r="O93" s="2" t="n"/>
+      <c r="P93" s="2" t="n"/>
+      <c r="Q93" s="2" t="n"/>
+      <c r="R93" s="2" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="5" t="inlineStr">
-        <is>
-          <t>Воронки внутреннего водостока</t>
-        </is>
-      </c>
-      <c r="B94" s="5" t="n"/>
-      <c r="C94" s="5" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D94" s="5" t="inlineStr">
-        <is>
-          <t>Проверьте</t>
-        </is>
-      </c>
-      <c r="E94" s="5" t="inlineStr">
-        <is>
-          <t>Проверьте количество воронок внутреннего водостока.</t>
-        </is>
-      </c>
-      <c r="F94" s="5" t="inlineStr"/>
-      <c r="G94" s="5" t="inlineStr"/>
-      <c r="H94" s="5" t="inlineStr"/>
-      <c r="I94" s="5" t="inlineStr"/>
-      <c r="J94" s="5" t="inlineStr">
-        <is>
-          <t>flat_roof</t>
-        </is>
-      </c>
-      <c r="K94" s="5" t="inlineStr">
-        <is>
-          <t>internal_roof_drains_count</t>
-        </is>
-      </c>
-      <c r="L94" s="5" t="inlineStr">
-        <is>
-          <t>AUTO_PROJECT</t>
-        </is>
-      </c>
-      <c r="M94" s="5" t="inlineStr">
-        <is>
-          <t>roof_internal_drains_count</t>
-        </is>
-      </c>
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>Перекрытие 2 этажа — Позиции балок плиты перекрытия 2-го этажа (Если у этой плиты перекрытия есть балки, проверьте их построчно; если балок нет, оставьте пустым.)</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="n"/>
+      <c r="C94" s="4" t="n"/>
+      <c r="D94" s="4" t="n"/>
+      <c r="E94" s="4" t="n"/>
+      <c r="F94" s="4" t="n"/>
+      <c r="G94" s="4" t="n"/>
+      <c r="H94" s="4" t="n"/>
+      <c r="I94" s="4" t="n"/>
+      <c r="J94" s="4" t="n"/>
+      <c r="K94" s="4" t="n"/>
+      <c r="L94" s="4" t="n"/>
+      <c r="M94" s="4" t="n"/>
+      <c r="N94" s="4" t="n"/>
+      <c r="O94" s="4" t="n"/>
+      <c r="P94" s="4" t="n"/>
+      <c r="Q94" s="4" t="n"/>
+      <c r="R94" s="4" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="5" t="inlineStr">
-        <is>
-          <t>Высота внутреннего водостока на одну воронку</t>
-        </is>
-      </c>
-      <c r="B95" s="5" t="n"/>
-      <c r="C95" s="5" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="D95" s="5" t="inlineStr">
-        <is>
-          <t>Проверьте</t>
-        </is>
-      </c>
-      <c r="E95" s="5" t="inlineStr">
-        <is>
-          <t>Проверьте высоту/длину внутреннего водостока на одну воронку.</t>
-        </is>
-      </c>
-      <c r="F95" s="5" t="inlineStr"/>
-      <c r="G95" s="5" t="inlineStr"/>
-      <c r="H95" s="5" t="inlineStr"/>
-      <c r="I95" s="5" t="inlineStr"/>
-      <c r="J95" s="5" t="inlineStr">
-        <is>
-          <t>flat_roof</t>
-        </is>
-      </c>
-      <c r="K95" s="5" t="inlineStr">
-        <is>
-          <t>internal_drain_height_per_drain_m</t>
-        </is>
-      </c>
-      <c r="L95" s="5" t="inlineStr">
-        <is>
-          <t>AUTO_PROJECT</t>
-        </is>
-      </c>
-      <c r="M95" s="5" t="inlineStr">
-        <is>
-          <t>roof_internal_drain_height_per_drain</t>
+      <c r="A95" s="1" t="inlineStr">
+        <is>
+          <t>Что проверяем</t>
+        </is>
+      </c>
+      <c r="B95" s="1" t="inlineStr">
+        <is>
+          <t>Найдено в проекте</t>
+        </is>
+      </c>
+      <c r="C95" s="1" t="inlineStr">
+        <is>
+          <t>Ед.</t>
+        </is>
+      </c>
+      <c r="D95" s="1" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="E95" s="1" t="inlineStr">
+        <is>
+          <t>Что нужно сделать</t>
+        </is>
+      </c>
+      <c r="F95" s="1" t="inlineStr">
+        <is>
+          <t>Источник</t>
+        </is>
+      </c>
+      <c r="G95" s="1" t="inlineStr">
+        <is>
+          <t>Фрагмент проекта</t>
+        </is>
+      </c>
+      <c r="H95" s="1" t="inlineStr">
+        <is>
+          <t>Исправить / ввести значение</t>
+        </is>
+      </c>
+      <c r="I95" s="1" t="inlineStr">
+        <is>
+          <t>Комментарий Елены</t>
+        </is>
+      </c>
+      <c r="J95" s="1" t="inlineStr">
+        <is>
+          <t>section_code</t>
+        </is>
+      </c>
+      <c r="K95" s="1" t="inlineStr">
+        <is>
+          <t>technical_key</t>
+        </is>
+      </c>
+      <c r="L95" s="1" t="inlineStr">
+        <is>
+          <t>source_class</t>
+        </is>
+      </c>
+      <c r="M95" s="1" t="inlineStr">
+        <is>
+          <t>target_code</t>
+        </is>
+      </c>
+      <c r="N95" s="1" t="inlineStr">
+        <is>
+          <t>Исправить: Длина, м</t>
+        </is>
+      </c>
+      <c r="O95" s="1" t="inlineStr">
+        <is>
+          <t>Исправить: Ширина, м</t>
+        </is>
+      </c>
+      <c r="P95" s="1" t="inlineStr">
+        <is>
+          <t>Исправить: Высота, м</t>
+        </is>
+      </c>
+      <c r="Q95" s="1" t="inlineStr">
+        <is>
+          <t>Исправить: Количество, шт</t>
+        </is>
+      </c>
+      <c r="R95" s="1" t="inlineStr">
+        <is>
+          <t>row_data_json</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="5" t="inlineStr">
-        <is>
-          <t>Сырые строки спецификации кровли</t>
-        </is>
-      </c>
-      <c r="B96" s="5" t="n"/>
-      <c r="C96" s="5" t="inlineStr"/>
-      <c r="D96" s="5" t="inlineStr">
-        <is>
-          <t>Проверьте</t>
-        </is>
-      </c>
-      <c r="E96" s="5" t="inlineStr">
-        <is>
-          <t>Необязательные сырые строки спецификации кровли, для справки.</t>
-        </is>
-      </c>
-      <c r="F96" s="5" t="inlineStr"/>
-      <c r="G96" s="5" t="inlineStr"/>
-      <c r="H96" s="5" t="inlineStr"/>
-      <c r="I96" s="5" t="inlineStr"/>
-      <c r="J96" s="5" t="inlineStr">
-        <is>
-          <t>flat_roof</t>
-        </is>
-      </c>
-      <c r="K96" s="5" t="inlineStr">
-        <is>
-          <t>roof_raw_material_spec_rows</t>
-        </is>
-      </c>
-      <c r="L96" s="5" t="inlineStr">
-        <is>
-          <t>AUTO_PROJECT</t>
-        </is>
-      </c>
-      <c r="M96" s="5" t="inlineStr">
-        <is>
-          <t>roof_raw_material_spec_rows</t>
-        </is>
-      </c>
+      <c r="A96" s="2" t="n"/>
+      <c r="B96" s="2" t="n"/>
+      <c r="C96" s="2" t="n"/>
+      <c r="D96" s="2" t="n"/>
+      <c r="E96" s="2" t="n"/>
+      <c r="F96" s="2" t="n"/>
+      <c r="G96" s="2" t="n"/>
+      <c r="H96" s="2" t="n"/>
+      <c r="I96" s="2" t="n"/>
+      <c r="J96" s="2" t="n"/>
+      <c r="K96" s="2" t="n"/>
+      <c r="L96" s="2" t="n"/>
+      <c r="M96" s="2" t="n"/>
+      <c r="N96" s="2" t="n"/>
+      <c r="O96" s="2" t="n"/>
+      <c r="P96" s="2" t="n"/>
+      <c r="Q96" s="2" t="n"/>
+      <c r="R96" s="2" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="5" t="inlineStr">
-        <is>
-          <t>Коэффициент работ кровли</t>
-        </is>
-      </c>
-      <c r="B97" s="5" t="n"/>
-      <c r="C97" s="5" t="inlineStr"/>
-      <c r="D97" s="5" t="inlineStr">
-        <is>
-          <t>Проверьте</t>
-        </is>
-      </c>
-      <c r="E97" s="5" t="inlineStr">
-        <is>
-          <t>Проверьте коэффициент работ кровли.</t>
-        </is>
-      </c>
-      <c r="F97" s="5" t="inlineStr"/>
-      <c r="G97" s="5" t="inlineStr"/>
-      <c r="H97" s="5" t="inlineStr"/>
-      <c r="I97" s="5" t="inlineStr"/>
-      <c r="J97" s="5" t="inlineStr">
-        <is>
-          <t>flat_roof</t>
-        </is>
-      </c>
-      <c r="K97" s="5" t="inlineStr">
-        <is>
-          <t>roof_work_coeff</t>
-        </is>
-      </c>
-      <c r="L97" s="5" t="inlineStr">
-        <is>
-          <t>SUPPLIER_INPUT</t>
-        </is>
-      </c>
-      <c r="M97" s="5" t="inlineStr"/>
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>Перекрытие 2 этажа — Арматура плиты перекрытия 2-го этажа по диаметрам (Проверьте позиции арматуры плиты перекрытия 2-го этажа по диаметрам, каждая строка спецификации отдельной строкой.)</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="n"/>
+      <c r="C97" s="4" t="n"/>
+      <c r="D97" s="4" t="n"/>
+      <c r="E97" s="4" t="n"/>
+      <c r="F97" s="4" t="n"/>
+      <c r="G97" s="4" t="n"/>
+      <c r="H97" s="4" t="n"/>
+      <c r="I97" s="4" t="n"/>
+      <c r="J97" s="4" t="n"/>
+      <c r="K97" s="4" t="n"/>
+      <c r="L97" s="4" t="n"/>
+      <c r="M97" s="4" t="n"/>
+      <c r="N97" s="4" t="n"/>
+      <c r="O97" s="4" t="n"/>
+      <c r="P97" s="4" t="n"/>
+      <c r="Q97" s="4" t="n"/>
+      <c r="R97" s="4" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="5" t="inlineStr">
-        <is>
-          <t>ЭППС 50 мм, требуемый объем поставщика</t>
-        </is>
-      </c>
-      <c r="B98" s="5" t="n"/>
-      <c r="C98" s="5" t="inlineStr">
-        <is>
-          <t>м3</t>
-        </is>
-      </c>
-      <c r="D98" s="5" t="inlineStr">
-        <is>
-          <t>Проверьте</t>
-        </is>
-      </c>
-      <c r="E98" s="5" t="inlineStr">
-        <is>
-          <t>Укажите объем ЭППС 50 мм от поставщика/Технониколь.</t>
-        </is>
-      </c>
-      <c r="F98" s="5" t="inlineStr"/>
-      <c r="G98" s="5" t="inlineStr"/>
-      <c r="H98" s="5" t="inlineStr"/>
-      <c r="I98" s="5" t="inlineStr"/>
-      <c r="J98" s="5" t="inlineStr">
-        <is>
-          <t>flat_roof</t>
-        </is>
-      </c>
-      <c r="K98" s="5" t="inlineStr">
-        <is>
-          <t>eps50_supplier_required_volume_m3</t>
-        </is>
-      </c>
-      <c r="L98" s="5" t="inlineStr">
-        <is>
-          <t>SUPPLIER_INPUT</t>
-        </is>
-      </c>
-      <c r="M98" s="5" t="inlineStr"/>
+      <c r="A98" s="1" t="inlineStr">
+        <is>
+          <t>Что проверяем</t>
+        </is>
+      </c>
+      <c r="B98" s="1" t="inlineStr">
+        <is>
+          <t>Найдено в проекте</t>
+        </is>
+      </c>
+      <c r="C98" s="1" t="inlineStr">
+        <is>
+          <t>Ед.</t>
+        </is>
+      </c>
+      <c r="D98" s="1" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="E98" s="1" t="inlineStr">
+        <is>
+          <t>Что нужно сделать</t>
+        </is>
+      </c>
+      <c r="F98" s="1" t="inlineStr">
+        <is>
+          <t>Источник</t>
+        </is>
+      </c>
+      <c r="G98" s="1" t="inlineStr">
+        <is>
+          <t>Фрагмент проекта</t>
+        </is>
+      </c>
+      <c r="H98" s="1" t="inlineStr">
+        <is>
+          <t>Исправить / ввести значение</t>
+        </is>
+      </c>
+      <c r="I98" s="1" t="inlineStr">
+        <is>
+          <t>Комментарий Елены</t>
+        </is>
+      </c>
+      <c r="J98" s="1" t="inlineStr">
+        <is>
+          <t>section_code</t>
+        </is>
+      </c>
+      <c r="K98" s="1" t="inlineStr">
+        <is>
+          <t>technical_key</t>
+        </is>
+      </c>
+      <c r="L98" s="1" t="inlineStr">
+        <is>
+          <t>source_class</t>
+        </is>
+      </c>
+      <c r="M98" s="1" t="inlineStr">
+        <is>
+          <t>target_code</t>
+        </is>
+      </c>
+      <c r="N98" s="1" t="inlineStr">
+        <is>
+          <t>Исправить: Длина по спецификации, мп</t>
+        </is>
+      </c>
+      <c r="O98" s="1" t="inlineStr">
+        <is>
+          <t>Исправить: Масса 1 м, кг/м</t>
+        </is>
+      </c>
+      <c r="P98" s="1" t="inlineStr"/>
+      <c r="Q98" s="1" t="inlineStr"/>
+      <c r="R98" s="1" t="inlineStr">
+        <is>
+          <t>row_data_json</t>
+        </is>
+      </c>
     </row>
     <row r="99">
-      <c r="A99" s="5" t="inlineStr">
-        <is>
-          <t>SLOPE плиты A, требуемый объем поставщика</t>
-        </is>
-      </c>
-      <c r="B99" s="5" t="n"/>
-      <c r="C99" s="5" t="inlineStr">
-        <is>
-          <t>м3</t>
-        </is>
-      </c>
-      <c r="D99" s="5" t="inlineStr">
-        <is>
-          <t>Проверьте</t>
-        </is>
-      </c>
-      <c r="E99" s="5" t="inlineStr">
-        <is>
-          <t>Укажите объем SLOPE плит A от поставщика.</t>
-        </is>
-      </c>
-      <c r="F99" s="5" t="inlineStr"/>
-      <c r="G99" s="5" t="inlineStr"/>
-      <c r="H99" s="5" t="inlineStr"/>
-      <c r="I99" s="5" t="inlineStr"/>
-      <c r="J99" s="5" t="inlineStr">
-        <is>
-          <t>flat_roof</t>
-        </is>
-      </c>
-      <c r="K99" s="5" t="inlineStr">
-        <is>
-          <t>slope_plate_a_supplier_required_volume_m3</t>
-        </is>
-      </c>
-      <c r="L99" s="5" t="inlineStr">
-        <is>
-          <t>SUPPLIER_INPUT</t>
-        </is>
-      </c>
-      <c r="M99" s="5" t="inlineStr"/>
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>Кровля</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr"/>
+      <c r="C99" s="4" t="inlineStr"/>
+      <c r="D99" s="4" t="inlineStr"/>
+      <c r="E99" s="4" t="inlineStr"/>
+      <c r="F99" s="4" t="inlineStr"/>
+      <c r="G99" s="4" t="inlineStr"/>
+      <c r="H99" s="4" t="inlineStr"/>
+      <c r="I99" s="4" t="inlineStr"/>
+      <c r="J99" s="4" t="inlineStr"/>
+      <c r="K99" s="4" t="inlineStr"/>
+      <c r="L99" s="4" t="inlineStr"/>
+      <c r="M99" s="4" t="inlineStr"/>
+      <c r="N99" s="4" t="n"/>
+      <c r="O99" s="4" t="n"/>
+      <c r="P99" s="4" t="n"/>
+      <c r="Q99" s="4" t="n"/>
+      <c r="R99" s="4" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>SLOPE плиты B, требуемый объем поставщика</t>
+          <t>Площадь кровли уровня 1</t>
         </is>
       </c>
       <c r="B100" s="5" t="n"/>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
@@ -5167,7 +5507,7 @@
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>Укажите объем SLOPE плит B от поставщика.</t>
+          <t>Проверьте площадь кровли первого уровня.</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr"/>
@@ -5181,26 +5521,35 @@
       </c>
       <c r="K100" s="5" t="inlineStr">
         <is>
-          <t>slope_plate_b_supplier_required_volume_m3</t>
+          <t>roof_area_level_1_m2</t>
         </is>
       </c>
       <c r="L100" s="5" t="inlineStr">
         <is>
-          <t>SUPPLIER_INPUT</t>
-        </is>
-      </c>
-      <c r="M100" s="5" t="inlineStr"/>
+          <t>AUTO_PROJECT</t>
+        </is>
+      </c>
+      <c r="M100" s="5" t="inlineStr">
+        <is>
+          <t>roof_area_level_1</t>
+        </is>
+      </c>
+      <c r="N100" s="5" t="n"/>
+      <c r="O100" s="5" t="n"/>
+      <c r="P100" s="5" t="n"/>
+      <c r="Q100" s="5" t="n"/>
+      <c r="R100" s="5" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>SLOPE плиты J, требуемый объем поставщика</t>
+          <t>Площадь кровли уровня 2</t>
         </is>
       </c>
       <c r="B101" s="5" t="n"/>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
@@ -5210,7 +5559,7 @@
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>Укажите объем SLOPE плит J от поставщика.</t>
+          <t>Проверьте площадь кровли второго уровня или подтвердите 0.</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr"/>
@@ -5224,26 +5573,35 @@
       </c>
       <c r="K101" s="5" t="inlineStr">
         <is>
-          <t>slope_plate_j_supplier_required_volume_m3</t>
+          <t>roof_area_level_2_m2</t>
         </is>
       </c>
       <c r="L101" s="5" t="inlineStr">
         <is>
-          <t>SUPPLIER_INPUT</t>
-        </is>
-      </c>
-      <c r="M101" s="5" t="inlineStr"/>
+          <t>AUTO_PROJECT</t>
+        </is>
+      </c>
+      <c r="M101" s="5" t="inlineStr">
+        <is>
+          <t>roof_area_level_2</t>
+        </is>
+      </c>
+      <c r="N101" s="5" t="n"/>
+      <c r="O101" s="5" t="n"/>
+      <c r="P101" s="5" t="n"/>
+      <c r="Q101" s="5" t="n"/>
+      <c r="R101" s="5" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>SLOPE плиты K, требуемый объем поставщика</t>
+          <t>Площадь кровли по спецификации, контроль</t>
         </is>
       </c>
       <c r="B102" s="5" t="n"/>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
@@ -5253,7 +5611,7 @@
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>Укажите объем SLOPE плит K от поставщика.</t>
+          <t>Если есть отдельная итоговая площадь кровли, проверьте ее как контроль.</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr"/>
@@ -5267,26 +5625,35 @@
       </c>
       <c r="K102" s="5" t="inlineStr">
         <is>
-          <t>slope_plate_k_supplier_required_volume_m3</t>
+          <t>project_spec_roof_area_m2</t>
         </is>
       </c>
       <c r="L102" s="5" t="inlineStr">
         <is>
-          <t>SUPPLIER_INPUT</t>
-        </is>
-      </c>
-      <c r="M102" s="5" t="inlineStr"/>
+          <t>AUTO_PROJECT</t>
+        </is>
+      </c>
+      <c r="M102" s="5" t="inlineStr">
+        <is>
+          <t>project_spec_roof_area</t>
+        </is>
+      </c>
+      <c r="N102" s="5" t="n"/>
+      <c r="O102" s="5" t="n"/>
+      <c r="P102" s="5" t="n"/>
+      <c r="Q102" s="5" t="n"/>
+      <c r="R102" s="5" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>Примыкания к вентшахтам, количество</t>
+          <t>Длина парапета уровня 1</t>
         </is>
       </c>
       <c r="B103" s="5" t="n"/>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>мп</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
@@ -5296,7 +5663,7 @@
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>Проверьте количество примыканий к вентшахтам.</t>
+          <t>Проверьте длину парапета первого уровня.</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr"/>
@@ -5310,30 +5677,35 @@
       </c>
       <c r="K103" s="5" t="inlineStr">
         <is>
-          <t>vent_shaft_abutment_count</t>
+          <t>parapet_length_level_1_m</t>
         </is>
       </c>
       <c r="L103" s="5" t="inlineStr">
         <is>
-          <t>SUPPLIER_INPUT</t>
+          <t>AUTO_PROJECT</t>
         </is>
       </c>
       <c r="M103" s="5" t="inlineStr">
         <is>
-          <t>vent_shaft_abutment_count</t>
-        </is>
-      </c>
+          <t>roof_parapet_length_level_1</t>
+        </is>
+      </c>
+      <c r="N103" s="5" t="n"/>
+      <c r="O103" s="5" t="n"/>
+      <c r="P103" s="5" t="n"/>
+      <c r="Q103" s="5" t="n"/>
+      <c r="R103" s="5" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>Отверстия в стенах из газоблока</t>
+          <t>Длина парапета уровня 2</t>
         </is>
       </c>
       <c r="B104" s="5" t="n"/>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>мп</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
@@ -5343,7 +5715,7 @@
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>Проверьте количество отверстий в газоблоке.</t>
+          <t>Проверьте длину парапета второго уровня или подтвердите 0.</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr"/>
@@ -5357,30 +5729,35 @@
       </c>
       <c r="K104" s="5" t="inlineStr">
         <is>
-          <t>gas_block_wall_holes_count</t>
+          <t>parapet_length_level_2_m</t>
         </is>
       </c>
       <c r="L104" s="5" t="inlineStr">
         <is>
-          <t>SUPPLIER_INPUT</t>
+          <t>AUTO_PROJECT</t>
         </is>
       </c>
       <c r="M104" s="5" t="inlineStr">
         <is>
-          <t>gas_block_wall_holes_count</t>
-        </is>
-      </c>
+          <t>roof_parapet_length_level_2</t>
+        </is>
+      </c>
+      <c r="N104" s="5" t="n"/>
+      <c r="O104" s="5" t="n"/>
+      <c r="P104" s="5" t="n"/>
+      <c r="Q104" s="5" t="n"/>
+      <c r="R104" s="5" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>Подъем материалов автокраном</t>
+          <t>Длина примыканий к вентшахтам уровня 1</t>
         </is>
       </c>
       <c r="B105" s="5" t="n"/>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>смена</t>
+          <t>мп</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
@@ -5390,7 +5767,7 @@
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>Укажите смены автокрана для кровли.</t>
+          <t>Проверьте длину примыканий к вентшахтам первого уровня.</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr"/>
@@ -5404,26 +5781,35 @@
       </c>
       <c r="K105" s="5" t="inlineStr">
         <is>
-          <t>roof_crane_lifting_shifts</t>
+          <t>vent_wall_abutment_level_1_m</t>
         </is>
       </c>
       <c r="L105" s="5" t="inlineStr">
         <is>
-          <t>SUPPLIER_INPUT</t>
-        </is>
-      </c>
-      <c r="M105" s="5" t="inlineStr"/>
+          <t>AUTO_PROJECT</t>
+        </is>
+      </c>
+      <c r="M105" s="5" t="inlineStr">
+        <is>
+          <t>roof_vent_wall_abutment_level_1</t>
+        </is>
+      </c>
+      <c r="N105" s="5" t="n"/>
+      <c r="O105" s="5" t="n"/>
+      <c r="P105" s="5" t="n"/>
+      <c r="Q105" s="5" t="n"/>
+      <c r="R105" s="5" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>Расходные материалы кровли</t>
+          <t>Длина примыканий к вентшахтам уровня 2</t>
         </is>
       </c>
       <c r="B106" s="5" t="n"/>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>руб.</t>
+          <t>мп</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
@@ -5433,7 +5819,7 @@
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>Укажите сумму расходников кровли или будущую формулу.</t>
+          <t>Проверьте длину примыканий к вентшахтам второго уровня или подтвердите 0.</t>
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr"/>
@@ -5447,26 +5833,35 @@
       </c>
       <c r="K106" s="5" t="inlineStr">
         <is>
-          <t>roof_consumables_total_raw</t>
+          <t>vent_wall_abutment_level_2_m</t>
         </is>
       </c>
       <c r="L106" s="5" t="inlineStr">
         <is>
-          <t>SUPPLIER_INPUT</t>
-        </is>
-      </c>
-      <c r="M106" s="5" t="inlineStr"/>
+          <t>AUTO_PROJECT</t>
+        </is>
+      </c>
+      <c r="M106" s="5" t="inlineStr">
+        <is>
+          <t>roof_vent_wall_abutment_level_2</t>
+        </is>
+      </c>
+      <c r="N106" s="5" t="n"/>
+      <c r="O106" s="5" t="n"/>
+      <c r="P106" s="5" t="n"/>
+      <c r="Q106" s="5" t="n"/>
+      <c r="R106" s="5" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>Вывоз мусора кровли</t>
+          <t>Аэраторы кровельные</t>
         </is>
       </c>
       <c r="B107" s="5" t="n"/>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>маш</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
@@ -5476,7 +5871,7 @@
       </c>
       <c r="E107" s="5" t="inlineStr">
         <is>
-          <t>Укажите количество машин вывоза мусора по кровле.</t>
+          <t>Проверьте количество кровельных аэраторов.</t>
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr"/>
@@ -5490,26 +5885,35 @@
       </c>
       <c r="K107" s="5" t="inlineStr">
         <is>
-          <t>roof_waste_removal_trucks</t>
+          <t>roof_aerators_count</t>
         </is>
       </c>
       <c r="L107" s="5" t="inlineStr">
         <is>
-          <t>SUPPLIER_INPUT</t>
-        </is>
-      </c>
-      <c r="M107" s="5" t="inlineStr"/>
+          <t>AUTO_PROJECT</t>
+        </is>
+      </c>
+      <c r="M107" s="5" t="inlineStr">
+        <is>
+          <t>roof_aerators_count</t>
+        </is>
+      </c>
+      <c r="N107" s="5" t="n"/>
+      <c r="O107" s="5" t="n"/>
+      <c r="P107" s="5" t="n"/>
+      <c r="Q107" s="5" t="n"/>
+      <c r="R107" s="5" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>Логистика и снабжение кровли</t>
+          <t>Парапетные воронки</t>
         </is>
       </c>
       <c r="B108" s="5" t="n"/>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>руб.</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
@@ -5519,7 +5923,7 @@
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>Укажите сумму логистики и снабжения кровли или будущую формулу.</t>
+          <t>Проверьте количество парапетных воронок.</t>
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr"/>
@@ -5533,26 +5937,35 @@
       </c>
       <c r="K108" s="5" t="inlineStr">
         <is>
-          <t>roof_logistics_and_supply_total_raw</t>
+          <t>parapet_roof_drains_count</t>
         </is>
       </c>
       <c r="L108" s="5" t="inlineStr">
         <is>
-          <t>SUPPLIER_INPUT</t>
-        </is>
-      </c>
-      <c r="M108" s="5" t="inlineStr"/>
+          <t>AUTO_PROJECT</t>
+        </is>
+      </c>
+      <c r="M108" s="5" t="inlineStr">
+        <is>
+          <t>roof_parapet_drains_count</t>
+        </is>
+      </c>
+      <c r="N108" s="5" t="n"/>
+      <c r="O108" s="5" t="n"/>
+      <c r="P108" s="5" t="n"/>
+      <c r="Q108" s="5" t="n"/>
+      <c r="R108" s="5" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>Технический надзор кровли</t>
+          <t>Воронки внутреннего водостока</t>
         </is>
       </c>
       <c r="B109" s="5" t="n"/>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>руб.</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
@@ -5562,7 +5975,7 @@
       </c>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>Укажите технический надзор по кровле.</t>
+          <t>Проверьте количество воронок внутреннего водостока.</t>
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr"/>
@@ -5576,26 +5989,35 @@
       </c>
       <c r="K109" s="5" t="inlineStr">
         <is>
-          <t>technical_supervision_work_total</t>
+          <t>internal_roof_drains_count</t>
         </is>
       </c>
       <c r="L109" s="5" t="inlineStr">
         <is>
-          <t>SUPPLIER_INPUT</t>
-        </is>
-      </c>
-      <c r="M109" s="5" t="inlineStr"/>
+          <t>AUTO_PROJECT</t>
+        </is>
+      </c>
+      <c r="M109" s="5" t="inlineStr">
+        <is>
+          <t>roof_internal_drains_count</t>
+        </is>
+      </c>
+      <c r="N109" s="5" t="n"/>
+      <c r="O109" s="5" t="n"/>
+      <c r="P109" s="5" t="n"/>
+      <c r="Q109" s="5" t="n"/>
+      <c r="R109" s="5" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>Заготовительно-складские расходы кровли</t>
+          <t>Высота внутреннего водостока на одну воронку</t>
         </is>
       </c>
       <c r="B110" s="5" t="n"/>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>руб.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
@@ -5605,7 +6027,7 @@
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>Укажите заготовительно-складские расходы по кровле.</t>
+          <t>Проверьте высоту/длину внутреннего водостока на одну воронку.</t>
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr"/>
@@ -5619,47 +6041,81 @@
       </c>
       <c r="K110" s="5" t="inlineStr">
         <is>
-          <t>procurement_storage_work_total</t>
+          <t>internal_drain_height_per_drain_m</t>
         </is>
       </c>
       <c r="L110" s="5" t="inlineStr">
         <is>
-          <t>SUPPLIER_INPUT</t>
-        </is>
-      </c>
-      <c r="M110" s="5" t="inlineStr"/>
+          <t>AUTO_PROJECT</t>
+        </is>
+      </c>
+      <c r="M110" s="5" t="inlineStr">
+        <is>
+          <t>roof_internal_drain_height_per_drain</t>
+        </is>
+      </c>
+      <c r="N110" s="5" t="n"/>
+      <c r="O110" s="5" t="n"/>
+      <c r="P110" s="5" t="n"/>
+      <c r="Q110" s="5" t="n"/>
+      <c r="R110" s="5" t="n"/>
     </row>
     <row r="111">
-      <c r="A111" s="4" t="inlineStr">
-        <is>
-          <t>Вентиляционные каналы Schiedel</t>
-        </is>
-      </c>
-      <c r="B111" s="4" t="inlineStr"/>
-      <c r="C111" s="4" t="inlineStr"/>
-      <c r="D111" s="4" t="inlineStr"/>
-      <c r="E111" s="4" t="inlineStr"/>
-      <c r="F111" s="4" t="inlineStr"/>
-      <c r="G111" s="4" t="inlineStr"/>
-      <c r="H111" s="4" t="inlineStr"/>
-      <c r="I111" s="4" t="inlineStr"/>
-      <c r="J111" s="4" t="inlineStr"/>
-      <c r="K111" s="4" t="inlineStr"/>
-      <c r="L111" s="4" t="inlineStr"/>
-      <c r="M111" s="4" t="inlineStr"/>
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t>Сырые строки спецификации кровли</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="n"/>
+      <c r="C111" s="5" t="inlineStr"/>
+      <c r="D111" s="5" t="inlineStr">
+        <is>
+          <t>Проверьте</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="inlineStr">
+        <is>
+          <t>Необязательные сырые строки спецификации кровли, для справки.</t>
+        </is>
+      </c>
+      <c r="F111" s="5" t="inlineStr"/>
+      <c r="G111" s="5" t="inlineStr"/>
+      <c r="H111" s="5" t="inlineStr"/>
+      <c r="I111" s="5" t="inlineStr"/>
+      <c r="J111" s="5" t="inlineStr">
+        <is>
+          <t>flat_roof</t>
+        </is>
+      </c>
+      <c r="K111" s="5" t="inlineStr">
+        <is>
+          <t>roof_raw_material_spec_rows</t>
+        </is>
+      </c>
+      <c r="L111" s="5" t="inlineStr">
+        <is>
+          <t>AUTO_PROJECT</t>
+        </is>
+      </c>
+      <c r="M111" s="5" t="inlineStr">
+        <is>
+          <t>roof_raw_material_spec_rows</t>
+        </is>
+      </c>
+      <c r="N111" s="5" t="n"/>
+      <c r="O111" s="5" t="n"/>
+      <c r="P111" s="5" t="n"/>
+      <c r="Q111" s="5" t="n"/>
+      <c r="R111" s="5" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>Общая длина кладки вентканалов Schiedel</t>
+          <t>Коэффициент работ кровли</t>
         </is>
       </c>
       <c r="B112" s="5" t="n"/>
-      <c r="C112" s="5" t="inlineStr">
-        <is>
-          <t>мп</t>
-        </is>
-      </c>
+      <c r="C112" s="5" t="inlineStr"/>
       <c r="D112" s="5" t="inlineStr">
         <is>
           <t>Проверьте</t>
@@ -5667,7 +6123,7 @@
       </c>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>Проверьте общую длину/высоту кладки вентканалов Schiedel.</t>
+          <t>Проверьте коэффициент работ кровли.</t>
         </is>
       </c>
       <c r="F112" s="5" t="inlineStr"/>
@@ -5676,35 +6132,36 @@
       <c r="I112" s="5" t="inlineStr"/>
       <c r="J112" s="5" t="inlineStr">
         <is>
-          <t>schiedel_vent_channels</t>
+          <t>flat_roof</t>
         </is>
       </c>
       <c r="K112" s="5" t="inlineStr">
         <is>
-          <t>schiedel_masonry_total_length_m</t>
+          <t>roof_work_coeff</t>
         </is>
       </c>
       <c r="L112" s="5" t="inlineStr">
         <is>
-          <t>AUTO_PROJECT</t>
-        </is>
-      </c>
-      <c r="M112" s="5" t="inlineStr">
-        <is>
-          <t>schiedel_masonry_total_length_m</t>
-        </is>
-      </c>
+          <t>SUPPLIER_INPUT</t>
+        </is>
+      </c>
+      <c r="M112" s="5" t="inlineStr"/>
+      <c r="N112" s="5" t="n"/>
+      <c r="O112" s="5" t="n"/>
+      <c r="P112" s="5" t="n"/>
+      <c r="Q112" s="5" t="n"/>
+      <c r="R112" s="5" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>Высота вентканала 1</t>
+          <t>ЭППС 50 мм, требуемый объем поставщика</t>
         </is>
       </c>
       <c r="B113" s="5" t="n"/>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
@@ -5714,7 +6171,7 @@
       </c>
       <c r="E113" s="5" t="inlineStr">
         <is>
-          <t>Проверьте высоту вентканала 1 как контроль длины кладки.</t>
+          <t>Укажите объем ЭППС 50 мм от поставщика/Технониколь.</t>
         </is>
       </c>
       <c r="F113" s="5" t="inlineStr"/>
@@ -5723,35 +6180,36 @@
       <c r="I113" s="5" t="inlineStr"/>
       <c r="J113" s="5" t="inlineStr">
         <is>
-          <t>schiedel_vent_channels</t>
+          <t>flat_roof</t>
         </is>
       </c>
       <c r="K113" s="5" t="inlineStr">
         <is>
-          <t>vent_channel_1_height_m</t>
+          <t>eps50_supplier_required_volume_m3</t>
         </is>
       </c>
       <c r="L113" s="5" t="inlineStr">
         <is>
-          <t>AUTO_PROJECT</t>
-        </is>
-      </c>
-      <c r="M113" s="5" t="inlineStr">
-        <is>
-          <t>vent_channel_1_height</t>
-        </is>
-      </c>
+          <t>SUPPLIER_INPUT</t>
+        </is>
+      </c>
+      <c r="M113" s="5" t="inlineStr"/>
+      <c r="N113" s="5" t="n"/>
+      <c r="O113" s="5" t="n"/>
+      <c r="P113" s="5" t="n"/>
+      <c r="Q113" s="5" t="n"/>
+      <c r="R113" s="5" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>Высота вентканала 2</t>
+          <t>SLOPE плиты A, требуемый объем поставщика</t>
         </is>
       </c>
       <c r="B114" s="5" t="n"/>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
@@ -5761,7 +6219,7 @@
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>Проверьте высоту вентканала 2 как контроль длины кладки.</t>
+          <t>Укажите объем SLOPE плит A от поставщика.</t>
         </is>
       </c>
       <c r="F114" s="5" t="inlineStr"/>
@@ -5770,35 +6228,36 @@
       <c r="I114" s="5" t="inlineStr"/>
       <c r="J114" s="5" t="inlineStr">
         <is>
-          <t>schiedel_vent_channels</t>
+          <t>flat_roof</t>
         </is>
       </c>
       <c r="K114" s="5" t="inlineStr">
         <is>
-          <t>vent_channel_2_height_m</t>
+          <t>slope_plate_a_supplier_required_volume_m3</t>
         </is>
       </c>
       <c r="L114" s="5" t="inlineStr">
         <is>
-          <t>AUTO_PROJECT</t>
-        </is>
-      </c>
-      <c r="M114" s="5" t="inlineStr">
-        <is>
-          <t>vent_channel_2_height</t>
-        </is>
-      </c>
+          <t>SUPPLIER_INPUT</t>
+        </is>
+      </c>
+      <c r="M114" s="5" t="inlineStr"/>
+      <c r="N114" s="5" t="n"/>
+      <c r="O114" s="5" t="n"/>
+      <c r="P114" s="5" t="n"/>
+      <c r="Q114" s="5" t="n"/>
+      <c r="R114" s="5" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>Количество вентканалов типа 2 для контроля длины</t>
+          <t>SLOPE плиты B, требуемый объем поставщика</t>
         </is>
       </c>
       <c r="B115" s="5" t="n"/>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
@@ -5808,7 +6267,7 @@
       </c>
       <c r="E115" s="5" t="inlineStr">
         <is>
-          <t>Проверьте количество вентканалов типа 2 для контрольной формулы длины.</t>
+          <t>Укажите объем SLOPE плит B от поставщика.</t>
         </is>
       </c>
       <c r="F115" s="5" t="inlineStr"/>
@@ -5817,35 +6276,36 @@
       <c r="I115" s="5" t="inlineStr"/>
       <c r="J115" s="5" t="inlineStr">
         <is>
-          <t>schiedel_vent_channels</t>
+          <t>flat_roof</t>
         </is>
       </c>
       <c r="K115" s="5" t="inlineStr">
         <is>
-          <t>vent_channel_2_count</t>
+          <t>slope_plate_b_supplier_required_volume_m3</t>
         </is>
       </c>
       <c r="L115" s="5" t="inlineStr">
         <is>
-          <t>AUTO_PROJECT</t>
-        </is>
-      </c>
-      <c r="M115" s="5" t="inlineStr">
-        <is>
-          <t>vent_channel_2_count</t>
-        </is>
-      </c>
+          <t>SUPPLIER_INPUT</t>
+        </is>
+      </c>
+      <c r="M115" s="5" t="inlineStr"/>
+      <c r="N115" s="5" t="n"/>
+      <c r="O115" s="5" t="n"/>
+      <c r="P115" s="5" t="n"/>
+      <c r="Q115" s="5" t="n"/>
+      <c r="R115" s="5" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>Сегменты / строки спецификации вентканалов</t>
+          <t>SLOPE плиты J, требуемый объем поставщика</t>
         </is>
       </c>
       <c r="B116" s="5" t="n"/>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
@@ -5855,7 +6315,7 @@
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>Проверьте строки спецификации вентканалов построчно, если есть.</t>
+          <t>Укажите объем SLOPE плит J от поставщика.</t>
         </is>
       </c>
       <c r="F116" s="5" t="inlineStr"/>
@@ -5864,35 +6324,36 @@
       <c r="I116" s="5" t="inlineStr"/>
       <c r="J116" s="5" t="inlineStr">
         <is>
-          <t>schiedel_vent_channels</t>
+          <t>flat_roof</t>
         </is>
       </c>
       <c r="K116" s="5" t="inlineStr">
         <is>
-          <t>schiedel_vent_chimney_cladding_segments</t>
+          <t>slope_plate_j_supplier_required_volume_m3</t>
         </is>
       </c>
       <c r="L116" s="5" t="inlineStr">
         <is>
-          <t>AUTO_PROJECT</t>
-        </is>
-      </c>
-      <c r="M116" s="5" t="inlineStr">
-        <is>
-          <t>schiedel_vent_chimney_cladding_segments</t>
-        </is>
-      </c>
+          <t>SUPPLIER_INPUT</t>
+        </is>
+      </c>
+      <c r="M116" s="5" t="inlineStr"/>
+      <c r="N116" s="5" t="n"/>
+      <c r="O116" s="5" t="n"/>
+      <c r="P116" s="5" t="n"/>
+      <c r="Q116" s="5" t="n"/>
+      <c r="R116" s="5" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>Вентиляционный канал 2х,36/25 см Schiedel — количество</t>
+          <t>SLOPE плиты K, требуемый объем поставщика</t>
         </is>
       </c>
       <c r="B117" s="5" t="n"/>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
@@ -5902,7 +6363,7 @@
       </c>
       <c r="E117" s="5" t="inlineStr">
         <is>
-          <t>Подтвердите закупочное количество Schiedel 2х по спецификации или таблице Елены.</t>
+          <t>Укажите объем SLOPE плит K от поставщика.</t>
         </is>
       </c>
       <c r="F117" s="5" t="inlineStr"/>
@@ -5911,12 +6372,12 @@
       <c r="I117" s="5" t="inlineStr"/>
       <c r="J117" s="5" t="inlineStr">
         <is>
-          <t>schiedel_vent_channels</t>
+          <t>flat_roof</t>
         </is>
       </c>
       <c r="K117" s="5" t="inlineStr">
         <is>
-          <t>schiedel_vent_channel_2x_count</t>
+          <t>slope_plate_k_supplier_required_volume_m3</t>
         </is>
       </c>
       <c r="L117" s="5" t="inlineStr">
@@ -5924,16 +6385,17 @@
           <t>SUPPLIER_INPUT</t>
         </is>
       </c>
-      <c r="M117" s="5" t="inlineStr">
-        <is>
-          <t>schiedel_vent_channel_2x_count</t>
-        </is>
-      </c>
+      <c r="M117" s="5" t="inlineStr"/>
+      <c r="N117" s="5" t="n"/>
+      <c r="O117" s="5" t="n"/>
+      <c r="P117" s="5" t="n"/>
+      <c r="Q117" s="5" t="n"/>
+      <c r="R117" s="5" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>Вентиляционный канал 3х,52/25 см Schiedel — количество</t>
+          <t>Примыкания к вентшахтам, количество</t>
         </is>
       </c>
       <c r="B118" s="5" t="n"/>
@@ -5949,7 +6411,7 @@
       </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>Подтвердите закупочное количество Schiedel 3х по спецификации или таблице Елены.</t>
+          <t>Проверьте количество примыканий к вентшахтам.</t>
         </is>
       </c>
       <c r="F118" s="5" t="inlineStr"/>
@@ -5958,12 +6420,12 @@
       <c r="I118" s="5" t="inlineStr"/>
       <c r="J118" s="5" t="inlineStr">
         <is>
-          <t>schiedel_vent_channels</t>
+          <t>flat_roof</t>
         </is>
       </c>
       <c r="K118" s="5" t="inlineStr">
         <is>
-          <t>schiedel_vent_channel_3x_count</t>
+          <t>vent_shaft_abutment_count</t>
         </is>
       </c>
       <c r="L118" s="5" t="inlineStr">
@@ -5973,20 +6435,25 @@
       </c>
       <c r="M118" s="5" t="inlineStr">
         <is>
-          <t>schiedel_vent_channel_3x_count</t>
-        </is>
-      </c>
+          <t>vent_shaft_abutment_count</t>
+        </is>
+      </c>
+      <c r="N118" s="5" t="n"/>
+      <c r="O118" s="5" t="n"/>
+      <c r="P118" s="5" t="n"/>
+      <c r="Q118" s="5" t="n"/>
+      <c r="R118" s="5" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>Количество доставок вентканалов</t>
+          <t>Отверстия в стенах из газоблока</t>
         </is>
       </c>
       <c r="B119" s="5" t="n"/>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>маш</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
@@ -5996,7 +6463,7 @@
       </c>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t>Введите или подтвердите количество доставок вентканалов.</t>
+          <t>Проверьте количество отверстий в газоблоке.</t>
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr"/>
@@ -6005,20 +6472,753 @@
       <c r="I119" s="5" t="inlineStr"/>
       <c r="J119" s="5" t="inlineStr">
         <is>
+          <t>flat_roof</t>
+        </is>
+      </c>
+      <c r="K119" s="5" t="inlineStr">
+        <is>
+          <t>gas_block_wall_holes_count</t>
+        </is>
+      </c>
+      <c r="L119" s="5" t="inlineStr">
+        <is>
+          <t>SUPPLIER_INPUT</t>
+        </is>
+      </c>
+      <c r="M119" s="5" t="inlineStr">
+        <is>
+          <t>gas_block_wall_holes_count</t>
+        </is>
+      </c>
+      <c r="N119" s="5" t="n"/>
+      <c r="O119" s="5" t="n"/>
+      <c r="P119" s="5" t="n"/>
+      <c r="Q119" s="5" t="n"/>
+      <c r="R119" s="5" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>Подъем материалов автокраном</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="n"/>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>смена</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t>Проверьте</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="inlineStr">
+        <is>
+          <t>Укажите смены автокрана для кровли.</t>
+        </is>
+      </c>
+      <c r="F120" s="5" t="inlineStr"/>
+      <c r="G120" s="5" t="inlineStr"/>
+      <c r="H120" s="5" t="inlineStr"/>
+      <c r="I120" s="5" t="inlineStr"/>
+      <c r="J120" s="5" t="inlineStr">
+        <is>
+          <t>flat_roof</t>
+        </is>
+      </c>
+      <c r="K120" s="5" t="inlineStr">
+        <is>
+          <t>roof_crane_lifting_shifts</t>
+        </is>
+      </c>
+      <c r="L120" s="5" t="inlineStr">
+        <is>
+          <t>SUPPLIER_INPUT</t>
+        </is>
+      </c>
+      <c r="M120" s="5" t="inlineStr"/>
+      <c r="N120" s="5" t="n"/>
+      <c r="O120" s="5" t="n"/>
+      <c r="P120" s="5" t="n"/>
+      <c r="Q120" s="5" t="n"/>
+      <c r="R120" s="5" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>Расходные материалы кровли</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="n"/>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>руб.</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="inlineStr">
+        <is>
+          <t>Проверьте</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="inlineStr">
+        <is>
+          <t>Укажите сумму расходников кровли или будущую формулу.</t>
+        </is>
+      </c>
+      <c r="F121" s="5" t="inlineStr"/>
+      <c r="G121" s="5" t="inlineStr"/>
+      <c r="H121" s="5" t="inlineStr"/>
+      <c r="I121" s="5" t="inlineStr"/>
+      <c r="J121" s="5" t="inlineStr">
+        <is>
+          <t>flat_roof</t>
+        </is>
+      </c>
+      <c r="K121" s="5" t="inlineStr">
+        <is>
+          <t>roof_consumables_total_raw</t>
+        </is>
+      </c>
+      <c r="L121" s="5" t="inlineStr">
+        <is>
+          <t>SUPPLIER_INPUT</t>
+        </is>
+      </c>
+      <c r="M121" s="5" t="inlineStr"/>
+      <c r="N121" s="5" t="n"/>
+      <c r="O121" s="5" t="n"/>
+      <c r="P121" s="5" t="n"/>
+      <c r="Q121" s="5" t="n"/>
+      <c r="R121" s="5" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t>Вывоз мусора кровли</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="n"/>
+      <c r="C122" s="5" t="inlineStr">
+        <is>
+          <t>маш</t>
+        </is>
+      </c>
+      <c r="D122" s="5" t="inlineStr">
+        <is>
+          <t>Проверьте</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="inlineStr">
+        <is>
+          <t>Укажите количество машин вывоза мусора по кровле.</t>
+        </is>
+      </c>
+      <c r="F122" s="5" t="inlineStr"/>
+      <c r="G122" s="5" t="inlineStr"/>
+      <c r="H122" s="5" t="inlineStr"/>
+      <c r="I122" s="5" t="inlineStr"/>
+      <c r="J122" s="5" t="inlineStr">
+        <is>
+          <t>flat_roof</t>
+        </is>
+      </c>
+      <c r="K122" s="5" t="inlineStr">
+        <is>
+          <t>roof_waste_removal_trucks</t>
+        </is>
+      </c>
+      <c r="L122" s="5" t="inlineStr">
+        <is>
+          <t>SUPPLIER_INPUT</t>
+        </is>
+      </c>
+      <c r="M122" s="5" t="inlineStr"/>
+      <c r="N122" s="5" t="n"/>
+      <c r="O122" s="5" t="n"/>
+      <c r="P122" s="5" t="n"/>
+      <c r="Q122" s="5" t="n"/>
+      <c r="R122" s="5" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>Логистика и снабжение кровли</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="n"/>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>руб.</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t>Проверьте</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="inlineStr">
+        <is>
+          <t>Укажите сумму логистики и снабжения кровли или будущую формулу.</t>
+        </is>
+      </c>
+      <c r="F123" s="5" t="inlineStr"/>
+      <c r="G123" s="5" t="inlineStr"/>
+      <c r="H123" s="5" t="inlineStr"/>
+      <c r="I123" s="5" t="inlineStr"/>
+      <c r="J123" s="5" t="inlineStr">
+        <is>
+          <t>flat_roof</t>
+        </is>
+      </c>
+      <c r="K123" s="5" t="inlineStr">
+        <is>
+          <t>roof_logistics_and_supply_total_raw</t>
+        </is>
+      </c>
+      <c r="L123" s="5" t="inlineStr">
+        <is>
+          <t>SUPPLIER_INPUT</t>
+        </is>
+      </c>
+      <c r="M123" s="5" t="inlineStr"/>
+      <c r="N123" s="5" t="n"/>
+      <c r="O123" s="5" t="n"/>
+      <c r="P123" s="5" t="n"/>
+      <c r="Q123" s="5" t="n"/>
+      <c r="R123" s="5" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>Технический надзор кровли</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="n"/>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>руб.</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="inlineStr">
+        <is>
+          <t>Проверьте</t>
+        </is>
+      </c>
+      <c r="E124" s="5" t="inlineStr">
+        <is>
+          <t>Укажите технический надзор по кровле.</t>
+        </is>
+      </c>
+      <c r="F124" s="5" t="inlineStr"/>
+      <c r="G124" s="5" t="inlineStr"/>
+      <c r="H124" s="5" t="inlineStr"/>
+      <c r="I124" s="5" t="inlineStr"/>
+      <c r="J124" s="5" t="inlineStr">
+        <is>
+          <t>flat_roof</t>
+        </is>
+      </c>
+      <c r="K124" s="5" t="inlineStr">
+        <is>
+          <t>technical_supervision_work_total</t>
+        </is>
+      </c>
+      <c r="L124" s="5" t="inlineStr">
+        <is>
+          <t>SUPPLIER_INPUT</t>
+        </is>
+      </c>
+      <c r="M124" s="5" t="inlineStr"/>
+      <c r="N124" s="5" t="n"/>
+      <c r="O124" s="5" t="n"/>
+      <c r="P124" s="5" t="n"/>
+      <c r="Q124" s="5" t="n"/>
+      <c r="R124" s="5" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>Заготовительно-складские расходы кровли</t>
+        </is>
+      </c>
+      <c r="B125" s="5" t="n"/>
+      <c r="C125" s="5" t="inlineStr">
+        <is>
+          <t>руб.</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="inlineStr">
+        <is>
+          <t>Проверьте</t>
+        </is>
+      </c>
+      <c r="E125" s="5" t="inlineStr">
+        <is>
+          <t>Укажите заготовительно-складские расходы по кровле.</t>
+        </is>
+      </c>
+      <c r="F125" s="5" t="inlineStr"/>
+      <c r="G125" s="5" t="inlineStr"/>
+      <c r="H125" s="5" t="inlineStr"/>
+      <c r="I125" s="5" t="inlineStr"/>
+      <c r="J125" s="5" t="inlineStr">
+        <is>
+          <t>flat_roof</t>
+        </is>
+      </c>
+      <c r="K125" s="5" t="inlineStr">
+        <is>
+          <t>procurement_storage_work_total</t>
+        </is>
+      </c>
+      <c r="L125" s="5" t="inlineStr">
+        <is>
+          <t>SUPPLIER_INPUT</t>
+        </is>
+      </c>
+      <c r="M125" s="5" t="inlineStr"/>
+      <c r="N125" s="5" t="n"/>
+      <c r="O125" s="5" t="n"/>
+      <c r="P125" s="5" t="n"/>
+      <c r="Q125" s="5" t="n"/>
+      <c r="R125" s="5" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="4" t="inlineStr">
+        <is>
+          <t>Вентиляционные каналы Schiedel</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="inlineStr"/>
+      <c r="C126" s="4" t="inlineStr"/>
+      <c r="D126" s="4" t="inlineStr"/>
+      <c r="E126" s="4" t="inlineStr"/>
+      <c r="F126" s="4" t="inlineStr"/>
+      <c r="G126" s="4" t="inlineStr"/>
+      <c r="H126" s="4" t="inlineStr"/>
+      <c r="I126" s="4" t="inlineStr"/>
+      <c r="J126" s="4" t="inlineStr"/>
+      <c r="K126" s="4" t="inlineStr"/>
+      <c r="L126" s="4" t="inlineStr"/>
+      <c r="M126" s="4" t="inlineStr"/>
+      <c r="N126" s="4" t="n"/>
+      <c r="O126" s="4" t="n"/>
+      <c r="P126" s="4" t="n"/>
+      <c r="Q126" s="4" t="n"/>
+      <c r="R126" s="4" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>Общая длина кладки вентканалов Schiedel</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="n"/>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>мп</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="inlineStr">
+        <is>
+          <t>Проверьте</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="inlineStr">
+        <is>
+          <t>Проверьте общую длину/высоту кладки вентканалов Schiedel.</t>
+        </is>
+      </c>
+      <c r="F127" s="5" t="inlineStr"/>
+      <c r="G127" s="5" t="inlineStr"/>
+      <c r="H127" s="5" t="inlineStr"/>
+      <c r="I127" s="5" t="inlineStr"/>
+      <c r="J127" s="5" t="inlineStr">
+        <is>
           <t>schiedel_vent_channels</t>
         </is>
       </c>
-      <c r="K119" s="5" t="inlineStr">
+      <c r="K127" s="5" t="inlineStr">
+        <is>
+          <t>schiedel_masonry_total_length_m</t>
+        </is>
+      </c>
+      <c r="L127" s="5" t="inlineStr">
+        <is>
+          <t>AUTO_PROJECT</t>
+        </is>
+      </c>
+      <c r="M127" s="5" t="inlineStr">
+        <is>
+          <t>schiedel_masonry_total_length_m</t>
+        </is>
+      </c>
+      <c r="N127" s="5" t="n"/>
+      <c r="O127" s="5" t="n"/>
+      <c r="P127" s="5" t="n"/>
+      <c r="Q127" s="5" t="n"/>
+      <c r="R127" s="5" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>Высота вентканала 1</t>
+        </is>
+      </c>
+      <c r="B128" s="5" t="n"/>
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="D128" s="5" t="inlineStr">
+        <is>
+          <t>Проверьте</t>
+        </is>
+      </c>
+      <c r="E128" s="5" t="inlineStr">
+        <is>
+          <t>Проверьте высоту вентканала 1 как контроль длины кладки.</t>
+        </is>
+      </c>
+      <c r="F128" s="5" t="inlineStr"/>
+      <c r="G128" s="5" t="inlineStr"/>
+      <c r="H128" s="5" t="inlineStr"/>
+      <c r="I128" s="5" t="inlineStr"/>
+      <c r="J128" s="5" t="inlineStr">
+        <is>
+          <t>schiedel_vent_channels</t>
+        </is>
+      </c>
+      <c r="K128" s="5" t="inlineStr">
+        <is>
+          <t>vent_channel_1_height_m</t>
+        </is>
+      </c>
+      <c r="L128" s="5" t="inlineStr">
+        <is>
+          <t>AUTO_PROJECT</t>
+        </is>
+      </c>
+      <c r="M128" s="5" t="inlineStr">
+        <is>
+          <t>vent_channel_1_height</t>
+        </is>
+      </c>
+      <c r="N128" s="5" t="n"/>
+      <c r="O128" s="5" t="n"/>
+      <c r="P128" s="5" t="n"/>
+      <c r="Q128" s="5" t="n"/>
+      <c r="R128" s="5" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
+          <t>Высота вентканала 2</t>
+        </is>
+      </c>
+      <c r="B129" s="5" t="n"/>
+      <c r="C129" s="5" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="D129" s="5" t="inlineStr">
+        <is>
+          <t>Проверьте</t>
+        </is>
+      </c>
+      <c r="E129" s="5" t="inlineStr">
+        <is>
+          <t>Проверьте высоту вентканала 2 как контроль длины кладки.</t>
+        </is>
+      </c>
+      <c r="F129" s="5" t="inlineStr"/>
+      <c r="G129" s="5" t="inlineStr"/>
+      <c r="H129" s="5" t="inlineStr"/>
+      <c r="I129" s="5" t="inlineStr"/>
+      <c r="J129" s="5" t="inlineStr">
+        <is>
+          <t>schiedel_vent_channels</t>
+        </is>
+      </c>
+      <c r="K129" s="5" t="inlineStr">
+        <is>
+          <t>vent_channel_2_height_m</t>
+        </is>
+      </c>
+      <c r="L129" s="5" t="inlineStr">
+        <is>
+          <t>AUTO_PROJECT</t>
+        </is>
+      </c>
+      <c r="M129" s="5" t="inlineStr">
+        <is>
+          <t>vent_channel_2_height</t>
+        </is>
+      </c>
+      <c r="N129" s="5" t="n"/>
+      <c r="O129" s="5" t="n"/>
+      <c r="P129" s="5" t="n"/>
+      <c r="Q129" s="5" t="n"/>
+      <c r="R129" s="5" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t>Количество вентканалов типа 2 для контроля длины</t>
+        </is>
+      </c>
+      <c r="B130" s="5" t="n"/>
+      <c r="C130" s="5" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D130" s="5" t="inlineStr">
+        <is>
+          <t>Проверьте</t>
+        </is>
+      </c>
+      <c r="E130" s="5" t="inlineStr">
+        <is>
+          <t>Проверьте количество вентканалов типа 2 для контрольной формулы длины.</t>
+        </is>
+      </c>
+      <c r="F130" s="5" t="inlineStr"/>
+      <c r="G130" s="5" t="inlineStr"/>
+      <c r="H130" s="5" t="inlineStr"/>
+      <c r="I130" s="5" t="inlineStr"/>
+      <c r="J130" s="5" t="inlineStr">
+        <is>
+          <t>schiedel_vent_channels</t>
+        </is>
+      </c>
+      <c r="K130" s="5" t="inlineStr">
+        <is>
+          <t>vent_channel_2_count</t>
+        </is>
+      </c>
+      <c r="L130" s="5" t="inlineStr">
+        <is>
+          <t>AUTO_PROJECT</t>
+        </is>
+      </c>
+      <c r="M130" s="5" t="inlineStr">
+        <is>
+          <t>vent_channel_2_count</t>
+        </is>
+      </c>
+      <c r="N130" s="5" t="n"/>
+      <c r="O130" s="5" t="n"/>
+      <c r="P130" s="5" t="n"/>
+      <c r="Q130" s="5" t="n"/>
+      <c r="R130" s="5" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>Сегменты / строки спецификации вентканалов</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="n"/>
+      <c r="C131" s="5" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="inlineStr">
+        <is>
+          <t>Проверьте</t>
+        </is>
+      </c>
+      <c r="E131" s="5" t="inlineStr">
+        <is>
+          <t>Проверьте строки спецификации вентканалов построчно, если есть.</t>
+        </is>
+      </c>
+      <c r="F131" s="5" t="inlineStr"/>
+      <c r="G131" s="5" t="inlineStr"/>
+      <c r="H131" s="5" t="inlineStr"/>
+      <c r="I131" s="5" t="inlineStr"/>
+      <c r="J131" s="5" t="inlineStr">
+        <is>
+          <t>schiedel_vent_channels</t>
+        </is>
+      </c>
+      <c r="K131" s="5" t="inlineStr">
+        <is>
+          <t>schiedel_vent_chimney_cladding_segments</t>
+        </is>
+      </c>
+      <c r="L131" s="5" t="inlineStr">
+        <is>
+          <t>AUTO_PROJECT</t>
+        </is>
+      </c>
+      <c r="M131" s="5" t="inlineStr">
+        <is>
+          <t>schiedel_vent_chimney_cladding_segments</t>
+        </is>
+      </c>
+      <c r="N131" s="5" t="n"/>
+      <c r="O131" s="5" t="n"/>
+      <c r="P131" s="5" t="n"/>
+      <c r="Q131" s="5" t="n"/>
+      <c r="R131" s="5" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>Вентиляционный канал 2х,36/25 см Schiedel — количество</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="n"/>
+      <c r="C132" s="5" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D132" s="5" t="inlineStr">
+        <is>
+          <t>Проверьте</t>
+        </is>
+      </c>
+      <c r="E132" s="5" t="inlineStr">
+        <is>
+          <t>Подтвердите закупочное количество Schiedel 2х по спецификации или таблице Елены.</t>
+        </is>
+      </c>
+      <c r="F132" s="5" t="inlineStr"/>
+      <c r="G132" s="5" t="inlineStr"/>
+      <c r="H132" s="5" t="inlineStr"/>
+      <c r="I132" s="5" t="inlineStr"/>
+      <c r="J132" s="5" t="inlineStr">
+        <is>
+          <t>schiedel_vent_channels</t>
+        </is>
+      </c>
+      <c r="K132" s="5" t="inlineStr">
+        <is>
+          <t>schiedel_vent_channel_2x_count</t>
+        </is>
+      </c>
+      <c r="L132" s="5" t="inlineStr">
+        <is>
+          <t>SUPPLIER_INPUT</t>
+        </is>
+      </c>
+      <c r="M132" s="5" t="inlineStr">
+        <is>
+          <t>schiedel_vent_channel_2x_count</t>
+        </is>
+      </c>
+      <c r="N132" s="5" t="n"/>
+      <c r="O132" s="5" t="n"/>
+      <c r="P132" s="5" t="n"/>
+      <c r="Q132" s="5" t="n"/>
+      <c r="R132" s="5" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>Вентиляционный канал 3х,52/25 см Schiedel — количество</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="n"/>
+      <c r="C133" s="5" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="inlineStr">
+        <is>
+          <t>Проверьте</t>
+        </is>
+      </c>
+      <c r="E133" s="5" t="inlineStr">
+        <is>
+          <t>Подтвердите закупочное количество Schiedel 3х по спецификации или таблице Елены.</t>
+        </is>
+      </c>
+      <c r="F133" s="5" t="inlineStr"/>
+      <c r="G133" s="5" t="inlineStr"/>
+      <c r="H133" s="5" t="inlineStr"/>
+      <c r="I133" s="5" t="inlineStr"/>
+      <c r="J133" s="5" t="inlineStr">
+        <is>
+          <t>schiedel_vent_channels</t>
+        </is>
+      </c>
+      <c r="K133" s="5" t="inlineStr">
+        <is>
+          <t>schiedel_vent_channel_3x_count</t>
+        </is>
+      </c>
+      <c r="L133" s="5" t="inlineStr">
+        <is>
+          <t>SUPPLIER_INPUT</t>
+        </is>
+      </c>
+      <c r="M133" s="5" t="inlineStr">
+        <is>
+          <t>schiedel_vent_channel_3x_count</t>
+        </is>
+      </c>
+      <c r="N133" s="5" t="n"/>
+      <c r="O133" s="5" t="n"/>
+      <c r="P133" s="5" t="n"/>
+      <c r="Q133" s="5" t="n"/>
+      <c r="R133" s="5" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>Количество доставок вентканалов</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="n"/>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>маш</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="inlineStr">
+        <is>
+          <t>Проверьте</t>
+        </is>
+      </c>
+      <c r="E134" s="5" t="inlineStr">
+        <is>
+          <t>Введите или подтвердите количество доставок вентканалов.</t>
+        </is>
+      </c>
+      <c r="F134" s="5" t="inlineStr"/>
+      <c r="G134" s="5" t="inlineStr"/>
+      <c r="H134" s="5" t="inlineStr"/>
+      <c r="I134" s="5" t="inlineStr"/>
+      <c r="J134" s="5" t="inlineStr">
+        <is>
+          <t>schiedel_vent_channels</t>
+        </is>
+      </c>
+      <c r="K134" s="5" t="inlineStr">
         <is>
           <t>schiedel_delivery_trips</t>
         </is>
       </c>
-      <c r="L119" s="5" t="inlineStr">
+      <c r="L134" s="5" t="inlineStr">
         <is>
           <t>MANUAL_REVIEW</t>
         </is>
       </c>
-      <c r="M119" s="5" t="inlineStr"/>
+      <c r="M134" s="5" t="inlineStr"/>
+      <c r="N134" s="5" t="n"/>
+      <c r="O134" s="5" t="n"/>
+      <c r="P134" s="5" t="n"/>
+      <c r="Q134" s="5" t="n"/>
+      <c r="R134" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13656,7 +14856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P64"/>
+  <dimension ref="A1:P57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -14166,7 +15366,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Стены и перемычки — Позиции перемычек</t>
+          <t>Перекрытие 1 этажа — Арматура плиты перекрытия 1-го этажа по диаметрам</t>
         </is>
       </c>
       <c r="B16" s="4" t="n"/>
@@ -14188,43 +15388,59 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Марка</t>
+          <t>Этаж</t>
         </is>
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>Длина одной, м</t>
+          <t>Компонент</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>Количество, шт</t>
+          <t>Класс стали</t>
         </is>
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>Итоговая длина, м</t>
+          <t>Диаметр, мм</t>
         </is>
       </c>
       <c r="E17" s="1" t="inlineStr">
         <is>
+          <t>Длина по спецификации, мп</t>
+        </is>
+      </c>
+      <c r="F17" s="1" t="inlineStr">
+        <is>
+          <t>Масса 1 м, кг/м</t>
+        </is>
+      </c>
+      <c r="G17" s="1" t="inlineStr">
+        <is>
+          <t>Длина прутка, м</t>
+        </is>
+      </c>
+      <c r="H17" s="1" t="inlineStr">
+        <is>
+          <t>Цена за метр, руб/мп</t>
+        </is>
+      </c>
+      <c r="I17" s="1" t="inlineStr">
+        <is>
           <t>Комментарий Елены</t>
         </is>
       </c>
-      <c r="F17" s="1" t="inlineStr">
+      <c r="J17" s="1" t="inlineStr">
         <is>
           <t>section_code</t>
         </is>
       </c>
-      <c r="G17" s="1" t="inlineStr">
+      <c r="K17" s="1" t="inlineStr">
         <is>
           <t>target_code</t>
         </is>
       </c>
-      <c r="H17" s="2" t="n"/>
-      <c r="I17" s="2" t="n"/>
-      <c r="J17" s="2" t="n"/>
-      <c r="K17" s="2" t="n"/>
       <c r="L17" s="2" t="n"/>
       <c r="M17" s="2" t="n"/>
       <c r="N17" s="2" t="n"/>
@@ -14252,7 +15468,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Перекрытие 1 этажа — Арматура плиты перекрытия 1-го этажа по диаметрам</t>
+          <t>Перекрытие 1 этажа — Ж/Б балки плиты перекрытия 1-го этажа</t>
         </is>
       </c>
       <c r="B19" s="4" t="n"/>
@@ -14274,59 +15490,51 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Этаж</t>
+          <t>Код</t>
         </is>
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>Компонент</t>
+          <t>Наименование</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>Класс стали</t>
+          <t>Длина, м</t>
         </is>
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>Диаметр, мм</t>
+          <t>Ширина, м</t>
         </is>
       </c>
       <c r="E20" s="1" t="inlineStr">
         <is>
-          <t>Длина по спецификации, мп</t>
+          <t>Высота, м</t>
         </is>
       </c>
       <c r="F20" s="1" t="inlineStr">
         <is>
-          <t>Масса 1 м, кг/м</t>
+          <t>Количество, шт</t>
         </is>
       </c>
       <c r="G20" s="1" t="inlineStr">
         <is>
-          <t>Длина прутка, м</t>
+          <t>Комментарий Елены</t>
         </is>
       </c>
       <c r="H20" s="1" t="inlineStr">
         <is>
-          <t>Цена за метр, руб/мп</t>
+          <t>section_code</t>
         </is>
       </c>
       <c r="I20" s="1" t="inlineStr">
         <is>
-          <t>Комментарий Елены</t>
-        </is>
-      </c>
-      <c r="J20" s="1" t="inlineStr">
-        <is>
-          <t>section_code</t>
-        </is>
-      </c>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
           <t>target_code</t>
         </is>
       </c>
+      <c r="J20" s="2" t="n"/>
+      <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="n"/>
       <c r="M20" s="2" t="n"/>
       <c r="N20" s="2" t="n"/>
@@ -14354,7 +15562,7 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Перекрытие 1 этажа — Ж/Б балки плиты перекрытия 1-го этажа</t>
+          <t>Перекрытие 1 этажа — Контрольные итоги таблицы Ж/Б балок</t>
         </is>
       </c>
       <c r="B22" s="4" t="n"/>
@@ -14376,49 +15584,37 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Код</t>
+          <t>Строка итога</t>
         </is>
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>Наименование</t>
+          <t>Значение</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>Длина, м</t>
+          <t>Ед.</t>
         </is>
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
-          <t>Ширина, м</t>
+          <t>Комментарий Елены</t>
         </is>
       </c>
       <c r="E23" s="1" t="inlineStr">
         <is>
-          <t>Высота, м</t>
+          <t>section_code</t>
         </is>
       </c>
       <c r="F23" s="1" t="inlineStr">
         <is>
-          <t>Количество, шт</t>
-        </is>
-      </c>
-      <c r="G23" s="1" t="inlineStr">
-        <is>
-          <t>Комментарий Елены</t>
-        </is>
-      </c>
-      <c r="H23" s="1" t="inlineStr">
-        <is>
-          <t>section_code</t>
-        </is>
-      </c>
-      <c r="I23" s="1" t="inlineStr">
-        <is>
           <t>target_code</t>
         </is>
       </c>
+      <c r="G23" s="2" t="n"/>
+      <c r="H23" s="2" t="n"/>
+      <c r="I23" s="2" t="n"/>
       <c r="J23" s="2" t="n"/>
       <c r="K23" s="2" t="n"/>
       <c r="L23" s="2" t="n"/>
@@ -14448,7 +15644,7 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Перекрытие 1 этажа — Контрольные итоги таблицы Ж/Б балок</t>
+          <t>Перекрытие 2 этажа — Позиции балок плиты перекрытия 2-го этажа</t>
         </is>
       </c>
       <c r="B25" s="4" t="n"/>
@@ -14470,37 +15666,49 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Строка итога</t>
+          <t>Код балки</t>
         </is>
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>Значение</t>
+          <t>Наименование</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>Ед.</t>
+          <t>Длина, м</t>
         </is>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
+          <t>Ширина, м</t>
+        </is>
+      </c>
+      <c r="E26" s="1" t="inlineStr">
+        <is>
+          <t>Высота, м</t>
+        </is>
+      </c>
+      <c r="F26" s="1" t="inlineStr">
+        <is>
+          <t>Количество, шт</t>
+        </is>
+      </c>
+      <c r="G26" s="1" t="inlineStr">
+        <is>
           <t>Комментарий Елены</t>
         </is>
       </c>
-      <c r="E26" s="1" t="inlineStr">
+      <c r="H26" s="1" t="inlineStr">
         <is>
           <t>section_code</t>
         </is>
       </c>
-      <c r="F26" s="1" t="inlineStr">
+      <c r="I26" s="1" t="inlineStr">
         <is>
           <t>target_code</t>
         </is>
       </c>
-      <c r="G26" s="2" t="n"/>
-      <c r="H26" s="2" t="n"/>
-      <c r="I26" s="2" t="n"/>
       <c r="J26" s="2" t="n"/>
       <c r="K26" s="2" t="n"/>
       <c r="L26" s="2" t="n"/>
@@ -14530,7 +15738,7 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Перекрытие 2 этажа — Позиции балок плиты перекрытия 2-го этажа</t>
+          <t>Перекрытие 2 этажа — Арматура плиты перекрытия 2-го этажа по диаметрам</t>
         </is>
       </c>
       <c r="B28" s="4" t="n"/>
@@ -14552,32 +15760,32 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Код балки</t>
+          <t>Класс стали</t>
         </is>
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>Наименование</t>
+          <t>Диаметр, мм</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>Длина, м</t>
+          <t>Длина по спецификации, мп</t>
         </is>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
-          <t>Ширина, м</t>
+          <t>Масса 1 м, кг/м</t>
         </is>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
-          <t>Высота, м</t>
+          <t>Длина прутка, м</t>
         </is>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
-          <t>Количество, шт</t>
+          <t>Цена за метр, руб/мп</t>
         </is>
       </c>
       <c r="G29" s="1" t="inlineStr">
@@ -14624,7 +15832,7 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Перекрытие 2 этажа — Арматура плиты перекрытия 2-го этажа по диаметрам</t>
+          <t>Кровля — Сырые строки спецификации кровли</t>
         </is>
       </c>
       <c r="B31" s="4" t="n"/>
@@ -14646,49 +15854,37 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>Класс стали</t>
+          <t>Наименование</t>
         </is>
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>Диаметр, мм</t>
+          <t>Количество</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>Длина по спецификации, мп</t>
+          <t>Ед.</t>
         </is>
       </c>
       <c r="D32" s="1" t="inlineStr">
         <is>
-          <t>Масса 1 м, кг/м</t>
+          <t>Комментарий Елены</t>
         </is>
       </c>
       <c r="E32" s="1" t="inlineStr">
         <is>
-          <t>Длина прутка, м</t>
+          <t>section_code</t>
         </is>
       </c>
       <c r="F32" s="1" t="inlineStr">
         <is>
-          <t>Цена за метр, руб/мп</t>
-        </is>
-      </c>
-      <c r="G32" s="1" t="inlineStr">
-        <is>
-          <t>Комментарий Елены</t>
-        </is>
-      </c>
-      <c r="H32" s="1" t="inlineStr">
-        <is>
-          <t>section_code</t>
-        </is>
-      </c>
-      <c r="I32" s="1" t="inlineStr">
-        <is>
           <t>target_code</t>
         </is>
       </c>
+      <c r="G32" s="2" t="n"/>
+      <c r="H32" s="2" t="n"/>
+      <c r="I32" s="2" t="n"/>
       <c r="J32" s="2" t="n"/>
       <c r="K32" s="2" t="n"/>
       <c r="L32" s="2" t="n"/>
@@ -14718,7 +15914,7 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Кровля — Сырые строки спецификации кровли</t>
+          <t>Вентиляционные каналы Schiedel — Сегменты / строки спецификации вентканалов</t>
         </is>
       </c>
       <c r="B34" s="4" t="n"/>
@@ -14745,30 +15941,34 @@
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>Количество</t>
+          <t>Высота / длина, м</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>Ед.</t>
+          <t>Количество, шт</t>
         </is>
       </c>
       <c r="D35" s="1" t="inlineStr">
         <is>
+          <t>Итоговая длина, м</t>
+        </is>
+      </c>
+      <c r="E35" s="1" t="inlineStr">
+        <is>
           <t>Комментарий Елены</t>
         </is>
       </c>
-      <c r="E35" s="1" t="inlineStr">
+      <c r="F35" s="1" t="inlineStr">
         <is>
           <t>section_code</t>
         </is>
       </c>
-      <c r="F35" s="1" t="inlineStr">
+      <c r="G35" s="1" t="inlineStr">
         <is>
           <t>target_code</t>
         </is>
       </c>
-      <c r="G35" s="2" t="n"/>
       <c r="H35" s="2" t="n"/>
       <c r="I35" s="2" t="n"/>
       <c r="J35" s="2" t="n"/>
@@ -14800,7 +16000,7 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Вентиляционные каналы Schiedel — Сегменты / строки спецификации вентканалов</t>
+          <t>Будущие detail-шаблоны (общие заготовки, не привязаны к конкретному контракту)</t>
         </is>
       </c>
       <c r="B37" s="4" t="n"/>
@@ -14820,41 +16020,13 @@
       <c r="P37" s="4" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>Наименование</t>
-        </is>
-      </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>Высота / длина, м</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>Количество, шт</t>
-        </is>
-      </c>
-      <c r="D38" s="1" t="inlineStr">
-        <is>
-          <t>Итоговая длина, м</t>
-        </is>
-      </c>
-      <c r="E38" s="1" t="inlineStr">
-        <is>
-          <t>Комментарий Елены</t>
-        </is>
-      </c>
-      <c r="F38" s="1" t="inlineStr">
-        <is>
-          <t>section_code</t>
-        </is>
-      </c>
-      <c r="G38" s="1" t="inlineStr">
-        <is>
-          <t>target_code</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="n"/>
+      <c r="B38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n"/>
+      <c r="E38" s="2" t="n"/>
+      <c r="F38" s="2" t="n"/>
+      <c r="G38" s="2" t="n"/>
       <c r="H38" s="2" t="n"/>
       <c r="I38" s="2" t="n"/>
       <c r="J38" s="2" t="n"/>
@@ -14866,1060 +16038,830 @@
       <c r="P38" s="2" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n"/>
-      <c r="B39" s="2" t="n"/>
-      <c r="C39" s="2" t="n"/>
-      <c r="D39" s="2" t="n"/>
-      <c r="E39" s="2" t="n"/>
-      <c r="F39" s="2" t="n"/>
-      <c r="G39" s="2" t="n"/>
-      <c r="H39" s="2" t="n"/>
-      <c r="I39" s="2" t="n"/>
-      <c r="J39" s="2" t="n"/>
-      <c r="K39" s="2" t="n"/>
-      <c r="L39" s="2" t="n"/>
-      <c r="M39" s="2" t="n"/>
-      <c r="N39" s="2" t="n"/>
-      <c r="O39" s="2" t="n"/>
-      <c r="P39" s="2" t="n"/>
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Арматура</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr"/>
+      <c r="C39" s="4" t="inlineStr"/>
+      <c r="D39" s="4" t="inlineStr"/>
+      <c r="E39" s="4" t="inlineStr"/>
+      <c r="F39" s="4" t="inlineStr"/>
+      <c r="G39" s="4" t="inlineStr"/>
+      <c r="H39" s="4" t="inlineStr"/>
+      <c r="I39" s="4" t="inlineStr"/>
+      <c r="J39" s="4" t="inlineStr"/>
+      <c r="K39" s="4" t="inlineStr"/>
+      <c r="L39" s="4" t="inlineStr"/>
+      <c r="M39" s="4" t="inlineStr"/>
+      <c r="N39" s="4" t="inlineStr"/>
+      <c r="O39" s="4" t="inlineStr"/>
+      <c r="P39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>Будущие detail-шаблоны (общие заготовки, не привязаны к конкретному контракту)</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="n"/>
-      <c r="C40" s="4" t="n"/>
-      <c r="D40" s="4" t="n"/>
-      <c r="E40" s="4" t="n"/>
-      <c r="F40" s="4" t="n"/>
-      <c r="G40" s="4" t="n"/>
-      <c r="H40" s="4" t="n"/>
-      <c r="I40" s="4" t="n"/>
-      <c r="J40" s="4" t="n"/>
-      <c r="K40" s="4" t="n"/>
-      <c r="L40" s="4" t="n"/>
-      <c r="M40" s="4" t="n"/>
-      <c r="N40" s="4" t="n"/>
-      <c r="O40" s="4" t="n"/>
-      <c r="P40" s="4" t="n"/>
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>Тип</t>
+        </is>
+      </c>
+      <c r="B40" s="1" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="C40" s="1" t="inlineStr">
+        <is>
+          <t>Длина, м</t>
+        </is>
+      </c>
+      <c r="D40" s="1" t="inlineStr">
+        <is>
+          <t>Глубина, м</t>
+        </is>
+      </c>
+      <c r="E40" s="1" t="inlineStr">
+        <is>
+          <t>Ширина, м</t>
+        </is>
+      </c>
+      <c r="F40" s="1" t="inlineStr">
+        <is>
+          <t>Объем, м3</t>
+        </is>
+      </c>
+      <c r="G40" s="1" t="inlineStr">
+        <is>
+          <t>Диаметр, мм</t>
+        </is>
+      </c>
+      <c r="H40" s="1" t="inlineStr">
+        <is>
+          <t>Длина одной, м</t>
+        </is>
+      </c>
+      <c r="I40" s="1" t="inlineStr">
+        <is>
+          <t>Количество</t>
+        </is>
+      </c>
+      <c r="J40" s="1" t="inlineStr">
+        <is>
+          <t>Итоговая длина, м</t>
+        </is>
+      </c>
+      <c r="K40" s="1" t="inlineStr">
+        <is>
+          <t>Включено</t>
+        </is>
+      </c>
+      <c r="L40" s="1" t="inlineStr">
+        <is>
+          <t>Источник</t>
+        </is>
+      </c>
+      <c r="M40" s="1" t="inlineStr">
+        <is>
+          <t>Фрагмент проекта</t>
+        </is>
+      </c>
+      <c r="N40" s="1" t="inlineStr">
+        <is>
+          <t>Комментарий Елены</t>
+        </is>
+      </c>
+      <c r="O40" s="1" t="inlineStr">
+        <is>
+          <t>section_code</t>
+        </is>
+      </c>
+      <c r="P40" s="1" t="inlineStr">
+        <is>
+          <t>detail_table_key</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n"/>
-      <c r="B41" s="2" t="n"/>
-      <c r="C41" s="2" t="n"/>
-      <c r="D41" s="2" t="n"/>
-      <c r="E41" s="2" t="n"/>
-      <c r="F41" s="2" t="n"/>
-      <c r="G41" s="2" t="n"/>
-      <c r="H41" s="2" t="n"/>
-      <c r="I41" s="2" t="n"/>
-      <c r="J41" s="2" t="n"/>
-      <c r="K41" s="2" t="n"/>
-      <c r="L41" s="2" t="n"/>
-      <c r="M41" s="2" t="n"/>
-      <c r="N41" s="2" t="n"/>
-      <c r="O41" s="2" t="n"/>
-      <c r="P41" s="2" t="n"/>
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>Арматура</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Марка / позиция арматуры</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr"/>
+      <c r="D41" s="7" t="inlineStr"/>
+      <c r="E41" s="7" t="inlineStr"/>
+      <c r="F41" s="7" t="inlineStr"/>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>Диаметр, мм</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>Длина, м/п</t>
+        </is>
+      </c>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>Количество</t>
+        </is>
+      </c>
+      <c r="J41" s="7" t="inlineStr">
+        <is>
+          <t>Итоговая длина, м/п</t>
+        </is>
+      </c>
+      <c r="K41" s="7" t="inlineStr"/>
+      <c r="L41" s="7" t="inlineStr"/>
+      <c r="M41" s="7" t="inlineStr">
+        <is>
+          <t>Для foundation/floor slabs/load-bearing/lintels: spec_length_m является первичной единицей, если PDF дает м/п.</t>
+        </is>
+      </c>
+      <c r="N41" s="7" t="inlineStr"/>
+      <c r="O41" s="7" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="P41" s="7" t="inlineStr">
+        <is>
+          <t>rebar_items</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>Арматура</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr"/>
-      <c r="C42" s="4" t="inlineStr"/>
-      <c r="D42" s="4" t="inlineStr"/>
-      <c r="E42" s="4" t="inlineStr"/>
-      <c r="F42" s="4" t="inlineStr"/>
-      <c r="G42" s="4" t="inlineStr"/>
-      <c r="H42" s="4" t="inlineStr"/>
-      <c r="I42" s="4" t="inlineStr"/>
-      <c r="J42" s="4" t="inlineStr"/>
-      <c r="K42" s="4" t="inlineStr"/>
-      <c r="L42" s="4" t="inlineStr"/>
-      <c r="M42" s="4" t="inlineStr"/>
-      <c r="N42" s="4" t="inlineStr"/>
-      <c r="O42" s="4" t="inlineStr"/>
-      <c r="P42" s="4" t="inlineStr"/>
+      <c r="A42" s="2" t="n"/>
+      <c r="B42" s="2" t="n"/>
+      <c r="C42" s="2" t="n"/>
+      <c r="D42" s="2" t="n"/>
+      <c r="E42" s="2" t="n"/>
+      <c r="F42" s="2" t="n"/>
+      <c r="G42" s="2" t="n"/>
+      <c r="H42" s="2" t="n"/>
+      <c r="I42" s="2" t="n"/>
+      <c r="J42" s="2" t="n"/>
+      <c r="K42" s="2" t="n"/>
+      <c r="L42" s="2" t="n"/>
+      <c r="M42" s="2" t="n"/>
+      <c r="N42" s="2" t="n"/>
+      <c r="O42" s="2" t="n"/>
+      <c r="P42" s="2" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Балки</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr"/>
+      <c r="C43" s="4" t="inlineStr"/>
+      <c r="D43" s="4" t="inlineStr"/>
+      <c r="E43" s="4" t="inlineStr"/>
+      <c r="F43" s="4" t="inlineStr"/>
+      <c r="G43" s="4" t="inlineStr"/>
+      <c r="H43" s="4" t="inlineStr"/>
+      <c r="I43" s="4" t="inlineStr"/>
+      <c r="J43" s="4" t="inlineStr"/>
+      <c r="K43" s="4" t="inlineStr"/>
+      <c r="L43" s="4" t="inlineStr"/>
+      <c r="M43" s="4" t="inlineStr"/>
+      <c r="N43" s="4" t="inlineStr"/>
+      <c r="O43" s="4" t="inlineStr"/>
+      <c r="P43" s="4" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
         <is>
           <t>Тип</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr">
+      <c r="B44" s="1" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>Длина, м</t>
         </is>
       </c>
-      <c r="D43" s="1" t="inlineStr">
+      <c r="D44" s="1" t="inlineStr">
         <is>
           <t>Глубина, м</t>
         </is>
       </c>
-      <c r="E43" s="1" t="inlineStr">
+      <c r="E44" s="1" t="inlineStr">
         <is>
           <t>Ширина, м</t>
         </is>
       </c>
-      <c r="F43" s="1" t="inlineStr">
+      <c r="F44" s="1" t="inlineStr">
         <is>
           <t>Объем, м3</t>
         </is>
       </c>
-      <c r="G43" s="1" t="inlineStr">
+      <c r="G44" s="1" t="inlineStr">
         <is>
           <t>Диаметр, мм</t>
         </is>
       </c>
-      <c r="H43" s="1" t="inlineStr">
+      <c r="H44" s="1" t="inlineStr">
         <is>
           <t>Длина одной, м</t>
         </is>
       </c>
-      <c r="I43" s="1" t="inlineStr">
+      <c r="I44" s="1" t="inlineStr">
         <is>
           <t>Количество</t>
         </is>
       </c>
-      <c r="J43" s="1" t="inlineStr">
+      <c r="J44" s="1" t="inlineStr">
         <is>
           <t>Итоговая длина, м</t>
         </is>
       </c>
-      <c r="K43" s="1" t="inlineStr">
+      <c r="K44" s="1" t="inlineStr">
         <is>
           <t>Включено</t>
         </is>
       </c>
-      <c r="L43" s="1" t="inlineStr">
+      <c r="L44" s="1" t="inlineStr">
         <is>
           <t>Источник</t>
         </is>
       </c>
-      <c r="M43" s="1" t="inlineStr">
+      <c r="M44" s="1" t="inlineStr">
         <is>
           <t>Фрагмент проекта</t>
         </is>
       </c>
-      <c r="N43" s="1" t="inlineStr">
+      <c r="N44" s="1" t="inlineStr">
         <is>
           <t>Комментарий Елены</t>
         </is>
       </c>
-      <c r="O43" s="1" t="inlineStr">
+      <c r="O44" s="1" t="inlineStr">
         <is>
           <t>section_code</t>
         </is>
       </c>
-      <c r="P43" s="1" t="inlineStr">
+      <c r="P44" s="1" t="inlineStr">
         <is>
           <t>detail_table_key</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>Арматура</t>
-        </is>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>Марка / позиция арматуры</t>
-        </is>
-      </c>
-      <c r="C44" s="7" t="inlineStr"/>
-      <c r="D44" s="7" t="inlineStr"/>
-      <c r="E44" s="7" t="inlineStr"/>
-      <c r="F44" s="7" t="inlineStr"/>
-      <c r="G44" s="7" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>Балка</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>Балка / позиция</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>Длина, м</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>Высота, м</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>Ширина, м</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr"/>
+      <c r="G45" s="7" t="inlineStr"/>
+      <c r="H45" s="7" t="inlineStr"/>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>Количество</t>
+        </is>
+      </c>
+      <c r="J45" s="7" t="inlineStr"/>
+      <c r="K45" s="7" t="inlineStr"/>
+      <c r="L45" s="7" t="inlineStr"/>
+      <c r="M45" s="7" t="inlineStr">
+        <is>
+          <t>Для плит перекрытия с балками: геометрия балки и/или строка спецификации Ж/Б балок.</t>
+        </is>
+      </c>
+      <c r="N45" s="7" t="inlineStr"/>
+      <c r="O45" s="7" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="P45" s="7" t="inlineStr">
+        <is>
+          <t>beam_items</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n"/>
+      <c r="B46" s="2" t="n"/>
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="n"/>
+      <c r="E46" s="2" t="n"/>
+      <c r="F46" s="2" t="n"/>
+      <c r="G46" s="2" t="n"/>
+      <c r="H46" s="2" t="n"/>
+      <c r="I46" s="2" t="n"/>
+      <c r="J46" s="2" t="n"/>
+      <c r="K46" s="2" t="n"/>
+      <c r="L46" s="2" t="n"/>
+      <c r="M46" s="2" t="n"/>
+      <c r="N46" s="2" t="n"/>
+      <c r="O46" s="2" t="n"/>
+      <c r="P46" s="2" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Вентканалы / сегменты</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr"/>
+      <c r="C47" s="4" t="inlineStr"/>
+      <c r="D47" s="4" t="inlineStr"/>
+      <c r="E47" s="4" t="inlineStr"/>
+      <c r="F47" s="4" t="inlineStr"/>
+      <c r="G47" s="4" t="inlineStr"/>
+      <c r="H47" s="4" t="inlineStr"/>
+      <c r="I47" s="4" t="inlineStr"/>
+      <c r="J47" s="4" t="inlineStr"/>
+      <c r="K47" s="4" t="inlineStr"/>
+      <c r="L47" s="4" t="inlineStr"/>
+      <c r="M47" s="4" t="inlineStr"/>
+      <c r="N47" s="4" t="inlineStr"/>
+      <c r="O47" s="4" t="inlineStr"/>
+      <c r="P47" s="4" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>Тип</t>
+        </is>
+      </c>
+      <c r="B48" s="1" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="C48" s="1" t="inlineStr">
+        <is>
+          <t>Длина, м</t>
+        </is>
+      </c>
+      <c r="D48" s="1" t="inlineStr">
+        <is>
+          <t>Глубина, м</t>
+        </is>
+      </c>
+      <c r="E48" s="1" t="inlineStr">
+        <is>
+          <t>Ширина, м</t>
+        </is>
+      </c>
+      <c r="F48" s="1" t="inlineStr">
+        <is>
+          <t>Объем, м3</t>
+        </is>
+      </c>
+      <c r="G48" s="1" t="inlineStr">
         <is>
           <t>Диаметр, мм</t>
         </is>
       </c>
-      <c r="H44" s="7" t="inlineStr">
-        <is>
-          <t>Длина, м/п</t>
-        </is>
-      </c>
-      <c r="I44" s="7" t="inlineStr">
+      <c r="H48" s="1" t="inlineStr">
+        <is>
+          <t>Длина одной, м</t>
+        </is>
+      </c>
+      <c r="I48" s="1" t="inlineStr">
         <is>
           <t>Количество</t>
         </is>
       </c>
-      <c r="J44" s="7" t="inlineStr">
-        <is>
-          <t>Итоговая длина, м/п</t>
-        </is>
-      </c>
-      <c r="K44" s="7" t="inlineStr"/>
-      <c r="L44" s="7" t="inlineStr"/>
-      <c r="M44" s="7" t="inlineStr">
-        <is>
-          <t>Для foundation/floor slabs/load-bearing/lintels: spec_length_m является первичной единицей, если PDF дает м/п.</t>
-        </is>
-      </c>
-      <c r="N44" s="7" t="inlineStr"/>
-      <c r="O44" s="7" t="inlineStr">
+      <c r="J48" s="1" t="inlineStr">
+        <is>
+          <t>Итоговая длина, м</t>
+        </is>
+      </c>
+      <c r="K48" s="1" t="inlineStr">
+        <is>
+          <t>Включено</t>
+        </is>
+      </c>
+      <c r="L48" s="1" t="inlineStr">
+        <is>
+          <t>Источник</t>
+        </is>
+      </c>
+      <c r="M48" s="1" t="inlineStr">
+        <is>
+          <t>Фрагмент проекта</t>
+        </is>
+      </c>
+      <c r="N48" s="1" t="inlineStr">
+        <is>
+          <t>Комментарий Елены</t>
+        </is>
+      </c>
+      <c r="O48" s="1" t="inlineStr">
+        <is>
+          <t>section_code</t>
+        </is>
+      </c>
+      <c r="P48" s="1" t="inlineStr">
+        <is>
+          <t>detail_table_key</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>Вентканал</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>Сегмент / канал</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>Длина, м</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr"/>
+      <c r="E49" s="7" t="inlineStr"/>
+      <c r="F49" s="7" t="inlineStr"/>
+      <c r="G49" s="7" t="inlineStr"/>
+      <c r="H49" s="7" t="inlineStr"/>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>Количество</t>
+        </is>
+      </c>
+      <c r="J49" s="7" t="inlineStr"/>
+      <c r="K49" s="7" t="inlineStr"/>
+      <c r="L49" s="7" t="inlineStr"/>
+      <c r="M49" s="7" t="inlineStr">
+        <is>
+          <t>Для Schiedel и обкладки вентканалов, если PDF дает повторяющиеся сегменты.</t>
+        </is>
+      </c>
+      <c r="N49" s="7" t="inlineStr"/>
+      <c r="O49" s="7" t="inlineStr">
         <is>
           <t>template</t>
         </is>
       </c>
-      <c r="P44" s="7" t="inlineStr">
-        <is>
-          <t>rebar_items</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="n"/>
-      <c r="B45" s="2" t="n"/>
-      <c r="C45" s="2" t="n"/>
-      <c r="D45" s="2" t="n"/>
-      <c r="E45" s="2" t="n"/>
-      <c r="F45" s="2" t="n"/>
-      <c r="G45" s="2" t="n"/>
-      <c r="H45" s="2" t="n"/>
-      <c r="I45" s="2" t="n"/>
-      <c r="J45" s="2" t="n"/>
-      <c r="K45" s="2" t="n"/>
-      <c r="L45" s="2" t="n"/>
-      <c r="M45" s="2" t="n"/>
-      <c r="N45" s="2" t="n"/>
-      <c r="O45" s="2" t="n"/>
-      <c r="P45" s="2" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>Балки</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr"/>
-      <c r="C46" s="4" t="inlineStr"/>
-      <c r="D46" s="4" t="inlineStr"/>
-      <c r="E46" s="4" t="inlineStr"/>
-      <c r="F46" s="4" t="inlineStr"/>
-      <c r="G46" s="4" t="inlineStr"/>
-      <c r="H46" s="4" t="inlineStr"/>
-      <c r="I46" s="4" t="inlineStr"/>
-      <c r="J46" s="4" t="inlineStr"/>
-      <c r="K46" s="4" t="inlineStr"/>
-      <c r="L46" s="4" t="inlineStr"/>
-      <c r="M46" s="4" t="inlineStr"/>
-      <c r="N46" s="4" t="inlineStr"/>
-      <c r="O46" s="4" t="inlineStr"/>
-      <c r="P46" s="4" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr">
+      <c r="P49" s="7" t="inlineStr">
+        <is>
+          <t>vent_chimney_cladding_segments</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n"/>
+      <c r="B50" s="2" t="n"/>
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="2" t="n"/>
+      <c r="E50" s="2" t="n"/>
+      <c r="F50" s="2" t="n"/>
+      <c r="G50" s="2" t="n"/>
+      <c r="H50" s="2" t="n"/>
+      <c r="I50" s="2" t="n"/>
+      <c r="J50" s="2" t="n"/>
+      <c r="K50" s="2" t="n"/>
+      <c r="L50" s="2" t="n"/>
+      <c r="M50" s="2" t="n"/>
+      <c r="N50" s="2" t="n"/>
+      <c r="O50" s="2" t="n"/>
+      <c r="P50" s="2" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Спецификация материалов</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr"/>
+      <c r="C51" s="4" t="inlineStr"/>
+      <c r="D51" s="4" t="inlineStr"/>
+      <c r="E51" s="4" t="inlineStr"/>
+      <c r="F51" s="4" t="inlineStr"/>
+      <c r="G51" s="4" t="inlineStr"/>
+      <c r="H51" s="4" t="inlineStr"/>
+      <c r="I51" s="4" t="inlineStr"/>
+      <c r="J51" s="4" t="inlineStr"/>
+      <c r="K51" s="4" t="inlineStr"/>
+      <c r="L51" s="4" t="inlineStr"/>
+      <c r="M51" s="4" t="inlineStr"/>
+      <c r="N51" s="4" t="inlineStr"/>
+      <c r="O51" s="4" t="inlineStr"/>
+      <c r="P51" s="4" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
         <is>
           <t>Тип</t>
         </is>
       </c>
-      <c r="B47" s="1" t="inlineStr">
+      <c r="B52" s="1" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>Длина, м</t>
         </is>
       </c>
-      <c r="D47" s="1" t="inlineStr">
+      <c r="D52" s="1" t="inlineStr">
         <is>
           <t>Глубина, м</t>
         </is>
       </c>
-      <c r="E47" s="1" t="inlineStr">
+      <c r="E52" s="1" t="inlineStr">
         <is>
           <t>Ширина, м</t>
         </is>
       </c>
-      <c r="F47" s="1" t="inlineStr">
+      <c r="F52" s="1" t="inlineStr">
         <is>
           <t>Объем, м3</t>
         </is>
       </c>
-      <c r="G47" s="1" t="inlineStr">
+      <c r="G52" s="1" t="inlineStr">
         <is>
           <t>Диаметр, мм</t>
         </is>
       </c>
-      <c r="H47" s="1" t="inlineStr">
+      <c r="H52" s="1" t="inlineStr">
         <is>
           <t>Длина одной, м</t>
         </is>
       </c>
-      <c r="I47" s="1" t="inlineStr">
+      <c r="I52" s="1" t="inlineStr">
         <is>
           <t>Количество</t>
         </is>
       </c>
-      <c r="J47" s="1" t="inlineStr">
+      <c r="J52" s="1" t="inlineStr">
         <is>
           <t>Итоговая длина, м</t>
         </is>
       </c>
-      <c r="K47" s="1" t="inlineStr">
+      <c r="K52" s="1" t="inlineStr">
         <is>
           <t>Включено</t>
         </is>
       </c>
-      <c r="L47" s="1" t="inlineStr">
+      <c r="L52" s="1" t="inlineStr">
         <is>
           <t>Источник</t>
         </is>
       </c>
-      <c r="M47" s="1" t="inlineStr">
+      <c r="M52" s="1" t="inlineStr">
         <is>
           <t>Фрагмент проекта</t>
         </is>
       </c>
-      <c r="N47" s="1" t="inlineStr">
+      <c r="N52" s="1" t="inlineStr">
         <is>
           <t>Комментарий Елены</t>
         </is>
       </c>
-      <c r="O47" s="1" t="inlineStr">
+      <c r="O52" s="1" t="inlineStr">
         <is>
           <t>section_code</t>
         </is>
       </c>
-      <c r="P47" s="1" t="inlineStr">
+      <c r="P52" s="1" t="inlineStr">
         <is>
           <t>detail_table_key</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="7" t="inlineStr">
-        <is>
-          <t>Балка</t>
-        </is>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>Балка / позиция</t>
-        </is>
-      </c>
-      <c r="C48" s="7" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>Материал</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>Материал / строка спецификации</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr"/>
+      <c r="D53" s="7" t="inlineStr"/>
+      <c r="E53" s="7" t="inlineStr"/>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>Объем, м3</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr"/>
+      <c r="H53" s="7" t="inlineStr"/>
+      <c r="I53" s="7" t="inlineStr">
+        <is>
+          <t>Количество</t>
+        </is>
+      </c>
+      <c r="J53" s="7" t="inlineStr"/>
+      <c r="K53" s="7" t="inlineStr"/>
+      <c r="L53" s="7" t="inlineStr"/>
+      <c r="M53" s="7" t="inlineStr">
+        <is>
+          <t>Для ЭППС, бетона, опалубки, мембран и других строк спецификаций, которые не являются отдельной геометрией.</t>
+        </is>
+      </c>
+      <c r="N53" s="7" t="inlineStr"/>
+      <c r="O53" s="7" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="P53" s="7" t="inlineStr">
+        <is>
+          <t>material_spec_rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n"/>
+      <c r="B54" s="2" t="n"/>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="2" t="n"/>
+      <c r="E54" s="2" t="n"/>
+      <c r="F54" s="2" t="n"/>
+      <c r="G54" s="2" t="n"/>
+      <c r="H54" s="2" t="n"/>
+      <c r="I54" s="2" t="n"/>
+      <c r="J54" s="2" t="n"/>
+      <c r="K54" s="2" t="n"/>
+      <c r="L54" s="2" t="n"/>
+      <c r="M54" s="2" t="n"/>
+      <c r="N54" s="2" t="n"/>
+      <c r="O54" s="2" t="n"/>
+      <c r="P54" s="2" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Сырые строки таблиц</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr"/>
+      <c r="C55" s="4" t="inlineStr"/>
+      <c r="D55" s="4" t="inlineStr"/>
+      <c r="E55" s="4" t="inlineStr"/>
+      <c r="F55" s="4" t="inlineStr"/>
+      <c r="G55" s="4" t="inlineStr"/>
+      <c r="H55" s="4" t="inlineStr"/>
+      <c r="I55" s="4" t="inlineStr"/>
+      <c r="J55" s="4" t="inlineStr"/>
+      <c r="K55" s="4" t="inlineStr"/>
+      <c r="L55" s="4" t="inlineStr"/>
+      <c r="M55" s="4" t="inlineStr"/>
+      <c r="N55" s="4" t="inlineStr"/>
+      <c r="O55" s="4" t="inlineStr"/>
+      <c r="P55" s="4" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>Тип</t>
+        </is>
+      </c>
+      <c r="B56" s="1" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>Длина, м</t>
         </is>
       </c>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>Высота, м</t>
-        </is>
-      </c>
-      <c r="E48" s="7" t="inlineStr">
+      <c r="D56" s="1" t="inlineStr">
+        <is>
+          <t>Глубина, м</t>
+        </is>
+      </c>
+      <c r="E56" s="1" t="inlineStr">
         <is>
           <t>Ширина, м</t>
         </is>
       </c>
-      <c r="F48" s="7" t="inlineStr"/>
-      <c r="G48" s="7" t="inlineStr"/>
-      <c r="H48" s="7" t="inlineStr"/>
-      <c r="I48" s="7" t="inlineStr">
+      <c r="F56" s="1" t="inlineStr">
+        <is>
+          <t>Объем, м3</t>
+        </is>
+      </c>
+      <c r="G56" s="1" t="inlineStr">
+        <is>
+          <t>Диаметр, мм</t>
+        </is>
+      </c>
+      <c r="H56" s="1" t="inlineStr">
+        <is>
+          <t>Длина одной, м</t>
+        </is>
+      </c>
+      <c r="I56" s="1" t="inlineStr">
         <is>
           <t>Количество</t>
         </is>
       </c>
-      <c r="J48" s="7" t="inlineStr"/>
-      <c r="K48" s="7" t="inlineStr"/>
-      <c r="L48" s="7" t="inlineStr"/>
-      <c r="M48" s="7" t="inlineStr">
-        <is>
-          <t>Для плит перекрытия с балками: геометрия балки и/или строка спецификации Ж/Б балок.</t>
-        </is>
-      </c>
-      <c r="N48" s="7" t="inlineStr"/>
-      <c r="O48" s="7" t="inlineStr">
+      <c r="J56" s="1" t="inlineStr">
+        <is>
+          <t>Итоговая длина, м</t>
+        </is>
+      </c>
+      <c r="K56" s="1" t="inlineStr">
+        <is>
+          <t>Включено</t>
+        </is>
+      </c>
+      <c r="L56" s="1" t="inlineStr">
+        <is>
+          <t>Источник</t>
+        </is>
+      </c>
+      <c r="M56" s="1" t="inlineStr">
+        <is>
+          <t>Фрагмент проекта</t>
+        </is>
+      </c>
+      <c r="N56" s="1" t="inlineStr">
+        <is>
+          <t>Комментарий Елены</t>
+        </is>
+      </c>
+      <c r="O56" s="1" t="inlineStr">
+        <is>
+          <t>section_code</t>
+        </is>
+      </c>
+      <c r="P56" s="1" t="inlineStr">
+        <is>
+          <t>detail_table_key</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>Raw row</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>Сырая строка PDF</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr"/>
+      <c r="D57" s="7" t="inlineStr"/>
+      <c r="E57" s="7" t="inlineStr"/>
+      <c r="F57" s="7" t="inlineStr"/>
+      <c r="G57" s="7" t="inlineStr"/>
+      <c r="H57" s="7" t="inlineStr"/>
+      <c r="I57" s="7" t="inlineStr"/>
+      <c r="J57" s="7" t="inlineStr"/>
+      <c r="K57" s="7" t="inlineStr"/>
+      <c r="L57" s="7" t="inlineStr"/>
+      <c r="M57" s="7" t="inlineStr">
+        <is>
+          <t>Raw table row from chat extraction before mapping to target_code.</t>
+        </is>
+      </c>
+      <c r="N57" s="7" t="inlineStr"/>
+      <c r="O57" s="7" t="inlineStr">
         <is>
           <t>template</t>
         </is>
       </c>
-      <c r="P48" s="7" t="inlineStr">
-        <is>
-          <t>beam_items</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="n"/>
-      <c r="B49" s="2" t="n"/>
-      <c r="C49" s="2" t="n"/>
-      <c r="D49" s="2" t="n"/>
-      <c r="E49" s="2" t="n"/>
-      <c r="F49" s="2" t="n"/>
-      <c r="G49" s="2" t="n"/>
-      <c r="H49" s="2" t="n"/>
-      <c r="I49" s="2" t="n"/>
-      <c r="J49" s="2" t="n"/>
-      <c r="K49" s="2" t="n"/>
-      <c r="L49" s="2" t="n"/>
-      <c r="M49" s="2" t="n"/>
-      <c r="N49" s="2" t="n"/>
-      <c r="O49" s="2" t="n"/>
-      <c r="P49" s="2" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>Перемычки</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr"/>
-      <c r="C50" s="4" t="inlineStr"/>
-      <c r="D50" s="4" t="inlineStr"/>
-      <c r="E50" s="4" t="inlineStr"/>
-      <c r="F50" s="4" t="inlineStr"/>
-      <c r="G50" s="4" t="inlineStr"/>
-      <c r="H50" s="4" t="inlineStr"/>
-      <c r="I50" s="4" t="inlineStr"/>
-      <c r="J50" s="4" t="inlineStr"/>
-      <c r="K50" s="4" t="inlineStr"/>
-      <c r="L50" s="4" t="inlineStr"/>
-      <c r="M50" s="4" t="inlineStr"/>
-      <c r="N50" s="4" t="inlineStr"/>
-      <c r="O50" s="4" t="inlineStr"/>
-      <c r="P50" s="4" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>Тип</t>
-        </is>
-      </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>Наименование</t>
-        </is>
-      </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>Длина, м</t>
-        </is>
-      </c>
-      <c r="D51" s="1" t="inlineStr">
-        <is>
-          <t>Глубина, м</t>
-        </is>
-      </c>
-      <c r="E51" s="1" t="inlineStr">
-        <is>
-          <t>Ширина, м</t>
-        </is>
-      </c>
-      <c r="F51" s="1" t="inlineStr">
-        <is>
-          <t>Объем, м3</t>
-        </is>
-      </c>
-      <c r="G51" s="1" t="inlineStr">
-        <is>
-          <t>Диаметр, мм</t>
-        </is>
-      </c>
-      <c r="H51" s="1" t="inlineStr">
-        <is>
-          <t>Длина одной, м</t>
-        </is>
-      </c>
-      <c r="I51" s="1" t="inlineStr">
-        <is>
-          <t>Количество</t>
-        </is>
-      </c>
-      <c r="J51" s="1" t="inlineStr">
-        <is>
-          <t>Итоговая длина, м</t>
-        </is>
-      </c>
-      <c r="K51" s="1" t="inlineStr">
-        <is>
-          <t>Включено</t>
-        </is>
-      </c>
-      <c r="L51" s="1" t="inlineStr">
-        <is>
-          <t>Источник</t>
-        </is>
-      </c>
-      <c r="M51" s="1" t="inlineStr">
-        <is>
-          <t>Фрагмент проекта</t>
-        </is>
-      </c>
-      <c r="N51" s="1" t="inlineStr">
-        <is>
-          <t>Комментарий Елены</t>
-        </is>
-      </c>
-      <c r="O51" s="1" t="inlineStr">
-        <is>
-          <t>section_code</t>
-        </is>
-      </c>
-      <c r="P51" s="1" t="inlineStr">
-        <is>
-          <t>detail_table_key</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="7" t="inlineStr">
-        <is>
-          <t>Перемычка</t>
-        </is>
-      </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>Перемычка / U-блок</t>
-        </is>
-      </c>
-      <c r="C52" s="7" t="inlineStr">
-        <is>
-          <t>Длина, м</t>
-        </is>
-      </c>
-      <c r="D52" s="7" t="inlineStr"/>
-      <c r="E52" s="7" t="inlineStr"/>
-      <c r="F52" s="7" t="inlineStr"/>
-      <c r="G52" s="7" t="inlineStr"/>
-      <c r="H52" s="7" t="inlineStr"/>
-      <c r="I52" s="7" t="inlineStr">
-        <is>
-          <t>Количество</t>
-        </is>
-      </c>
-      <c r="J52" s="7" t="inlineStr">
-        <is>
-          <t>Итоговая длина, м</t>
-        </is>
-      </c>
-      <c r="K52" s="7" t="inlineStr"/>
-      <c r="L52" s="7" t="inlineStr"/>
-      <c r="M52" s="7" t="inlineStr">
-        <is>
-          <t>Для load_bearing_walls_lintels: длины перемычек и арматуры перемычек.</t>
-        </is>
-      </c>
-      <c r="N52" s="7" t="inlineStr"/>
-      <c r="O52" s="7" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
-      <c r="P52" s="7" t="inlineStr">
-        <is>
-          <t>lintel_items</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="n"/>
-      <c r="B53" s="2" t="n"/>
-      <c r="C53" s="2" t="n"/>
-      <c r="D53" s="2" t="n"/>
-      <c r="E53" s="2" t="n"/>
-      <c r="F53" s="2" t="n"/>
-      <c r="G53" s="2" t="n"/>
-      <c r="H53" s="2" t="n"/>
-      <c r="I53" s="2" t="n"/>
-      <c r="J53" s="2" t="n"/>
-      <c r="K53" s="2" t="n"/>
-      <c r="L53" s="2" t="n"/>
-      <c r="M53" s="2" t="n"/>
-      <c r="N53" s="2" t="n"/>
-      <c r="O53" s="2" t="n"/>
-      <c r="P53" s="2" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>Вентканалы / сегменты</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr"/>
-      <c r="C54" s="4" t="inlineStr"/>
-      <c r="D54" s="4" t="inlineStr"/>
-      <c r="E54" s="4" t="inlineStr"/>
-      <c r="F54" s="4" t="inlineStr"/>
-      <c r="G54" s="4" t="inlineStr"/>
-      <c r="H54" s="4" t="inlineStr"/>
-      <c r="I54" s="4" t="inlineStr"/>
-      <c r="J54" s="4" t="inlineStr"/>
-      <c r="K54" s="4" t="inlineStr"/>
-      <c r="L54" s="4" t="inlineStr"/>
-      <c r="M54" s="4" t="inlineStr"/>
-      <c r="N54" s="4" t="inlineStr"/>
-      <c r="O54" s="4" t="inlineStr"/>
-      <c r="P54" s="4" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t>Тип</t>
-        </is>
-      </c>
-      <c r="B55" s="1" t="inlineStr">
-        <is>
-          <t>Наименование</t>
-        </is>
-      </c>
-      <c r="C55" s="1" t="inlineStr">
-        <is>
-          <t>Длина, м</t>
-        </is>
-      </c>
-      <c r="D55" s="1" t="inlineStr">
-        <is>
-          <t>Глубина, м</t>
-        </is>
-      </c>
-      <c r="E55" s="1" t="inlineStr">
-        <is>
-          <t>Ширина, м</t>
-        </is>
-      </c>
-      <c r="F55" s="1" t="inlineStr">
-        <is>
-          <t>Объем, м3</t>
-        </is>
-      </c>
-      <c r="G55" s="1" t="inlineStr">
-        <is>
-          <t>Диаметр, мм</t>
-        </is>
-      </c>
-      <c r="H55" s="1" t="inlineStr">
-        <is>
-          <t>Длина одной, м</t>
-        </is>
-      </c>
-      <c r="I55" s="1" t="inlineStr">
-        <is>
-          <t>Количество</t>
-        </is>
-      </c>
-      <c r="J55" s="1" t="inlineStr">
-        <is>
-          <t>Итоговая длина, м</t>
-        </is>
-      </c>
-      <c r="K55" s="1" t="inlineStr">
-        <is>
-          <t>Включено</t>
-        </is>
-      </c>
-      <c r="L55" s="1" t="inlineStr">
-        <is>
-          <t>Источник</t>
-        </is>
-      </c>
-      <c r="M55" s="1" t="inlineStr">
-        <is>
-          <t>Фрагмент проекта</t>
-        </is>
-      </c>
-      <c r="N55" s="1" t="inlineStr">
-        <is>
-          <t>Комментарий Елены</t>
-        </is>
-      </c>
-      <c r="O55" s="1" t="inlineStr">
-        <is>
-          <t>section_code</t>
-        </is>
-      </c>
-      <c r="P55" s="1" t="inlineStr">
-        <is>
-          <t>detail_table_key</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="7" t="inlineStr">
-        <is>
-          <t>Вентканал</t>
-        </is>
-      </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>Сегмент / канал</t>
-        </is>
-      </c>
-      <c r="C56" s="7" t="inlineStr">
-        <is>
-          <t>Длина, м</t>
-        </is>
-      </c>
-      <c r="D56" s="7" t="inlineStr"/>
-      <c r="E56" s="7" t="inlineStr"/>
-      <c r="F56" s="7" t="inlineStr"/>
-      <c r="G56" s="7" t="inlineStr"/>
-      <c r="H56" s="7" t="inlineStr"/>
-      <c r="I56" s="7" t="inlineStr">
-        <is>
-          <t>Количество</t>
-        </is>
-      </c>
-      <c r="J56" s="7" t="inlineStr"/>
-      <c r="K56" s="7" t="inlineStr"/>
-      <c r="L56" s="7" t="inlineStr"/>
-      <c r="M56" s="7" t="inlineStr">
-        <is>
-          <t>Для Schiedel и обкладки вентканалов, если PDF дает повторяющиеся сегменты.</t>
-        </is>
-      </c>
-      <c r="N56" s="7" t="inlineStr"/>
-      <c r="O56" s="7" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
-      <c r="P56" s="7" t="inlineStr">
-        <is>
-          <t>vent_chimney_cladding_segments</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="n"/>
-      <c r="B57" s="2" t="n"/>
-      <c r="C57" s="2" t="n"/>
-      <c r="D57" s="2" t="n"/>
-      <c r="E57" s="2" t="n"/>
-      <c r="F57" s="2" t="n"/>
-      <c r="G57" s="2" t="n"/>
-      <c r="H57" s="2" t="n"/>
-      <c r="I57" s="2" t="n"/>
-      <c r="J57" s="2" t="n"/>
-      <c r="K57" s="2" t="n"/>
-      <c r="L57" s="2" t="n"/>
-      <c r="M57" s="2" t="n"/>
-      <c r="N57" s="2" t="n"/>
-      <c r="O57" s="2" t="n"/>
-      <c r="P57" s="2" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>Спецификация материалов</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="inlineStr"/>
-      <c r="C58" s="4" t="inlineStr"/>
-      <c r="D58" s="4" t="inlineStr"/>
-      <c r="E58" s="4" t="inlineStr"/>
-      <c r="F58" s="4" t="inlineStr"/>
-      <c r="G58" s="4" t="inlineStr"/>
-      <c r="H58" s="4" t="inlineStr"/>
-      <c r="I58" s="4" t="inlineStr"/>
-      <c r="J58" s="4" t="inlineStr"/>
-      <c r="K58" s="4" t="inlineStr"/>
-      <c r="L58" s="4" t="inlineStr"/>
-      <c r="M58" s="4" t="inlineStr"/>
-      <c r="N58" s="4" t="inlineStr"/>
-      <c r="O58" s="4" t="inlineStr"/>
-      <c r="P58" s="4" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="1" t="inlineStr">
-        <is>
-          <t>Тип</t>
-        </is>
-      </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>Наименование</t>
-        </is>
-      </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t>Длина, м</t>
-        </is>
-      </c>
-      <c r="D59" s="1" t="inlineStr">
-        <is>
-          <t>Глубина, м</t>
-        </is>
-      </c>
-      <c r="E59" s="1" t="inlineStr">
-        <is>
-          <t>Ширина, м</t>
-        </is>
-      </c>
-      <c r="F59" s="1" t="inlineStr">
-        <is>
-          <t>Объем, м3</t>
-        </is>
-      </c>
-      <c r="G59" s="1" t="inlineStr">
-        <is>
-          <t>Диаметр, мм</t>
-        </is>
-      </c>
-      <c r="H59" s="1" t="inlineStr">
-        <is>
-          <t>Длина одной, м</t>
-        </is>
-      </c>
-      <c r="I59" s="1" t="inlineStr">
-        <is>
-          <t>Количество</t>
-        </is>
-      </c>
-      <c r="J59" s="1" t="inlineStr">
-        <is>
-          <t>Итоговая длина, м</t>
-        </is>
-      </c>
-      <c r="K59" s="1" t="inlineStr">
-        <is>
-          <t>Включено</t>
-        </is>
-      </c>
-      <c r="L59" s="1" t="inlineStr">
-        <is>
-          <t>Источник</t>
-        </is>
-      </c>
-      <c r="M59" s="1" t="inlineStr">
-        <is>
-          <t>Фрагмент проекта</t>
-        </is>
-      </c>
-      <c r="N59" s="1" t="inlineStr">
-        <is>
-          <t>Комментарий Елены</t>
-        </is>
-      </c>
-      <c r="O59" s="1" t="inlineStr">
-        <is>
-          <t>section_code</t>
-        </is>
-      </c>
-      <c r="P59" s="1" t="inlineStr">
-        <is>
-          <t>detail_table_key</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="7" t="inlineStr">
-        <is>
-          <t>Материал</t>
-        </is>
-      </c>
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t>Материал / строка спецификации</t>
-        </is>
-      </c>
-      <c r="C60" s="7" t="inlineStr"/>
-      <c r="D60" s="7" t="inlineStr"/>
-      <c r="E60" s="7" t="inlineStr"/>
-      <c r="F60" s="7" t="inlineStr">
-        <is>
-          <t>Объем, м3</t>
-        </is>
-      </c>
-      <c r="G60" s="7" t="inlineStr"/>
-      <c r="H60" s="7" t="inlineStr"/>
-      <c r="I60" s="7" t="inlineStr">
-        <is>
-          <t>Количество</t>
-        </is>
-      </c>
-      <c r="J60" s="7" t="inlineStr"/>
-      <c r="K60" s="7" t="inlineStr"/>
-      <c r="L60" s="7" t="inlineStr"/>
-      <c r="M60" s="7" t="inlineStr">
-        <is>
-          <t>Для ЭППС, бетона, опалубки, мембран и других строк спецификаций, которые не являются отдельной геометрией.</t>
-        </is>
-      </c>
-      <c r="N60" s="7" t="inlineStr"/>
-      <c r="O60" s="7" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
-      <c r="P60" s="7" t="inlineStr">
-        <is>
-          <t>material_spec_rows</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="n"/>
-      <c r="B61" s="2" t="n"/>
-      <c r="C61" s="2" t="n"/>
-      <c r="D61" s="2" t="n"/>
-      <c r="E61" s="2" t="n"/>
-      <c r="F61" s="2" t="n"/>
-      <c r="G61" s="2" t="n"/>
-      <c r="H61" s="2" t="n"/>
-      <c r="I61" s="2" t="n"/>
-      <c r="J61" s="2" t="n"/>
-      <c r="K61" s="2" t="n"/>
-      <c r="L61" s="2" t="n"/>
-      <c r="M61" s="2" t="n"/>
-      <c r="N61" s="2" t="n"/>
-      <c r="O61" s="2" t="n"/>
-      <c r="P61" s="2" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t>Сырые строки таблиц</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="inlineStr"/>
-      <c r="C62" s="4" t="inlineStr"/>
-      <c r="D62" s="4" t="inlineStr"/>
-      <c r="E62" s="4" t="inlineStr"/>
-      <c r="F62" s="4" t="inlineStr"/>
-      <c r="G62" s="4" t="inlineStr"/>
-      <c r="H62" s="4" t="inlineStr"/>
-      <c r="I62" s="4" t="inlineStr"/>
-      <c r="J62" s="4" t="inlineStr"/>
-      <c r="K62" s="4" t="inlineStr"/>
-      <c r="L62" s="4" t="inlineStr"/>
-      <c r="M62" s="4" t="inlineStr"/>
-      <c r="N62" s="4" t="inlineStr"/>
-      <c r="O62" s="4" t="inlineStr"/>
-      <c r="P62" s="4" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="1" t="inlineStr">
-        <is>
-          <t>Тип</t>
-        </is>
-      </c>
-      <c r="B63" s="1" t="inlineStr">
-        <is>
-          <t>Наименование</t>
-        </is>
-      </c>
-      <c r="C63" s="1" t="inlineStr">
-        <is>
-          <t>Длина, м</t>
-        </is>
-      </c>
-      <c r="D63" s="1" t="inlineStr">
-        <is>
-          <t>Глубина, м</t>
-        </is>
-      </c>
-      <c r="E63" s="1" t="inlineStr">
-        <is>
-          <t>Ширина, м</t>
-        </is>
-      </c>
-      <c r="F63" s="1" t="inlineStr">
-        <is>
-          <t>Объем, м3</t>
-        </is>
-      </c>
-      <c r="G63" s="1" t="inlineStr">
-        <is>
-          <t>Диаметр, мм</t>
-        </is>
-      </c>
-      <c r="H63" s="1" t="inlineStr">
-        <is>
-          <t>Длина одной, м</t>
-        </is>
-      </c>
-      <c r="I63" s="1" t="inlineStr">
-        <is>
-          <t>Количество</t>
-        </is>
-      </c>
-      <c r="J63" s="1" t="inlineStr">
-        <is>
-          <t>Итоговая длина, м</t>
-        </is>
-      </c>
-      <c r="K63" s="1" t="inlineStr">
-        <is>
-          <t>Включено</t>
-        </is>
-      </c>
-      <c r="L63" s="1" t="inlineStr">
-        <is>
-          <t>Источник</t>
-        </is>
-      </c>
-      <c r="M63" s="1" t="inlineStr">
-        <is>
-          <t>Фрагмент проекта</t>
-        </is>
-      </c>
-      <c r="N63" s="1" t="inlineStr">
-        <is>
-          <t>Комментарий Елены</t>
-        </is>
-      </c>
-      <c r="O63" s="1" t="inlineStr">
-        <is>
-          <t>section_code</t>
-        </is>
-      </c>
-      <c r="P63" s="1" t="inlineStr">
-        <is>
-          <t>detail_table_key</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="7" t="inlineStr">
-        <is>
-          <t>Raw row</t>
-        </is>
-      </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>Сырая строка PDF</t>
-        </is>
-      </c>
-      <c r="C64" s="7" t="inlineStr"/>
-      <c r="D64" s="7" t="inlineStr"/>
-      <c r="E64" s="7" t="inlineStr"/>
-      <c r="F64" s="7" t="inlineStr"/>
-      <c r="G64" s="7" t="inlineStr"/>
-      <c r="H64" s="7" t="inlineStr"/>
-      <c r="I64" s="7" t="inlineStr"/>
-      <c r="J64" s="7" t="inlineStr"/>
-      <c r="K64" s="7" t="inlineStr"/>
-      <c r="L64" s="7" t="inlineStr"/>
-      <c r="M64" s="7" t="inlineStr">
-        <is>
-          <t>Raw table row from chat extraction before mapping to target_code.</t>
-        </is>
-      </c>
-      <c r="N64" s="7" t="inlineStr"/>
-      <c r="O64" s="7" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
-      <c r="P64" s="7" t="inlineStr">
+      <c r="P57" s="7" t="inlineStr">
         <is>
           <t>raw_table_rows</t>
         </is>
@@ -16026,7 +16968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16134,7 +17076,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
@@ -16178,7 +17120,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
@@ -16222,7 +17164,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
@@ -16467,7 +17409,7 @@
         </is>
       </c>
       <c r="C17" s="7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D17" s="7" t="n">
         <v>25</v>
@@ -16505,7 +17447,7 @@
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>17</v>
@@ -16543,7 +17485,7 @@
         </is>
       </c>
       <c r="C19" s="7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D19" s="7" t="n">
         <v>15</v>
@@ -16558,7 +17500,7 @@
         <v>19</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I19" s="7" t="n">
         <v>25</v>
@@ -16772,17 +17714,17 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>lintel_items</t>
+          <t>vent_chimney_cladding_segments</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Перемычки</t>
+          <t>Вентканалы / сегменты</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Перемычка</t>
+          <t>Вентканал</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
@@ -16792,7 +17734,7 @@
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>Для load_bearing_walls_lintels: длины перемычек и арматуры перемычек.</t>
+          <t>Для Schiedel и обкладки вентканалов, если PDF дает повторяющиеся сегменты.</t>
         </is>
       </c>
       <c r="F27" s="7" t="n"/>
@@ -16804,17 +17746,17 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>vent_chimney_cladding_segments</t>
+          <t>material_spec_rows</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Вентканалы / сегменты</t>
+          <t>Спецификация материалов</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Вентканал</t>
+          <t>Материал</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
@@ -16824,7 +17766,7 @@
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>Для Schiedel и обкладки вентканалов, если PDF дает повторяющиеся сегменты.</t>
+          <t>Для ЭППС, бетона, опалубки, мембран и других строк спецификаций, которые не являются отдельной геометрией.</t>
         </is>
       </c>
       <c r="F28" s="7" t="n"/>
@@ -16836,17 +17778,17 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>material_spec_rows</t>
+          <t>raw_table_rows</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Спецификация материалов</t>
+          <t>Сырые строки таблиц</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>Материал</t>
+          <t>Raw row</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
@@ -16856,7 +17798,7 @@
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>Для ЭППС, бетона, опалубки, мембран и других строк спецификаций, которые не являются отдельной геометрией.</t>
+          <t>Raw table row from chat extraction before mapping to target_code.</t>
         </is>
       </c>
       <c r="F29" s="7" t="n"/>
@@ -16864,38 +17806,6 @@
       <c r="H29" s="7" t="n"/>
       <c r="I29" s="7" t="n"/>
       <c r="J29" s="7" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>raw_table_rows</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>Сырые строки таблиц</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>Raw row</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>future sections</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>Raw table row from chat extraction before mapping to target_code.</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="n"/>
-      <c r="G30" s="7" t="n"/>
-      <c r="H30" s="7" t="n"/>
-      <c r="I30" s="7" t="n"/>
-      <c r="J30" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17313,6 +18223,7 @@
     "normalized_json_path": "sections.earthworks.parameters.trench_routes.rows",
     "value_kind": "repeated_rows",
     "row_key_field": "route_code",
+    "production_input": false,
     "columns": [
       {
         "key": "route_code",
@@ -17393,6 +18304,7 @@
     "normalized_json_path": "sections.earthworks.parameters.communications_pipe_items.rows",
     "value_kind": "repeated_rows",
     "row_key_field": "code",
+    "production_input": false,
     "columns": [
       {
         "key": "code",
@@ -18561,6 +19473,15 @@
     "normalized_json_path": "sections.foundation_slab.parameters.foundation_rebar_items.rows",
     "value_kind": "repeated_rows",
     "row_key_field": "code",
+    "production_input": true,
+    "item_label_columns": [
+      "steel_class",
+      "diameter_mm"
+    ],
+    "correction_columns": [
+      "source_length_m",
+      "kg_per_meter"
+    ],
     "columns": [
       {
         "key": "name",
@@ -21427,8 +22348,7 @@
     "value_kind": "scalar",
     "parser_mapping": {
       "target_codes": [
-        "lintel_total_length",
-        "lintel_items"
+        "lintel_total_length"
       ],
       "aliases_ru": [
         "суммарная длина перемычек",
@@ -21436,7 +22356,7 @@
         "ведомость перемычек"
       ],
       "expected_unit": "мп",
-      "notes": "Production uses spec_total_length. Row-by-row lintel_items may be kept as diagnostics."
+      "notes": "PDFs give this as an explicit total line in the lintel materials spec table (e.g. 'Длина перемычек в U-блоках'), verified against real ЮСВ/ТРЦ КР2 drawings 2026-07-12 — not a mark-by-mark table."
     },
     "review_behavior": {
       "show_to_user": true,
@@ -21608,6 +22528,15 @@
     "normalized_json_path": "sections.load_bearing_walls_lintels.parameters.main_wall_rebar_items.rows",
     "value_kind": "repeated_rows",
     "row_key_field": "code",
+    "production_input": true,
+    "item_label_columns": [
+      "steel_class",
+      "diameter_mm"
+    ],
+    "correction_columns": [
+      "spec_length_m",
+      "kg_per_meter"
+    ],
     "columns": [
       {
         "key": "floor",
@@ -21696,6 +22625,15 @@
     "normalized_json_path": "sections.load_bearing_walls_lintels.parameters.lintel_rebar_items.rows",
     "value_kind": "repeated_rows",
     "row_key_field": "code",
+    "production_input": true,
+    "item_label_columns": [
+      "steel_class",
+      "diameter_mm"
+    ],
+    "correction_columns": [
+      "spec_length_m",
+      "kg_per_meter"
+    ],
     "columns": [
       {
         "key": "floor",
@@ -21771,71 +22709,6 @@
       "max_value": null
     },
     "notes": "Do not mix with masonry reinforcement rows."
-  },
-  {
-    "key": "lintel_items",
-    "label_ru": "Позиции перемычек",
-    "unit": "м",
-    "source_class": "AUTO_PROJECT",
-    "required": false,
-    "review_sheet": "01_Проверка проекта",
-    "target_code": "lintel_items",
-    "calculator_input_path": "",
-    "normalized_json_path": "sections.load_bearing_walls_lintels.parameters.lintel_items.rows",
-    "value_kind": "repeated_rows",
-    "row_key_field": "mark",
-    "columns": [
-      {
-        "key": "mark",
-        "label_ru": "Марка",
-        "unit": "",
-        "value_kind": "string"
-      },
-      {
-        "key": "length_m",
-        "label_ru": "Длина одной",
-        "unit": "м",
-        "value_kind": "number"
-      },
-      {
-        "key": "count",
-        "label_ru": "Количество",
-        "unit": "шт",
-        "value_kind": "number"
-      },
-      {
-        "key": "total_length_m",
-        "label_ru": "Итоговая длина",
-        "unit": "м",
-        "value_kind": "number"
-      }
-    ],
-    "parser_mapping": {
-      "target_codes": [
-        "lintel_total_length",
-        "lintel_items"
-      ],
-      "aliases_ru": [
-        "ведомость перемычек",
-        "спецификация перемычек"
-      ],
-      "expected_unit": "м",
-      "notes": "Diagnostic breakdown; calculator production input is the lintel_total_length_m scalar above, not this breakdown."
-    },
-    "review_behavior": {
-      "show_to_user": true,
-      "allow_manual_override": true,
-      "status_if_missing": "optional",
-      "action_ru": "Необязательная разбивка перемычек по маркам, для справки; сверьте с lintel_total_length_m выше."
-    },
-    "mirror_to_details_sheet": true,
-    "mirror_notes": "Same rows shown read-only on 03_Детали объемов so Elena can check against the PDF spec table without opening it.",
-    "validation": {
-      "numeric": true,
-      "min_value": 0,
-      "max_value": null
-    },
-    "notes": "Diagnostic source table. Calculator production input is lintel_total_length_m. FUTURE NOTE (2026-07-09, non-blocking, nothing to do now): if `lintel_length_calc_method` is ever deliberately switched to `legacy_length_count_items`, these rows would feed the calculator's `LintelLength.from_dict()`, whose dataclass only declares `length_m`/`count` — the extra `mark`/`total_length_m` keys here would raise a TypeError on `**data` unpacking unless stripped first. Not relevant while `spec_total_length` stays the production mode; just don't forget it if that ever changes."
   }
 ]</t>
         </is>
@@ -24057,6 +24930,44 @@
     "notes": ""
   },
   {
+    "key": "beams_concrete_volume_m3",
+    "label_ru": "Объем бетона балок перекрытия 1-го этажа",
+    "unit": "м3",
+    "source_class": "AUTO_PROJECT",
+    "required": false,
+    "review_sheet": "01_Проверка проекта",
+    "target_code": "floor_slab_1_beams_concrete_volume",
+    "calculator_input_path": "beams_concrete_volume_m3",
+    "normalized_json_path": "sections.floor_slab_1.parameters.beams_concrete_volume_m3.value",
+    "value_kind": "scalar",
+    "parser_mapping": {
+      "target_codes": [
+        "floor_slab_1_beams_concrete_volume",
+        "beam_items"
+      ],
+      "aliases_ru": [
+        "бетон балок",
+        "объем бетона балок",
+        "бетон в теле плиты (балки)",
+        "бетон в теле плиты перекрытия"
+      ],
+      "expected_unit": "м3",
+      "notes": "Usually a ready 'Итого' line in the beam specification table (see beam_items below), separate from the slab's own concrete volume. If absent, leave null (not 0) so the calculator falls back to the sum of beam_items.concrete_volume_m3. Added 2026-07-12 after confirming both ЮСВ КР2 (лист 22) and ТРЦ КР2 (лист 31) give this as a ready total."
+    },
+    "review_behavior": {
+      "show_to_user": true,
+      "allow_manual_override": true,
+      "status_if_missing": "optional_default_zero",
+      "action_ru": "Если у этой плиты есть балки и в спецификации есть готовый итог по бетону балок, сверьте его; иначе оставьте пустым — он посчитается из позиций балок ниже."
+    },
+    "validation": {
+      "numeric": true,
+      "min_value": 0,
+      "max_value": null
+    },
+    "notes": "Calculator-code override added 2026-07-12 (exception to the normal never-touch-calculator-code rule, explicit user authorization) — mirrors the existing beams_formwork_area_m2 override pattern. beam_items rows remain required regardless for formwork area and insulation length/area, which have no scalar override."
+  },
+  {
     "key": "slab_outer_edge_eps_work_length_m",
     "label_ru": "ЭППС 100 мм торец плиты, длина работ",
     "unit": "мп",
@@ -24249,6 +25160,15 @@
     "normalized_json_path": "sections.floor_slab_1.parameters.floor_slab_1_rebar_items.rows",
     "value_kind": "repeated_rows",
     "row_key_field": "code",
+    "production_input": true,
+    "item_label_columns": [
+      "steel_class",
+      "diameter_mm"
+    ],
+    "correction_columns": [
+      "spec_length_m",
+      "kg_per_meter"
+    ],
     "columns": [
       {
         "key": "floor",
@@ -24337,6 +25257,16 @@
     "normalized_json_path": "sections.floor_slab_1.parameters.beam_items.rows",
     "value_kind": "repeated_rows",
     "row_key_field": "code",
+    "production_input": true,
+    "item_label_columns": [
+      "name"
+    ],
+    "correction_columns": [
+      "length_m",
+      "width_m",
+      "height_m",
+      "count"
+    ],
     "columns": [
       {
         "key": "code",
@@ -24415,6 +25345,7 @@
     "normalized_json_path": "sections.floor_slab_1.parameters.beam_table_controls.rows",
     "value_kind": "repeated_rows",
     "row_key_field": "label",
+    "production_input": false,
     "columns": [
       {
         "key": "label",
@@ -25948,6 +26879,44 @@
     "notes": "Do not send 0 explicitly when beam_items are present — 0 is treated as a real override and will suppress the per-beam sum. Leave null/absent instead."
   },
   {
+    "key": "beams_concrete_volume_m3",
+    "label_ru": "Объем бетона балок перекрытия 2-го этажа",
+    "unit": "м3",
+    "source_class": "AUTO_PROJECT",
+    "required": false,
+    "review_sheet": "01_Проверка проекта",
+    "target_code": "floor_slab_2_beams_concrete_volume",
+    "calculator_input_path": "beams_concrete_volume_m3",
+    "normalized_json_path": "sections.floor_slab_2.parameters.beams_concrete_volume_m3.value",
+    "value_kind": "scalar",
+    "parser_mapping": {
+      "target_codes": [
+        "floor_slab_2_beams_concrete_volume",
+        "floor_slab_2_beam_items"
+      ],
+      "aliases_ru": [
+        "бетон балок",
+        "объем бетона балок",
+        "бетон в теле плиты (балки)",
+        "бетон в теле плиты перекрытия"
+      ],
+      "expected_unit": "м3",
+      "notes": "Usually a ready 'Итого' line in the beam specification table (see beam_items below), separate from the slab's own concrete volume. If absent, leave null (not 0) so the calculator falls back to the sum of beam_items.concrete_volume_m3. Added 2026-07-12 after confirming both ЮСВ КР2 (лист 22) and ТРЦ КР2 (лист 31) give this as a ready total."
+    },
+    "review_behavior": {
+      "show_to_user": true,
+      "allow_manual_override": true,
+      "status_if_missing": "optional_default_zero",
+      "action_ru": "Если у этой плиты есть балки и в спецификации есть готовый итог по бетону балок, сверьте его; иначе оставьте пустым — он посчитается из позиций балок ниже."
+    },
+    "validation": {
+      "numeric": true,
+      "min_value": 0,
+      "max_value": null
+    },
+    "notes": "Calculator-code override added 2026-07-12 (exception to the normal never-touch-calculator-code rule, explicit user authorization) — mirrors the existing beams_formwork_area_m2 override pattern. Do not send 0 explicitly when beam_items are present — 0 is treated as a real override. beam_items rows remain required regardless for formwork area and insulation length/area, which have no scalar override."
+  },
+  {
     "key": "beam_items",
     "label_ru": "Позиции балок плиты перекрытия 2-го этажа",
     "unit": "м",
@@ -25959,6 +26928,16 @@
     "normalized_json_path": "sections.floor_slab_2.parameters.beam_items.rows",
     "value_kind": "repeated_rows",
     "row_key_field": "code",
+    "production_input": true,
+    "item_label_columns": [
+      "name"
+    ],
+    "correction_columns": [
+      "length_m",
+      "width_m",
+      "height_m",
+      "count"
+    ],
     "columns": [
       {
         "key": "code",
@@ -26178,6 +27157,15 @@
     "normalized_json_path": "sections.floor_slab_2.parameters.floor_slab_2_rebar_items.rows",
     "value_kind": "repeated_rows",
     "row_key_field": "code",
+    "production_input": true,
+    "item_label_columns": [
+      "steel_class",
+      "diameter_mm"
+    ],
+    "correction_columns": [
+      "spec_length_m",
+      "kg_per_meter"
+    ],
     "columns": [
       {
         "key": "steel_class",
@@ -26790,20 +27778,6 @@
         <is>
           <t>[
   {
-    "key": "beams_concrete_volume_m3",
-    "label_ru": "Бетон балок (сумма по позициям)",
-    "source_class": "AUTO_CALCULATED",
-    "formula": "sum(beam_items.length_m * beam_items.width_m * beam_items.height_m * beam_items.count)",
-    "leaf_inputs": [
-      {
-        "ref": "review_parameters.beam_items",
-        "source_class": "AUTO_PROJECT"
-      }
-    ],
-    "calculator_input_path": "",
-    "notes": "Computed by the calculator itself from beam_items; 0 when the group is empty. Shown here for workbook/report visibility, not sent as a separate calculator input."
-  },
-  {
     "key": "slab_concrete_volume_m3",
     "label_ru": "Бетон плиты (без балок)",
     "source_class": "AUTO_CALCULATED",
@@ -26814,12 +27788,12 @@
         "source_class": "AUTO_PROJECT"
       },
       {
-        "ref": "auto_calculated.beams_concrete_volume_m3",
-        "source_class": "AUTO_CALCULATED"
+        "ref": "review_parameters.beams_concrete_volume_m3",
+        "source_class": "AUTO_PROJECT"
       }
     ],
     "calculator_input_path": "",
-    "notes": "concrete_placing_volume_m3 is expected to already include beam concrete when beams exist, same convention as floor_slab_1_calculator.py. This is the concrete_placing_work estimate line's real quantity, not the raw scalar."
+    "notes": "concrete_placing_volume_m3 is expected to already include beam concrete when beams exist, same convention as floor_slab_1_calculator.py. beams_concrete_volume_m3 here already resolves to the sum of beam_items.concrete_volume_m3 when the scalar review_parameters value is left null (added 2026-07-12, mirrors edge_and_beam_formwork_area_m2's beams_formwork_area_m2 pattern). This is the concrete_placing_work estimate line's real quantity, not the raw scalar."
   },
   {
     "key": "edge_and_beam_formwork_area_m2",
@@ -28157,6 +29131,7 @@
     "normalized_json_path": "sections.flat_roof.parameters.roof_raw_material_spec_rows.rows",
     "value_kind": "repeated_rows",
     "row_key_field": "name",
+    "production_input": false,
     "columns": [
       {
         "key": "name",
@@ -30318,6 +31293,7 @@
     "normalized_json_path": "sections.schiedel_vent_channels.parameters.schiedel_vent_chimney_cladding_segments.rows",
     "value_kind": "repeated_rows",
     "row_key_field": "name",
+    "production_input": false,
     "columns": [
       {
         "key": "name",
